--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D393"/>
+  <dimension ref="A1:D396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
         <v>-1003035504222</v>
       </c>
       <c r="B3" t="n">
-        <v>12252</v>
+        <v>25744</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
@@ -479,7 +479,7 @@
         <v>-1002615496638</v>
       </c>
       <c r="B4" t="n">
-        <v>1663</v>
+        <v>6566</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
@@ -491,7 +491,7 @@
         <v>-1002795475468</v>
       </c>
       <c r="B5" t="n">
-        <v>16280</v>
+        <v>17791</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
@@ -503,7 +503,7 @@
         <v>-1001212305259</v>
       </c>
       <c r="B6" t="n">
-        <v>2872471</v>
+        <v>2963736</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
@@ -515,7 +515,7 @@
         <v>-1002864485836</v>
       </c>
       <c r="B7" t="n">
-        <v>92164</v>
+        <v>119478</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
@@ -551,7 +551,7 @@
         <v>-1002320283926</v>
       </c>
       <c r="B10" t="n">
-        <v>16679</v>
+        <v>22920</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
@@ -563,7 +563,7 @@
         <v>-1002510217399</v>
       </c>
       <c r="B11" t="n">
-        <v>12741</v>
+        <v>13630</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
@@ -575,7 +575,7 @@
         <v>-1002521509637</v>
       </c>
       <c r="B12" t="n">
-        <v>82105</v>
+        <v>91468</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
@@ -599,7 +599,7 @@
         <v>-1002189109599</v>
       </c>
       <c r="B14" t="n">
-        <v>794805</v>
+        <v>923209</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
@@ -611,7 +611,7 @@
         <v>-1002520212825</v>
       </c>
       <c r="B15" t="n">
-        <v>312</v>
+        <v>426</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
@@ -623,7 +623,7 @@
         <v>-1002747623711</v>
       </c>
       <c r="B16" t="n">
-        <v>329</v>
+        <v>798</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
@@ -635,7 +635,7 @@
         <v>-1002205410222</v>
       </c>
       <c r="B17" t="n">
-        <v>88673</v>
+        <v>117522</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -661,7 +661,7 @@
         <v>-1002527463407</v>
       </c>
       <c r="B19" t="n">
-        <v>773</v>
+        <v>1480</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
@@ -673,7 +673,7 @@
         <v>-1002623818368</v>
       </c>
       <c r="B20" t="n">
-        <v>73144</v>
+        <v>97339</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
@@ -685,7 +685,7 @@
         <v>-1002455033621</v>
       </c>
       <c r="B21" t="n">
-        <v>79692</v>
+        <v>88120</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
@@ -697,7 +697,7 @@
         <v>-1001596465392</v>
       </c>
       <c r="B22" t="n">
-        <v>4821087</v>
+        <v>4880874</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
@@ -709,7 +709,7 @@
         <v>-1001946166876</v>
       </c>
       <c r="B23" t="n">
-        <v>43697</v>
+        <v>43928</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
@@ -721,7 +721,7 @@
         <v>-1001818008631</v>
       </c>
       <c r="B24" t="n">
-        <v>13244</v>
+        <v>25563</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
@@ -733,7 +733,7 @@
         <v>-1001493770434</v>
       </c>
       <c r="B25" t="n">
-        <v>353859</v>
+        <v>354155</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
@@ -745,7 +745,7 @@
         <v>-1002473130324</v>
       </c>
       <c r="B26" t="n">
-        <v>29013</v>
+        <v>34152</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
@@ -769,7 +769,7 @@
         <v>-1002651996794</v>
       </c>
       <c r="B28" t="n">
-        <v>123655</v>
+        <v>130791</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
@@ -781,7 +781,7 @@
         <v>-1002555387875</v>
       </c>
       <c r="B29" t="n">
-        <v>54120</v>
+        <v>60964</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
@@ -805,7 +805,7 @@
         <v>-1002422251622</v>
       </c>
       <c r="B31" t="n">
-        <v>67342</v>
+        <v>84585</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
@@ -829,7 +829,7 @@
         <v>-1002454558597</v>
       </c>
       <c r="B33" t="n">
-        <v>174882</v>
+        <v>270773</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
@@ -841,7 +841,7 @@
         <v>-1001467801859</v>
       </c>
       <c r="B34" t="n">
-        <v>930222</v>
+        <v>979087</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
@@ -853,7 +853,7 @@
         <v>-1002322838597</v>
       </c>
       <c r="B35" t="n">
-        <v>1622623</v>
+        <v>2658777</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
@@ -889,7 +889,7 @@
         <v>-1002832898246</v>
       </c>
       <c r="B38" t="n">
-        <v>3653</v>
+        <v>8216</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
@@ -901,7 +901,7 @@
         <v>-1003092984130</v>
       </c>
       <c r="B39" t="n">
-        <v>49</v>
+        <v>532</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
@@ -913,7 +913,7 @@
         <v>-1001390053729</v>
       </c>
       <c r="B40" t="n">
-        <v>88503</v>
+        <v>90248</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
@@ -949,7 +949,7 @@
         <v>-1002556474841</v>
       </c>
       <c r="B43" t="n">
-        <v>40623</v>
+        <v>43739</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
@@ -961,7 +961,7 @@
         <v>-1002531829054</v>
       </c>
       <c r="B44" t="n">
-        <v>9246</v>
+        <v>15067</v>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
@@ -973,7 +973,7 @@
         <v>-1002750504156</v>
       </c>
       <c r="B45" t="n">
-        <v>857</v>
+        <v>1142</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
@@ -985,7 +985,7 @@
         <v>-1002359874556</v>
       </c>
       <c r="B46" t="n">
-        <v>18970</v>
+        <v>23939</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
@@ -1009,7 +1009,7 @@
         <v>-1002379714369</v>
       </c>
       <c r="B48" t="n">
-        <v>29658</v>
+        <v>38109</v>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
@@ -1021,7 +1021,7 @@
         <v>-1002985739762</v>
       </c>
       <c r="B49" t="n">
-        <v>163</v>
+        <v>642</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
@@ -1067,7 +1067,7 @@
         <v>-1003001093483</v>
       </c>
       <c r="B53" t="n">
-        <v>674</v>
+        <v>3510</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
@@ -1079,7 +1079,7 @@
         <v>-1001543478413</v>
       </c>
       <c r="B54" t="n">
-        <v>59697</v>
+        <v>61555</v>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
@@ -1091,7 +1091,7 @@
         <v>-1001668927089</v>
       </c>
       <c r="B55" t="n">
-        <v>103366</v>
+        <v>109246</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
@@ -1103,7 +1103,7 @@
         <v>-1002706892578</v>
       </c>
       <c r="B56" t="n">
-        <v>2825</v>
+        <v>6705</v>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
@@ -1115,7 +1115,7 @@
         <v>-1002761573267</v>
       </c>
       <c r="B57" t="n">
-        <v>88706</v>
+        <v>474933</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
@@ -1127,7 +1127,7 @@
         <v>-1002832174643</v>
       </c>
       <c r="B58" t="n">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
@@ -1139,7 +1139,7 @@
         <v>-1001929868118</v>
       </c>
       <c r="B59" t="n">
-        <v>2289</v>
+        <v>2411</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
@@ -1163,7 +1163,7 @@
         <v>-1003078207757</v>
       </c>
       <c r="B61" t="n">
-        <v>9</v>
+        <v>124</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
@@ -1189,7 +1189,7 @@
         <v>-1003048673651</v>
       </c>
       <c r="B63" t="n">
-        <v>2438</v>
+        <v>7398</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
@@ -1213,7 +1213,7 @@
         <v>-1001818742779</v>
       </c>
       <c r="B65" t="n">
-        <v>209637</v>
+        <v>244846</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
@@ -1225,7 +1225,7 @@
         <v>-1002845355669</v>
       </c>
       <c r="B66" t="n">
-        <v>3623</v>
+        <v>4040</v>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
@@ -1237,7 +1237,7 @@
         <v>-1002509299058</v>
       </c>
       <c r="B67" t="n">
-        <v>793</v>
+        <v>936</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
@@ -1249,7 +1249,7 @@
         <v>-1002728494984</v>
       </c>
       <c r="B68" t="n">
-        <v>1340</v>
+        <v>1992</v>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
@@ -1261,7 +1261,7 @@
         <v>-1002793180948</v>
       </c>
       <c r="B69" t="n">
-        <v>6225</v>
+        <v>10153</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
@@ -1273,7 +1273,7 @@
         <v>-1002519990156</v>
       </c>
       <c r="B70" t="n">
-        <v>7057</v>
+        <v>13047</v>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
@@ -1285,7 +1285,7 @@
         <v>-1002532154366</v>
       </c>
       <c r="B71" t="n">
-        <v>630</v>
+        <v>1268</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
@@ -1297,7 +1297,7 @@
         <v>-1002110839951</v>
       </c>
       <c r="B72" t="n">
-        <v>313548</v>
+        <v>338296</v>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
@@ -1309,7 +1309,7 @@
         <v>-1002679523819</v>
       </c>
       <c r="B73" t="n">
-        <v>2726</v>
+        <v>4071</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="n">
@@ -1321,7 +1321,7 @@
         <v>-1002619556227</v>
       </c>
       <c r="B74" t="n">
-        <v>10184</v>
+        <v>16392</v>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="n">
@@ -1333,7 +1333,7 @@
         <v>-1001859766402</v>
       </c>
       <c r="B75" t="n">
-        <v>28437</v>
+        <v>28811</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
@@ -1345,7 +1345,7 @@
         <v>-1002815530049</v>
       </c>
       <c r="B76" t="n">
-        <v>28103</v>
+        <v>31684</v>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
@@ -1357,7 +1357,7 @@
         <v>-1002683965508</v>
       </c>
       <c r="B77" t="n">
-        <v>7681</v>
+        <v>9393</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
@@ -1369,7 +1369,7 @@
         <v>-1002016912929</v>
       </c>
       <c r="B78" t="n">
-        <v>296415</v>
+        <v>303210</v>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
@@ -1381,7 +1381,7 @@
         <v>-1002591852942</v>
       </c>
       <c r="B79" t="n">
-        <v>59461</v>
+        <v>60109</v>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
@@ -1393,7 +1393,7 @@
         <v>-1002130498457</v>
       </c>
       <c r="B80" t="n">
-        <v>175980</v>
+        <v>179947</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
@@ -1405,7 +1405,7 @@
         <v>-1002274964696</v>
       </c>
       <c r="B81" t="n">
-        <v>1502</v>
+        <v>2682</v>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="n">
@@ -1429,7 +1429,7 @@
         <v>-1001741252369</v>
       </c>
       <c r="B83" t="n">
-        <v>35004</v>
+        <v>45760</v>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
@@ -1441,7 +1441,7 @@
         <v>-1002616170042</v>
       </c>
       <c r="B84" t="n">
-        <v>6262</v>
+        <v>6537</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
@@ -1453,7 +1453,7 @@
         <v>-1002437713625</v>
       </c>
       <c r="B85" t="n">
-        <v>20623</v>
+        <v>36084</v>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
@@ -1499,7 +1499,7 @@
         <v>-1002046646497</v>
       </c>
       <c r="B89" t="n">
-        <v>20434</v>
+        <v>22133</v>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
@@ -1511,7 +1511,7 @@
         <v>-1002114430690</v>
       </c>
       <c r="B90" t="n">
-        <v>46904</v>
+        <v>69964</v>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="n">
@@ -1523,7 +1523,7 @@
         <v>-1002532871843</v>
       </c>
       <c r="B91" t="n">
-        <v>6217</v>
+        <v>10323</v>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
@@ -1547,7 +1547,7 @@
         <v>-1002268045818</v>
       </c>
       <c r="B93" t="n">
-        <v>157271</v>
+        <v>179408</v>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="n">
@@ -1559,7 +1559,7 @@
         <v>-1002101571866</v>
       </c>
       <c r="B94" t="n">
-        <v>29796</v>
+        <v>30731</v>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="n">
@@ -1571,7 +1571,7 @@
         <v>-1002779291814</v>
       </c>
       <c r="B95" t="n">
-        <v>9296</v>
+        <v>11746</v>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
@@ -1583,7 +1583,7 @@
         <v>-1001473268532</v>
       </c>
       <c r="B96" t="n">
-        <v>744601</v>
+        <v>748350</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
@@ -1595,7 +1595,7 @@
         <v>-1002190969931</v>
       </c>
       <c r="B97" t="n">
-        <v>23960</v>
+        <v>27877</v>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
@@ -1619,7 +1619,7 @@
         <v>-1002071946221</v>
       </c>
       <c r="B99" t="n">
-        <v>7415</v>
+        <v>7552</v>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="n">
@@ -1631,7 +1631,7 @@
         <v>-1002581029977</v>
       </c>
       <c r="B100" t="n">
-        <v>109009</v>
+        <v>169123</v>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
@@ -1643,7 +1643,7 @@
         <v>-1002887971256</v>
       </c>
       <c r="B101" t="n">
-        <v>2168</v>
+        <v>2480</v>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
@@ -1667,7 +1667,7 @@
         <v>-1002312125060</v>
       </c>
       <c r="B103" t="n">
-        <v>46863</v>
+        <v>51098</v>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
@@ -1679,7 +1679,7 @@
         <v>-1001908446355</v>
       </c>
       <c r="B104" t="n">
-        <v>922343</v>
+        <v>989979</v>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
@@ -1691,7 +1691,7 @@
         <v>-1002278762192</v>
       </c>
       <c r="B105" t="n">
-        <v>2302</v>
+        <v>3250</v>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
@@ -1703,7 +1703,7 @@
         <v>-1002880181368</v>
       </c>
       <c r="B106" t="n">
-        <v>26282</v>
+        <v>61392</v>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
@@ -1739,7 +1739,7 @@
         <v>-1002634221315</v>
       </c>
       <c r="B109" t="n">
-        <v>22510</v>
+        <v>23889</v>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
@@ -1751,7 +1751,7 @@
         <v>-1002744838888</v>
       </c>
       <c r="B110" t="n">
-        <v>4987</v>
+        <v>5102</v>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
@@ -1763,7 +1763,7 @@
         <v>-1002809610954</v>
       </c>
       <c r="B111" t="n">
-        <v>5823</v>
+        <v>6734</v>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
@@ -1787,11 +1787,9 @@
         <v>-1002321829358</v>
       </c>
       <c r="B113" t="n">
-        <v>278115</v>
-      </c>
-      <c r="C113" t="n">
-        <v>1</v>
-      </c>
+        <v>287525</v>
+      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
         <v>112</v>
       </c>
@@ -1801,7 +1799,7 @@
         <v>-1002862636130</v>
       </c>
       <c r="B114" t="n">
-        <v>544</v>
+        <v>730</v>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
@@ -1813,7 +1811,7 @@
         <v>-1002887675015</v>
       </c>
       <c r="B115" t="n">
-        <v>2637</v>
+        <v>4302</v>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
@@ -1825,7 +1823,7 @@
         <v>-1002551612447</v>
       </c>
       <c r="B116" t="n">
-        <v>12483</v>
+        <v>16363</v>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
@@ -1849,7 +1847,7 @@
         <v>-1003030011311</v>
       </c>
       <c r="B118" t="n">
-        <v>75</v>
+        <v>598</v>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
@@ -1861,7 +1859,7 @@
         <v>-1002895178300</v>
       </c>
       <c r="B119" t="n">
-        <v>806</v>
+        <v>1121</v>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
@@ -1873,7 +1871,7 @@
         <v>-1002263664644</v>
       </c>
       <c r="B120" t="n">
-        <v>896481</v>
+        <v>1040973</v>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="n">
@@ -1897,7 +1895,7 @@
         <v>-1002226982992</v>
       </c>
       <c r="B122" t="n">
-        <v>9282</v>
+        <v>13160</v>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
@@ -1909,7 +1907,7 @@
         <v>-1002192798016</v>
       </c>
       <c r="B123" t="n">
-        <v>25906</v>
+        <v>27811</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -1935,7 +1933,7 @@
         <v>-1002144563093</v>
       </c>
       <c r="B125" t="n">
-        <v>125086</v>
+        <v>158984</v>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
@@ -1957,7 +1955,7 @@
         <v>-1002870935153</v>
       </c>
       <c r="B127" t="n">
-        <v>135379</v>
+        <v>175443</v>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
@@ -1969,7 +1967,7 @@
         <v>-1002710336139</v>
       </c>
       <c r="B128" t="n">
-        <v>2453</v>
+        <v>2569</v>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
@@ -1981,7 +1979,7 @@
         <v>-1002531024619</v>
       </c>
       <c r="B129" t="n">
-        <v>3897</v>
+        <v>9027</v>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
@@ -1993,7 +1991,7 @@
         <v>-1002288803058</v>
       </c>
       <c r="B130" t="n">
-        <v>195624</v>
+        <v>205520</v>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
@@ -2017,7 +2015,7 @@
         <v>-1002999867992</v>
       </c>
       <c r="B132" t="n">
-        <v>538</v>
+        <v>728</v>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
@@ -2029,7 +2027,7 @@
         <v>-1002822883977</v>
       </c>
       <c r="B133" t="n">
-        <v>19662</v>
+        <v>21568</v>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
@@ -2065,7 +2063,7 @@
         <v>-1001921955585</v>
       </c>
       <c r="B136" t="n">
-        <v>620123</v>
+        <v>735786</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
@@ -2079,7 +2077,7 @@
         <v>-1001546837418</v>
       </c>
       <c r="B137" t="n">
-        <v>165349</v>
+        <v>177249</v>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
@@ -2103,7 +2101,7 @@
         <v>-1001635430845</v>
       </c>
       <c r="B139" t="n">
-        <v>3132</v>
+        <v>3266</v>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
@@ -2115,7 +2113,7 @@
         <v>-1002234774760</v>
       </c>
       <c r="B140" t="n">
-        <v>8121</v>
+        <v>8537</v>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
@@ -2165,7 +2163,7 @@
         <v>-1002512266739</v>
       </c>
       <c r="B144" t="n">
-        <v>3616</v>
+        <v>3760</v>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
@@ -2201,7 +2199,7 @@
         <v>-1002428009204</v>
       </c>
       <c r="B147" t="n">
-        <v>189789</v>
+        <v>397581</v>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="n">
@@ -2213,7 +2211,7 @@
         <v>-1002834499433</v>
       </c>
       <c r="B148" t="n">
-        <v>3277</v>
+        <v>3392</v>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="n">
@@ -2225,7 +2223,7 @@
         <v>-1002320967880</v>
       </c>
       <c r="B149" t="n">
-        <v>31795</v>
+        <v>31920</v>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="n">
@@ -2237,7 +2235,7 @@
         <v>-4974060502</v>
       </c>
       <c r="B150" t="n">
-        <v>51353</v>
+        <v>70074</v>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="n">
@@ -2249,7 +2247,7 @@
         <v>-1002582926621</v>
       </c>
       <c r="B151" t="n">
-        <v>7024</v>
+        <v>11286</v>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
@@ -2261,7 +2259,7 @@
         <v>-1002778085921</v>
       </c>
       <c r="B152" t="n">
-        <v>87</v>
+        <v>199</v>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="n">
@@ -2273,7 +2271,7 @@
         <v>-1002815867232</v>
       </c>
       <c r="B153" t="n">
-        <v>10238</v>
+        <v>37435</v>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
@@ -2285,7 +2283,7 @@
         <v>-1002889562281</v>
       </c>
       <c r="B154" t="n">
-        <v>1963</v>
+        <v>2322</v>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
@@ -2297,7 +2295,7 @@
         <v>-1001406184711</v>
       </c>
       <c r="B155" t="n">
-        <v>477605</v>
+        <v>481897</v>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
@@ -2309,7 +2307,7 @@
         <v>-1002392635902</v>
       </c>
       <c r="B156" t="n">
-        <v>256382</v>
+        <v>303579</v>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="n">
@@ -2333,7 +2331,7 @@
         <v>-1003054525087</v>
       </c>
       <c r="B158" t="n">
-        <v>2352</v>
+        <v>2780</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
@@ -2347,7 +2345,7 @@
         <v>-1002879625349</v>
       </c>
       <c r="B159" t="n">
-        <v>443</v>
+        <v>557</v>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="n">
@@ -2383,7 +2381,7 @@
         <v>-1002359134904</v>
       </c>
       <c r="B162" t="n">
-        <v>17461</v>
+        <v>21339</v>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="n">
@@ -2395,7 +2393,7 @@
         <v>-1003007832445</v>
       </c>
       <c r="B163" t="n">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="n">
@@ -2407,7 +2405,7 @@
         <v>-1002908266830</v>
       </c>
       <c r="B164" t="n">
-        <v>8278</v>
+        <v>20672</v>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="n">
@@ -2419,7 +2417,7 @@
         <v>-1002588140799</v>
       </c>
       <c r="B165" t="n">
-        <v>55999</v>
+        <v>86620</v>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="n">
@@ -2431,7 +2429,7 @@
         <v>-1002152254687</v>
       </c>
       <c r="B166" t="n">
-        <v>284</v>
+        <v>406</v>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="n">
@@ -2443,7 +2441,7 @@
         <v>-1002769760671</v>
       </c>
       <c r="B167" t="n">
-        <v>6122</v>
+        <v>10919</v>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="n">
@@ -2455,7 +2453,7 @@
         <v>-1002529665437</v>
       </c>
       <c r="B168" t="n">
-        <v>384</v>
+        <v>488</v>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="n">
@@ -2479,7 +2477,7 @@
         <v>-1002680979996</v>
       </c>
       <c r="B170" t="n">
-        <v>71933</v>
+        <v>88875</v>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="n">
@@ -2491,7 +2489,7 @@
         <v>-1001801324223</v>
       </c>
       <c r="B171" t="n">
-        <v>93315</v>
+        <v>99528</v>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
@@ -2503,7 +2501,7 @@
         <v>-1002438767403</v>
       </c>
       <c r="B172" t="n">
-        <v>1068</v>
+        <v>1262</v>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="n">
@@ -2515,7 +2513,7 @@
         <v>-1002729517184</v>
       </c>
       <c r="B173" t="n">
-        <v>803</v>
+        <v>1593</v>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="n">
@@ -2527,7 +2525,7 @@
         <v>-1001765476229</v>
       </c>
       <c r="B174" t="n">
-        <v>154167</v>
+        <v>161779</v>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="n">
@@ -2553,7 +2551,7 @@
         <v>-4925721655</v>
       </c>
       <c r="B176" t="n">
-        <v>51356</v>
+        <v>70065</v>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="n">
@@ -2565,7 +2563,7 @@
         <v>-1002773230946</v>
       </c>
       <c r="B177" t="n">
-        <v>8659</v>
+        <v>12886</v>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="n">
@@ -2577,7 +2575,7 @@
         <v>-1001261718716</v>
       </c>
       <c r="B178" t="n">
-        <v>1662829</v>
+        <v>1705251</v>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="n">
@@ -2589,7 +2587,7 @@
         <v>-1002809543928</v>
       </c>
       <c r="B179" t="n">
-        <v>1195</v>
+        <v>1748</v>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="n">
@@ -2601,7 +2599,7 @@
         <v>-1002916180495</v>
       </c>
       <c r="B180" t="n">
-        <v>830</v>
+        <v>2390</v>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="n">
@@ -2613,7 +2611,7 @@
         <v>-4859108486</v>
       </c>
       <c r="B181" t="n">
-        <v>51360</v>
+        <v>70069</v>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="n">
@@ -2669,7 +2667,7 @@
         <v>-1001744426195</v>
       </c>
       <c r="B186" t="n">
-        <v>909347</v>
+        <v>925630</v>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="n">
@@ -2681,7 +2679,7 @@
         <v>-1002260533641</v>
       </c>
       <c r="B187" t="n">
-        <v>308</v>
+        <v>426</v>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
@@ -2705,7 +2703,7 @@
         <v>-1002549453056</v>
       </c>
       <c r="B189" t="n">
-        <v>5348</v>
+        <v>5573</v>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="n">
@@ -2729,7 +2727,7 @@
         <v>-1002465441179</v>
       </c>
       <c r="B191" t="n">
-        <v>458620</v>
+        <v>463754</v>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="n">
@@ -2741,7 +2739,7 @@
         <v>-1002338100665</v>
       </c>
       <c r="B192" t="n">
-        <v>135911</v>
+        <v>162572</v>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="n">
@@ -2763,7 +2761,7 @@
         <v>-1001807175468</v>
       </c>
       <c r="B194" t="n">
-        <v>1483755</v>
+        <v>1493067</v>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="n">
@@ -2775,7 +2773,7 @@
         <v>-1002288363987</v>
       </c>
       <c r="B195" t="n">
-        <v>282164</v>
+        <v>408280</v>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="n">
@@ -2787,7 +2785,7 @@
         <v>-4877376604</v>
       </c>
       <c r="B196" t="n">
-        <v>51365</v>
+        <v>70075</v>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="n">
@@ -2799,7 +2797,7 @@
         <v>-1002872770022</v>
       </c>
       <c r="B197" t="n">
-        <v>118404</v>
+        <v>247896</v>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
@@ -2811,7 +2809,7 @@
         <v>-4961873359</v>
       </c>
       <c r="B198" t="n">
-        <v>51362</v>
+        <v>70072</v>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="n">
@@ -2823,7 +2821,7 @@
         <v>-1002722253045</v>
       </c>
       <c r="B199" t="n">
-        <v>102</v>
+        <v>216</v>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="n">
@@ -2847,7 +2845,7 @@
         <v>-1002324412075</v>
       </c>
       <c r="B201" t="n">
-        <v>12894</v>
+        <v>13027</v>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="n">
@@ -2859,7 +2857,7 @@
         <v>-1002753235468</v>
       </c>
       <c r="B202" t="n">
-        <v>1337</v>
+        <v>2683</v>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="n">
@@ -2891,7 +2889,7 @@
         <v>-1002096741759</v>
       </c>
       <c r="B205" t="n">
-        <v>121105</v>
+        <v>124782</v>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="n">
@@ -2903,7 +2901,7 @@
         <v>-1002367453033</v>
       </c>
       <c r="B206" t="n">
-        <v>274792</v>
+        <v>434893</v>
       </c>
       <c r="C206" t="n">
         <v>1</v>
@@ -2917,7 +2915,7 @@
         <v>-1002806388271</v>
       </c>
       <c r="B207" t="n">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="n">
@@ -2941,7 +2939,7 @@
         <v>-1002388609283</v>
       </c>
       <c r="B209" t="n">
-        <v>265540</v>
+        <v>277339</v>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="n">
@@ -2953,7 +2951,7 @@
         <v>-1002155445752</v>
       </c>
       <c r="B210" t="n">
-        <v>1075</v>
+        <v>1208</v>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="n">
@@ -2965,7 +2963,7 @@
         <v>-1003066477129</v>
       </c>
       <c r="B211" t="n">
-        <v>9734</v>
+        <v>31015</v>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="n">
@@ -2977,7 +2975,7 @@
         <v>-1002587384955</v>
       </c>
       <c r="B212" t="n">
-        <v>19123</v>
+        <v>19494</v>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="n">
@@ -2989,7 +2987,7 @@
         <v>-1002661244330</v>
       </c>
       <c r="B213" t="n">
-        <v>1259</v>
+        <v>2725</v>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
@@ -3011,7 +3009,7 @@
         <v>-1002393739109</v>
       </c>
       <c r="B215" t="n">
-        <v>497829</v>
+        <v>653128</v>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="n">
@@ -3023,7 +3021,7 @@
         <v>-1002368728861</v>
       </c>
       <c r="B216" t="n">
-        <v>3786</v>
+        <v>3943</v>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="n">
@@ -3035,7 +3033,7 @@
         <v>-1001817635995</v>
       </c>
       <c r="B217" t="n">
-        <v>2662486</v>
+        <v>2744666</v>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="n">
@@ -3057,7 +3055,7 @@
         <v>-1002927005745</v>
       </c>
       <c r="B219" t="n">
-        <v>375</v>
+        <v>489</v>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="n">
@@ -3069,7 +3067,7 @@
         <v>-1002799861129</v>
       </c>
       <c r="B220" t="n">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="n">
@@ -3081,7 +3079,7 @@
         <v>-1002522147223</v>
       </c>
       <c r="B221" t="n">
-        <v>315</v>
+        <v>428</v>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="n">
@@ -3093,7 +3091,7 @@
         <v>-1002659291107</v>
       </c>
       <c r="B222" t="n">
-        <v>19682</v>
+        <v>22714</v>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="n">
@@ -3105,7 +3103,7 @@
         <v>-1002334852527</v>
       </c>
       <c r="B223" t="n">
-        <v>2074</v>
+        <v>2278</v>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="n">
@@ -3117,7 +3115,7 @@
         <v>-1002423915712</v>
       </c>
       <c r="B224" t="n">
-        <v>86357</v>
+        <v>103841</v>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="n">
@@ -3129,7 +3127,7 @@
         <v>-1002825020185</v>
       </c>
       <c r="B225" t="n">
-        <v>283</v>
+        <v>406</v>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="n">
@@ -3153,7 +3151,7 @@
         <v>-1002217503260</v>
       </c>
       <c r="B227" t="n">
-        <v>142139</v>
+        <v>157214</v>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="n">
@@ -3165,7 +3163,7 @@
         <v>-1002850122868</v>
       </c>
       <c r="B228" t="n">
-        <v>69530</v>
+        <v>121961</v>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="n">
@@ -3177,7 +3175,7 @@
         <v>-1002761685886</v>
       </c>
       <c r="B229" t="n">
-        <v>2918</v>
+        <v>6927</v>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="n">
@@ -3189,7 +3187,7 @@
         <v>-1002860460728</v>
       </c>
       <c r="B230" t="n">
-        <v>17044</v>
+        <v>46662</v>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="n">
@@ -3239,7 +3237,7 @@
         <v>-1002414175598</v>
       </c>
       <c r="B234" t="n">
-        <v>32587</v>
+        <v>32969</v>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="n">
@@ -3251,7 +3249,7 @@
         <v>-1002848062475</v>
       </c>
       <c r="B235" t="n">
-        <v>6696</v>
+        <v>10630</v>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="n">
@@ -3263,7 +3261,7 @@
         <v>-1003038352740</v>
       </c>
       <c r="B236" t="n">
-        <v>2090</v>
+        <v>8390</v>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="n">
@@ -3275,7 +3273,7 @@
         <v>-1002368488534</v>
       </c>
       <c r="B237" t="n">
-        <v>185638</v>
+        <v>195118</v>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="n">
@@ -3287,7 +3285,7 @@
         <v>-1002516135792</v>
       </c>
       <c r="B238" t="n">
-        <v>904</v>
+        <v>1018</v>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="n">
@@ -3299,7 +3297,7 @@
         <v>-1002651560084</v>
       </c>
       <c r="B239" t="n">
-        <v>10057</v>
+        <v>14645</v>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="n">
@@ -3311,7 +3309,7 @@
         <v>-1002518094653</v>
       </c>
       <c r="B240" t="n">
-        <v>5749</v>
+        <v>11233</v>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="n">
@@ -3323,7 +3321,7 @@
         <v>-1002760392715</v>
       </c>
       <c r="B241" t="n">
-        <v>67065</v>
+        <v>73176</v>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="n">
@@ -3335,7 +3333,7 @@
         <v>-1002579055686</v>
       </c>
       <c r="B242" t="n">
-        <v>25149</v>
+        <v>79500</v>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
@@ -3359,7 +3357,7 @@
         <v>-1002647444996</v>
       </c>
       <c r="B244" t="n">
-        <v>13806</v>
+        <v>19145</v>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="n">
@@ -3371,7 +3369,7 @@
         <v>-1002863926597</v>
       </c>
       <c r="B245" t="n">
-        <v>4101</v>
+        <v>8078</v>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="n">
@@ -3393,7 +3391,7 @@
         <v>-1002562282389</v>
       </c>
       <c r="B247" t="n">
-        <v>2123</v>
+        <v>4217</v>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="n">
@@ -3405,7 +3403,7 @@
         <v>-1002416638992</v>
       </c>
       <c r="B248" t="n">
-        <v>188469</v>
+        <v>200649</v>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="n">
@@ -3417,7 +3415,7 @@
         <v>-1002403581849</v>
       </c>
       <c r="B249" t="n">
-        <v>8883</v>
+        <v>9083</v>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="n">
@@ -3441,7 +3439,7 @@
         <v>-1001460104025</v>
       </c>
       <c r="B251" t="n">
-        <v>46082</v>
+        <v>46371</v>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="n">
@@ -3453,7 +3451,7 @@
         <v>-1002889377215</v>
       </c>
       <c r="B252" t="n">
-        <v>12157</v>
+        <v>18295</v>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="n">
@@ -3477,7 +3475,7 @@
         <v>-1002898563298</v>
       </c>
       <c r="B254" t="n">
-        <v>5287</v>
+        <v>10619</v>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="n">
@@ -3489,7 +3487,7 @@
         <v>-1002031457701</v>
       </c>
       <c r="B255" t="n">
-        <v>399920</v>
+        <v>462734</v>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="n">
@@ -3501,7 +3499,7 @@
         <v>-1002733851343</v>
       </c>
       <c r="B256" t="n">
-        <v>16886</v>
+        <v>20520</v>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="n">
@@ -3513,7 +3511,7 @@
         <v>-4921455900</v>
       </c>
       <c r="B257" t="n">
-        <v>51358</v>
+        <v>70067</v>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="n">
@@ -3525,7 +3523,7 @@
         <v>-1001611710912</v>
       </c>
       <c r="B258" t="n">
-        <v>1011674</v>
+        <v>1018139</v>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="n">
@@ -3537,7 +3535,7 @@
         <v>-1002977896648</v>
       </c>
       <c r="B259" t="n">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="n">
@@ -3561,7 +3559,7 @@
         <v>-1002782716052</v>
       </c>
       <c r="B261" t="n">
-        <v>14289</v>
+        <v>19144</v>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="n">
@@ -3585,7 +3583,7 @@
         <v>-1002582659607</v>
       </c>
       <c r="B263" t="n">
-        <v>859</v>
+        <v>984</v>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="n">
@@ -3609,7 +3607,7 @@
         <v>-1002169700144</v>
       </c>
       <c r="B265" t="n">
-        <v>39160</v>
+        <v>43525</v>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="n">
@@ -3621,7 +3619,7 @@
         <v>-1001652492827</v>
       </c>
       <c r="B266" t="n">
-        <v>3095</v>
+        <v>3263</v>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="n">
@@ -3633,7 +3631,7 @@
         <v>-1002560099813</v>
       </c>
       <c r="B267" t="n">
-        <v>16494</v>
+        <v>17755</v>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="n">
@@ -3667,7 +3665,7 @@
         <v>-1003045110726</v>
       </c>
       <c r="B270" t="n">
-        <v>1592</v>
+        <v>3264</v>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="n">
@@ -3679,7 +3677,7 @@
         <v>-1002168855114</v>
       </c>
       <c r="B271" t="n">
-        <v>203444</v>
+        <v>234965</v>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="n">
@@ -3703,7 +3701,7 @@
         <v>-1002420273008</v>
       </c>
       <c r="B273" t="n">
-        <v>94145</v>
+        <v>99239</v>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="n">
@@ -3761,7 +3759,7 @@
         <v>-1002860463322</v>
       </c>
       <c r="B278" t="n">
-        <v>138</v>
+        <v>260</v>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="n">
@@ -3773,7 +3771,7 @@
         <v>-1002300501716</v>
       </c>
       <c r="B279" t="n">
-        <v>12314</v>
+        <v>18341</v>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="n">
@@ -3785,7 +3783,7 @@
         <v>-1002621836135</v>
       </c>
       <c r="B280" t="n">
-        <v>4859</v>
+        <v>8746</v>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="n">
@@ -3797,7 +3795,7 @@
         <v>-1002632678475</v>
       </c>
       <c r="B281" t="n">
-        <v>805</v>
+        <v>974</v>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="n">
@@ -3809,7 +3807,7 @@
         <v>-1002658418497</v>
       </c>
       <c r="B282" t="n">
-        <v>5637</v>
+        <v>6075</v>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="n">
@@ -3833,7 +3831,7 @@
         <v>-1003011064222</v>
       </c>
       <c r="B284" t="n">
-        <v>348</v>
+        <v>462</v>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="n">
@@ -3845,7 +3843,7 @@
         <v>-1001671470841</v>
       </c>
       <c r="B285" t="n">
-        <v>155658</v>
+        <v>156916</v>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="n">
@@ -3869,7 +3867,7 @@
         <v>-1002391001829</v>
       </c>
       <c r="B287" t="n">
-        <v>384</v>
+        <v>501</v>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="n">
@@ -3881,7 +3879,7 @@
         <v>-1002614518240</v>
       </c>
       <c r="B288" t="n">
-        <v>56297</v>
+        <v>111560</v>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="n">
@@ -3905,7 +3903,7 @@
         <v>-1002713471991</v>
       </c>
       <c r="B290" t="n">
-        <v>51257</v>
+        <v>66565</v>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="n">
@@ -3927,7 +3925,7 @@
         <v>-1001950007498</v>
       </c>
       <c r="B292" t="n">
-        <v>545129</v>
+        <v>603631</v>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="n">
@@ -3939,7 +3937,7 @@
         <v>-1002778350864</v>
       </c>
       <c r="B293" t="n">
-        <v>4080</v>
+        <v>4488</v>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="n">
@@ -3951,7 +3949,7 @@
         <v>-1002670277933</v>
       </c>
       <c r="B294" t="n">
-        <v>19503</v>
+        <v>36180</v>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="n">
@@ -3963,7 +3961,7 @@
         <v>-1002776521317</v>
       </c>
       <c r="B295" t="n">
-        <v>4153</v>
+        <v>4822</v>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="n">
@@ -3975,7 +3973,7 @@
         <v>-1002593143797</v>
       </c>
       <c r="B296" t="n">
-        <v>2809</v>
+        <v>3656</v>
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="n">
@@ -3987,7 +3985,7 @@
         <v>-1002289430922</v>
       </c>
       <c r="B297" t="n">
-        <v>44795</v>
+        <v>57773</v>
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="n">
@@ -3999,7 +3997,7 @@
         <v>-1002761501601</v>
       </c>
       <c r="B298" t="n">
-        <v>3625</v>
+        <v>6367</v>
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="n">
@@ -4011,7 +4009,7 @@
         <v>-1002566090891</v>
       </c>
       <c r="B299" t="n">
-        <v>1699</v>
+        <v>5931</v>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="n">
@@ -4023,7 +4021,7 @@
         <v>-1001302667285</v>
       </c>
       <c r="B300" t="n">
-        <v>3743943</v>
+        <v>3793601</v>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="n">
@@ -4035,7 +4033,7 @@
         <v>-1002621241174</v>
       </c>
       <c r="B301" t="n">
-        <v>3092</v>
+        <v>7379</v>
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="n">
@@ -4069,11 +4067,9 @@
         <v>-1002579287925</v>
       </c>
       <c r="B304" t="n">
-        <v>447</v>
-      </c>
-      <c r="C304" t="n">
-        <v>1</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="C304" t="inlineStr"/>
       <c r="D304" t="n">
         <v>303</v>
       </c>
@@ -4083,7 +4079,7 @@
         <v>-1002040217076</v>
       </c>
       <c r="B305" t="n">
-        <v>98290</v>
+        <v>103149</v>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="n">
@@ -4095,7 +4091,7 @@
         <v>-1002486834455</v>
       </c>
       <c r="B306" t="n">
-        <v>5305</v>
+        <v>9642</v>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="n">
@@ -4107,7 +4103,7 @@
         <v>-1001977703658</v>
       </c>
       <c r="B307" t="n">
-        <v>72719</v>
+        <v>80345</v>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="n">
@@ -4119,7 +4115,7 @@
         <v>-1002702700644</v>
       </c>
       <c r="B308" t="n">
-        <v>276</v>
+        <v>467</v>
       </c>
       <c r="C308" t="n">
         <v>1</v>
@@ -4133,7 +4129,7 @@
         <v>-1002702518774</v>
       </c>
       <c r="B309" t="n">
-        <v>171</v>
+        <v>285</v>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="n">
@@ -4145,7 +4141,7 @@
         <v>-1002998185557</v>
       </c>
       <c r="B310" t="n">
-        <v>71</v>
+        <v>186</v>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="n">
@@ -4157,7 +4153,7 @@
         <v>-1002342685523</v>
       </c>
       <c r="B311" t="n">
-        <v>50160</v>
+        <v>62457</v>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="n">
@@ -4169,7 +4165,7 @@
         <v>-1002738115577</v>
       </c>
       <c r="B312" t="n">
-        <v>3849</v>
+        <v>11340</v>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="n">
@@ -4181,7 +4177,7 @@
         <v>-1002684891199</v>
       </c>
       <c r="B313" t="n">
-        <v>26000</v>
+        <v>30943</v>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="n">
@@ -4193,7 +4189,7 @@
         <v>-1002870267087</v>
       </c>
       <c r="B314" t="n">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="n">
@@ -4215,7 +4211,7 @@
         <v>-1002540598427</v>
       </c>
       <c r="B316" t="n">
-        <v>2622</v>
+        <v>4637</v>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="n">
@@ -4227,7 +4223,7 @@
         <v>-1001985964144</v>
       </c>
       <c r="B317" t="n">
-        <v>462013</v>
+        <v>489695</v>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="n">
@@ -4239,7 +4235,7 @@
         <v>-1003016951295</v>
       </c>
       <c r="B318" t="n">
-        <v>13016</v>
+        <v>39547</v>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="n">
@@ -4251,7 +4247,7 @@
         <v>-1002250428372</v>
       </c>
       <c r="B319" t="n">
-        <v>2887</v>
+        <v>6784</v>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="n">
@@ -4263,7 +4259,7 @@
         <v>-1002999961089</v>
       </c>
       <c r="B320" t="n">
-        <v>684</v>
+        <v>4724</v>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="n">
@@ -4275,7 +4271,7 @@
         <v>-1002727925450</v>
       </c>
       <c r="B321" t="n">
-        <v>718</v>
+        <v>1193</v>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="n">
@@ -4287,7 +4283,7 @@
         <v>-1001298208876</v>
       </c>
       <c r="B322" t="n">
-        <v>1478930</v>
+        <v>1501761</v>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="n">
@@ -4321,7 +4317,7 @@
         <v>-1002895659136</v>
       </c>
       <c r="B325" t="n">
-        <v>515</v>
+        <v>1260</v>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="n">
@@ -4333,7 +4329,7 @@
         <v>-1002534699760</v>
       </c>
       <c r="B326" t="n">
-        <v>14655</v>
+        <v>19395</v>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="n">
@@ -4345,7 +4341,7 @@
         <v>-1002359766306</v>
       </c>
       <c r="B327" t="n">
-        <v>10148</v>
+        <v>13438</v>
       </c>
       <c r="C327" t="n">
         <v>1</v>
@@ -4371,7 +4367,7 @@
         <v>-1002300324334</v>
       </c>
       <c r="B329" t="n">
-        <v>112628</v>
+        <v>165930</v>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="n">
@@ -4383,7 +4379,7 @@
         <v>-1002575818224</v>
       </c>
       <c r="B330" t="n">
-        <v>1292</v>
+        <v>1406</v>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="n">
@@ -4395,7 +4391,7 @@
         <v>-1002175510705</v>
       </c>
       <c r="B331" t="n">
-        <v>9980</v>
+        <v>13931</v>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="n">
@@ -4407,7 +4403,7 @@
         <v>-1002092627141</v>
       </c>
       <c r="B332" t="n">
-        <v>37245</v>
+        <v>41749</v>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="n">
@@ -4419,7 +4415,7 @@
         <v>-1002585116909</v>
       </c>
       <c r="B333" t="n">
-        <v>2095</v>
+        <v>2279</v>
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="n">
@@ -4431,7 +4427,7 @@
         <v>-1002209520317</v>
       </c>
       <c r="B334" t="n">
-        <v>192252</v>
+        <v>235370</v>
       </c>
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="n">
@@ -4443,7 +4439,7 @@
         <v>-1002760607433</v>
       </c>
       <c r="B335" t="n">
-        <v>3450</v>
+        <v>3562</v>
       </c>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="n">
@@ -4455,7 +4451,7 @@
         <v>-1002523705245</v>
       </c>
       <c r="B336" t="n">
-        <v>33084</v>
+        <v>43098</v>
       </c>
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="n">
@@ -4479,7 +4475,7 @@
         <v>-1002600708556</v>
       </c>
       <c r="B338" t="n">
-        <v>28004</v>
+        <v>32693</v>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="n">
@@ -4501,7 +4497,7 @@
         <v>-1002518146543</v>
       </c>
       <c r="B340" t="n">
-        <v>62515</v>
+        <v>127385</v>
       </c>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="n">
@@ -4525,7 +4521,7 @@
         <v>-1002509726671</v>
       </c>
       <c r="B342" t="n">
-        <v>185</v>
+        <v>310</v>
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="n">
@@ -4537,7 +4533,7 @@
         <v>-1002753083965</v>
       </c>
       <c r="B343" t="n">
-        <v>46217</v>
+        <v>48744</v>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="n">
@@ -4549,7 +4545,7 @@
         <v>-1002077075261</v>
       </c>
       <c r="B344" t="n">
-        <v>39590</v>
+        <v>46902</v>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="n">
@@ -4561,7 +4557,7 @@
         <v>-1002873170822</v>
       </c>
       <c r="B345" t="n">
-        <v>2358</v>
+        <v>6316</v>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="n">
@@ -4573,7 +4569,7 @@
         <v>-1002872579152</v>
       </c>
       <c r="B346" t="n">
-        <v>2981</v>
+        <v>7665</v>
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="n">
@@ -4609,7 +4605,7 @@
         <v>-1002296316011</v>
       </c>
       <c r="B349" t="n">
-        <v>9656</v>
+        <v>12571</v>
       </c>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="n">
@@ -4633,7 +4629,7 @@
         <v>-4162328212</v>
       </c>
       <c r="B351" t="n">
-        <v>51357</v>
+        <v>70071</v>
       </c>
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="n">
@@ -4645,7 +4641,7 @@
         <v>-4884314925</v>
       </c>
       <c r="B352" t="n">
-        <v>51364</v>
+        <v>70070</v>
       </c>
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="n">
@@ -4657,7 +4653,7 @@
         <v>-1002595442276</v>
       </c>
       <c r="B353" t="n">
-        <v>17008</v>
+        <v>21952</v>
       </c>
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="n">
@@ -4669,7 +4665,7 @@
         <v>-1002372506024</v>
       </c>
       <c r="B354" t="n">
-        <v>30180</v>
+        <v>36103</v>
       </c>
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="n">
@@ -4681,7 +4677,7 @@
         <v>-1002395833812</v>
       </c>
       <c r="B355" t="n">
-        <v>3688</v>
+        <v>9320</v>
       </c>
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="n">
@@ -4693,7 +4689,7 @@
         <v>-1002600128976</v>
       </c>
       <c r="B356" t="n">
-        <v>2643</v>
+        <v>6577</v>
       </c>
       <c r="C356" t="inlineStr"/>
       <c r="D356" t="n">
@@ -4731,7 +4727,7 @@
         <v>-1002773657299</v>
       </c>
       <c r="B359" t="n">
-        <v>1292</v>
+        <v>1876</v>
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="n">
@@ -4755,7 +4751,7 @@
         <v>-4819895741</v>
       </c>
       <c r="B361" t="n">
-        <v>51355</v>
+        <v>70068</v>
       </c>
       <c r="C361" t="inlineStr"/>
       <c r="D361" t="n">
@@ -4767,7 +4763,7 @@
         <v>-1002571339758</v>
       </c>
       <c r="B362" t="n">
-        <v>25861</v>
+        <v>36010</v>
       </c>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="n">
@@ -4779,7 +4775,7 @@
         <v>-1002664729996</v>
       </c>
       <c r="B363" t="n">
-        <v>2619</v>
+        <v>7827</v>
       </c>
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="n">
@@ -4803,7 +4799,7 @@
         <v>-1002624308239</v>
       </c>
       <c r="B365" t="n">
-        <v>8722</v>
+        <v>18135</v>
       </c>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="n">
@@ -4827,7 +4823,7 @@
         <v>-1001373559245</v>
       </c>
       <c r="B367" t="n">
-        <v>114540</v>
+        <v>116292</v>
       </c>
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="n">
@@ -4839,7 +4835,7 @@
         <v>-1002826605956</v>
       </c>
       <c r="B368" t="n">
-        <v>497</v>
+        <v>611</v>
       </c>
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="n">
@@ -4851,7 +4847,7 @@
         <v>-1002309114039</v>
       </c>
       <c r="B369" t="n">
-        <v>88619</v>
+        <v>90194</v>
       </c>
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="n">
@@ -4863,7 +4859,7 @@
         <v>-1002618584679</v>
       </c>
       <c r="B370" t="n">
-        <v>2930</v>
+        <v>4602</v>
       </c>
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="n">
@@ -4875,7 +4871,7 @@
         <v>-1001868146441</v>
       </c>
       <c r="B371" t="n">
-        <v>95141</v>
+        <v>245920</v>
       </c>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="n">
@@ -4887,7 +4883,7 @@
         <v>-1002288129210</v>
       </c>
       <c r="B372" t="n">
-        <v>104001</v>
+        <v>137343</v>
       </c>
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="n">
@@ -4899,7 +4895,7 @@
         <v>-1001701084460</v>
       </c>
       <c r="B373" t="n">
-        <v>192860</v>
+        <v>200498</v>
       </c>
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="n">
@@ -4911,7 +4907,7 @@
         <v>-1002418585410</v>
       </c>
       <c r="B374" t="n">
-        <v>5017</v>
+        <v>13451</v>
       </c>
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="n">
@@ -4923,7 +4919,7 @@
         <v>-1002588638126</v>
       </c>
       <c r="B375" t="n">
-        <v>18198</v>
+        <v>25243</v>
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="n">
@@ -4935,7 +4931,7 @@
         <v>-1003048077625</v>
       </c>
       <c r="B376" t="n">
-        <v>308</v>
+        <v>450</v>
       </c>
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="n">
@@ -4947,7 +4943,7 @@
         <v>-1002007016158</v>
       </c>
       <c r="B377" t="n">
-        <v>1137077</v>
+        <v>1198037</v>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="n">
@@ -4959,7 +4955,7 @@
         <v>-1002597892903</v>
       </c>
       <c r="B378" t="n">
-        <v>157708</v>
+        <v>225339</v>
       </c>
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="n">
@@ -4971,7 +4967,7 @@
         <v>-1002853960198</v>
       </c>
       <c r="B379" t="n">
-        <v>2409</v>
+        <v>6285</v>
       </c>
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="n">
@@ -4983,7 +4979,7 @@
         <v>-1002764128440</v>
       </c>
       <c r="B380" t="n">
-        <v>446</v>
+        <v>7206</v>
       </c>
       <c r="C380" t="n">
         <v>1</v>
@@ -4997,7 +4993,7 @@
         <v>-1002457910402</v>
       </c>
       <c r="B381" t="n">
-        <v>5388</v>
+        <v>5681</v>
       </c>
       <c r="C381" t="inlineStr"/>
       <c r="D381" t="n">
@@ -5009,7 +5005,7 @@
         <v>-1002695735836</v>
       </c>
       <c r="B382" t="n">
-        <v>5098</v>
+        <v>5216</v>
       </c>
       <c r="C382" t="inlineStr"/>
       <c r="D382" t="n">
@@ -5021,7 +5017,7 @@
         <v>-1003055781840</v>
       </c>
       <c r="B383" t="n">
-        <v>1366</v>
+        <v>5406</v>
       </c>
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="n">
@@ -5045,7 +5041,7 @@
         <v>-1001124651563</v>
       </c>
       <c r="B385" t="n">
-        <v>84943</v>
+        <v>93183</v>
       </c>
       <c r="C385" t="inlineStr"/>
       <c r="D385" t="n">
@@ -5067,7 +5063,7 @@
         <v>-1002237965843</v>
       </c>
       <c r="B387" t="n">
-        <v>94988</v>
+        <v>192191</v>
       </c>
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="n">
@@ -5091,7 +5087,7 @@
         <v>-1002933730666</v>
       </c>
       <c r="B389" t="n">
-        <v>100</v>
+        <v>2974</v>
       </c>
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="n">
@@ -5103,7 +5099,7 @@
         <v>-1002593501991</v>
       </c>
       <c r="B390" t="n">
-        <v>6176</v>
+        <v>6328</v>
       </c>
       <c r="C390" t="inlineStr"/>
       <c r="D390" t="n">
@@ -5115,7 +5111,7 @@
         <v>-1002265393780</v>
       </c>
       <c r="B391" t="n">
-        <v>34059</v>
+        <v>41592</v>
       </c>
       <c r="C391" t="inlineStr"/>
       <c r="D391" t="n">
@@ -5127,7 +5123,7 @@
         <v>-1003084989152</v>
       </c>
       <c r="B392" t="n">
-        <v>84</v>
+        <v>199</v>
       </c>
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="n">
@@ -5139,11 +5135,49 @@
         <v>-1003055719997</v>
       </c>
       <c r="B393" t="n">
-        <v>1942</v>
+        <v>6678</v>
       </c>
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="n">
         <v>392</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>-1003463864177</v>
+      </c>
+      <c r="B394" t="n">
+        <v>104411</v>
+      </c>
+      <c r="C394" t="n">
+        <v>1</v>
+      </c>
+      <c r="D394" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>-1002812268562</v>
+      </c>
+      <c r="B395" t="n">
+        <v>900</v>
+      </c>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>-1003141918793</v>
+      </c>
+      <c r="B396" t="n">
+        <v>25303</v>
+      </c>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="n">
+        <v>395</v>
       </c>
     </row>
   </sheetData>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D396"/>
+  <dimension ref="A1:D312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,4731 +452,3721 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-1001952004445</v>
+        <v>-1003035504222</v>
       </c>
       <c r="B2" t="n">
-        <v>615334</v>
+        <v>28806</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-1003035504222</v>
+        <v>-1002615496638</v>
       </c>
       <c r="B3" t="n">
-        <v>25744</v>
+        <v>6985</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-1002615496638</v>
+        <v>-1002795475468</v>
       </c>
       <c r="B4" t="n">
-        <v>6566</v>
+        <v>17835</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-1002795475468</v>
+        <v>-1001212305259</v>
       </c>
       <c r="B5" t="n">
-        <v>17791</v>
+        <v>2968649</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-1001212305259</v>
+        <v>-1002864485836</v>
       </c>
       <c r="B6" t="n">
-        <v>2963736</v>
+        <v>120962</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-1002864485836</v>
+        <v>-1002320283926</v>
       </c>
       <c r="B7" t="n">
-        <v>119478</v>
+        <v>23510</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-1002012086654</v>
+        <v>-1002510217399</v>
       </c>
       <c r="B8" t="n">
-        <v>645629</v>
+        <v>13795</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-1002571946861</v>
+        <v>-1002521509637</v>
       </c>
       <c r="B9" t="n">
-        <v>3880</v>
+        <v>91927</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-1002320283926</v>
+        <v>-1002189109599</v>
       </c>
       <c r="B10" t="n">
-        <v>22920</v>
+        <v>924716</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-1002510217399</v>
+        <v>-1002520212825</v>
       </c>
       <c r="B11" t="n">
-        <v>13630</v>
+        <v>438</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-1002521509637</v>
+        <v>-1002747623711</v>
       </c>
       <c r="B12" t="n">
-        <v>91468</v>
+        <v>852</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-1003076627076</v>
+        <v>-1002205410222</v>
       </c>
       <c r="B13" t="n">
-        <v>482</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>119969</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-1002189109599</v>
+        <v>-1002623818368</v>
       </c>
       <c r="B14" t="n">
-        <v>923209</v>
+        <v>99069</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-1002520212825</v>
+        <v>-1002455033621</v>
       </c>
       <c r="B15" t="n">
-        <v>426</v>
+        <v>88132</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-1002747623711</v>
+        <v>-1001596465392</v>
       </c>
       <c r="B16" t="n">
-        <v>798</v>
+        <v>4884596</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-1002205410222</v>
+        <v>-1001946166876</v>
       </c>
       <c r="B17" t="n">
-        <v>117522</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
+        <v>43945</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-1002538551462</v>
+        <v>-1001818008631</v>
       </c>
       <c r="B18" t="n">
-        <v>2809</v>
+        <v>25884</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-1002527463407</v>
+        <v>-1001493770434</v>
       </c>
       <c r="B19" t="n">
-        <v>1480</v>
+        <v>354175</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-1002623818368</v>
+        <v>-1002473130324</v>
       </c>
       <c r="B20" t="n">
-        <v>97339</v>
+        <v>34977</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-1002455033621</v>
+        <v>-1002651996794</v>
       </c>
       <c r="B21" t="n">
-        <v>88120</v>
+        <v>131201</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-1001596465392</v>
+        <v>-1002555387875</v>
       </c>
       <c r="B22" t="n">
-        <v>4880874</v>
+        <v>61087</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-1001946166876</v>
+        <v>-1002422251622</v>
       </c>
       <c r="B23" t="n">
-        <v>43928</v>
+        <v>84894</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-1001818008631</v>
+        <v>-1002454558597</v>
       </c>
       <c r="B24" t="n">
-        <v>25563</v>
+        <v>273588</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-1001493770434</v>
+        <v>-1001467801859</v>
       </c>
       <c r="B25" t="n">
-        <v>354155</v>
+        <v>981954</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-1002473130324</v>
+        <v>-1002322838597</v>
       </c>
       <c r="B26" t="n">
-        <v>34152</v>
+        <v>2733588</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-1002128565721</v>
+        <v>-1002337769587</v>
       </c>
       <c r="B27" t="n">
-        <v>442883</v>
+        <v>2576</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-1002651996794</v>
+        <v>-1002832898246</v>
       </c>
       <c r="B28" t="n">
-        <v>130791</v>
+        <v>8520</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-1002555387875</v>
+        <v>-1003092984130</v>
       </c>
       <c r="B29" t="n">
-        <v>60964</v>
+        <v>829</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-1002657005172</v>
+        <v>-1001390053729</v>
       </c>
       <c r="B30" t="n">
-        <v>43733</v>
+        <v>90303</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-1002422251622</v>
+        <v>-1002556474841</v>
       </c>
       <c r="B31" t="n">
-        <v>84585</v>
+        <v>43828</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-1002962470859</v>
+        <v>-1002531829054</v>
       </c>
       <c r="B32" t="n">
-        <v>229</v>
+        <v>15505</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-1002454558597</v>
+        <v>-1002750504156</v>
       </c>
       <c r="B33" t="n">
-        <v>270773</v>
+        <v>1154</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-1001467801859</v>
+        <v>-1002359874556</v>
       </c>
       <c r="B34" t="n">
-        <v>979087</v>
+        <v>24036</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-1002322838597</v>
+        <v>-1002379714369</v>
       </c>
       <c r="B35" t="n">
-        <v>2658777</v>
+        <v>38897</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-1002164951892</v>
+        <v>-1002985739762</v>
       </c>
       <c r="B36" t="n">
-        <v>3940</v>
+        <v>688</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-1002337769587</v>
-      </c>
-      <c r="B37" t="n">
-        <v>2576</v>
-      </c>
+        <v>-4822189866</v>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-1002832898246</v>
+        <v>-1003001093483</v>
       </c>
       <c r="B38" t="n">
-        <v>8216</v>
+        <v>3606</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-1003092984130</v>
+        <v>-1001543478413</v>
       </c>
       <c r="B39" t="n">
-        <v>532</v>
+        <v>61833</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-1001390053729</v>
+        <v>-1001668927089</v>
       </c>
       <c r="B40" t="n">
-        <v>90248</v>
+        <v>109473</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-1002176239244</v>
+        <v>-1002706892578</v>
       </c>
       <c r="B41" t="n">
-        <v>42185</v>
+        <v>7088</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-1002720382111</v>
+        <v>-1002761573267</v>
       </c>
       <c r="B42" t="n">
-        <v>67930</v>
+        <v>506592</v>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-1002556474841</v>
+        <v>-1002832174643</v>
       </c>
       <c r="B43" t="n">
-        <v>43739</v>
+        <v>204</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-1002531829054</v>
+        <v>-1001929868118</v>
       </c>
       <c r="B44" t="n">
-        <v>15067</v>
+        <v>2425</v>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-1002750504156</v>
+        <v>-1003078207757</v>
       </c>
       <c r="B45" t="n">
-        <v>1142</v>
+        <v>136</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-1002359874556</v>
+        <v>-1003048673651</v>
       </c>
       <c r="B46" t="n">
-        <v>23939</v>
+        <v>7781</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-1002861900346</v>
+        <v>-1001818742779</v>
       </c>
       <c r="B47" t="n">
-        <v>38820</v>
+        <v>247846</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-1002379714369</v>
+        <v>-1002845355669</v>
       </c>
       <c r="B48" t="n">
-        <v>38109</v>
+        <v>4054</v>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-1002985739762</v>
+        <v>-1002509299058</v>
       </c>
       <c r="B49" t="n">
-        <v>642</v>
+        <v>948</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-1002252138406</v>
+        <v>-1002728494984</v>
       </c>
       <c r="B50" t="n">
-        <v>13057</v>
+        <v>2045</v>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-1002165058341</v>
+        <v>-1002793180948</v>
       </c>
       <c r="B51" t="n">
-        <v>53392</v>
+        <v>10561</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-4822189866</v>
-      </c>
-      <c r="B52" t="inlineStr"/>
+        <v>-1002519990156</v>
+      </c>
+      <c r="B52" t="n">
+        <v>13619</v>
+      </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-1003001093483</v>
+        <v>-1002532154366</v>
       </c>
       <c r="B53" t="n">
-        <v>3510</v>
+        <v>1319</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-1001543478413</v>
+        <v>-1002110839951</v>
       </c>
       <c r="B54" t="n">
-        <v>61555</v>
+        <v>340107</v>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-1001668927089</v>
+        <v>-1002679523819</v>
       </c>
       <c r="B55" t="n">
-        <v>109246</v>
+        <v>4177</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-1002706892578</v>
+        <v>-1002619556227</v>
       </c>
       <c r="B56" t="n">
-        <v>6705</v>
+        <v>17019</v>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-1002761573267</v>
+        <v>-1001859766402</v>
       </c>
       <c r="B57" t="n">
-        <v>474933</v>
+        <v>28841</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-1002832174643</v>
+        <v>-1002815530049</v>
       </c>
       <c r="B58" t="n">
-        <v>192</v>
+        <v>31705</v>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-1001929868118</v>
+        <v>-1002683965508</v>
       </c>
       <c r="B59" t="n">
-        <v>2411</v>
+        <v>9410</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-1002587983907</v>
+        <v>-1002016912929</v>
       </c>
       <c r="B60" t="n">
-        <v>1939</v>
+        <v>303842</v>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-1003078207757</v>
+        <v>-1002591852942</v>
       </c>
       <c r="B61" t="n">
-        <v>124</v>
+        <v>60324</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-1002742559694</v>
+        <v>-1002130498457</v>
       </c>
       <c r="B62" t="n">
-        <v>23014</v>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
+        <v>180330</v>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-1003048673651</v>
+        <v>-1002274964696</v>
       </c>
       <c r="B63" t="n">
-        <v>7398</v>
+        <v>2864</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-1002168686437</v>
+        <v>-1001741252369</v>
       </c>
       <c r="B64" t="n">
-        <v>58895</v>
+        <v>46096</v>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-1001818742779</v>
+        <v>-1002616170042</v>
       </c>
       <c r="B65" t="n">
-        <v>244846</v>
+        <v>6555</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-1002845355669</v>
+        <v>-1002437713625</v>
       </c>
       <c r="B66" t="n">
-        <v>4040</v>
+        <v>36501</v>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-1002509299058</v>
-      </c>
-      <c r="B67" t="n">
-        <v>936</v>
-      </c>
+        <v>-1001819768369</v>
+      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-1002728494984</v>
+        <v>-1002046646497</v>
       </c>
       <c r="B68" t="n">
-        <v>1992</v>
+        <v>22279</v>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-1002793180948</v>
+        <v>-1002114430690</v>
       </c>
       <c r="B69" t="n">
-        <v>10153</v>
+        <v>71286</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-1002519990156</v>
+        <v>-1002532871843</v>
       </c>
       <c r="B70" t="n">
-        <v>13047</v>
+        <v>10708</v>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-1002532154366</v>
+        <v>-1002268045818</v>
       </c>
       <c r="B71" t="n">
-        <v>1268</v>
+        <v>181681</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-1002110839951</v>
+        <v>-1002101571866</v>
       </c>
       <c r="B72" t="n">
-        <v>338296</v>
+        <v>30789</v>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-1002679523819</v>
+        <v>-1002779291814</v>
       </c>
       <c r="B73" t="n">
-        <v>4071</v>
+        <v>12043</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-1002619556227</v>
+        <v>-1001473268532</v>
       </c>
       <c r="B74" t="n">
-        <v>16392</v>
+        <v>748597</v>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-1001859766402</v>
+        <v>-1002190969931</v>
       </c>
       <c r="B75" t="n">
-        <v>28811</v>
+        <v>28268</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-1002815530049</v>
+        <v>-1002071946221</v>
       </c>
       <c r="B76" t="n">
-        <v>31684</v>
+        <v>7568</v>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-1002683965508</v>
+        <v>-1002581029977</v>
       </c>
       <c r="B77" t="n">
-        <v>9393</v>
+        <v>174146</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-1002016912929</v>
+        <v>-1002887971256</v>
       </c>
       <c r="B78" t="n">
-        <v>303210</v>
+        <v>2530</v>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-1002591852942</v>
+        <v>-1002312125060</v>
       </c>
       <c r="B79" t="n">
-        <v>60109</v>
+        <v>53595</v>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
-        <v>78</v>
+        <v>102</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-1002130498457</v>
+        <v>-1001908446355</v>
       </c>
       <c r="B80" t="n">
-        <v>179947</v>
+        <v>991497</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
-        <v>79</v>
+        <v>103</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-1002274964696</v>
+        <v>-1002278762192</v>
       </c>
       <c r="B81" t="n">
-        <v>2682</v>
+        <v>3280</v>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-1003081798051</v>
+        <v>-1002880181368</v>
       </c>
       <c r="B82" t="n">
-        <v>574</v>
+        <v>63452</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="n">
-        <v>81</v>
+        <v>105</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-1001741252369</v>
+        <v>-1002634221315</v>
       </c>
       <c r="B83" t="n">
-        <v>45760</v>
+        <v>25104</v>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
-        <v>82</v>
+        <v>108</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-1002616170042</v>
+        <v>-1002744838888</v>
       </c>
       <c r="B84" t="n">
-        <v>6537</v>
+        <v>5114</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>83</v>
+        <v>109</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-1002437713625</v>
+        <v>-1002809610954</v>
       </c>
       <c r="B85" t="n">
-        <v>36084</v>
+        <v>6757</v>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
-        <v>84</v>
+        <v>110</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-1002311273623</v>
+        <v>-1002321829358</v>
       </c>
       <c r="B86" t="n">
-        <v>45851</v>
+        <v>288450</v>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="n">
-        <v>85</v>
+        <v>112</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-1003045298701</v>
+        <v>-1002862636130</v>
       </c>
       <c r="B87" t="n">
-        <v>10</v>
+        <v>749</v>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-1001819768369</v>
-      </c>
-      <c r="B88" t="inlineStr"/>
+        <v>-1002887675015</v>
+      </c>
+      <c r="B88" t="n">
+        <v>4455</v>
+      </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-1002046646497</v>
+        <v>-1002551612447</v>
       </c>
       <c r="B89" t="n">
-        <v>22133</v>
+        <v>16748</v>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-1002114430690</v>
+        <v>-1003030011311</v>
       </c>
       <c r="B90" t="n">
-        <v>69964</v>
+        <v>634</v>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="n">
-        <v>89</v>
+        <v>117</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-1002532871843</v>
+        <v>-1002895178300</v>
       </c>
       <c r="B91" t="n">
-        <v>10323</v>
+        <v>1236</v>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
-        <v>90</v>
+        <v>118</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-1002378905284</v>
+        <v>-1002263664644</v>
       </c>
       <c r="B92" t="n">
-        <v>144680</v>
+        <v>1059868</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-1002268045818</v>
+        <v>-1002226982992</v>
       </c>
       <c r="B93" t="n">
-        <v>179408</v>
+        <v>13547</v>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="n">
-        <v>92</v>
+        <v>121</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-1002101571866</v>
+        <v>-1002192798016</v>
       </c>
       <c r="B94" t="n">
-        <v>30731</v>
-      </c>
-      <c r="C94" t="inlineStr"/>
+        <v>28076</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
       <c r="D94" t="n">
-        <v>93</v>
+        <v>122</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-1002779291814</v>
+        <v>-1002144563093</v>
       </c>
       <c r="B95" t="n">
-        <v>11746</v>
+        <v>159831</v>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>94</v>
+        <v>124</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-1001473268532</v>
+        <v>-1002870935153</v>
       </c>
       <c r="B96" t="n">
-        <v>748350</v>
+        <v>175913</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-1002190969931</v>
+        <v>-1002710336139</v>
       </c>
       <c r="B97" t="n">
-        <v>27877</v>
+        <v>2581</v>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>96</v>
+        <v>127</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-1002634538610</v>
+        <v>-1002531024619</v>
       </c>
       <c r="B98" t="n">
-        <v>3767</v>
+        <v>9538</v>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-1002071946221</v>
+        <v>-1002288803058</v>
       </c>
       <c r="B99" t="n">
-        <v>7552</v>
+        <v>205992</v>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="n">
-        <v>98</v>
+        <v>129</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-1002581029977</v>
+        <v>-1002822883977</v>
       </c>
       <c r="B100" t="n">
-        <v>169123</v>
+        <v>21742</v>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
-        <v>99</v>
+        <v>132</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-1002887971256</v>
+        <v>-1001921955585</v>
       </c>
       <c r="B101" t="n">
-        <v>2480</v>
-      </c>
-      <c r="C101" t="inlineStr"/>
+        <v>748557</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
       <c r="D101" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>-1002666720446</v>
+        <v>-1001546837418</v>
       </c>
       <c r="B102" t="n">
-        <v>2016</v>
+        <v>177912</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>101</v>
+        <v>136</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>-1002312125060</v>
+        <v>-1001635430845</v>
       </c>
       <c r="B103" t="n">
-        <v>51098</v>
+        <v>3280</v>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>102</v>
+        <v>138</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>-1001908446355</v>
+        <v>-1002234774760</v>
       </c>
       <c r="B104" t="n">
-        <v>989979</v>
+        <v>8612</v>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>103</v>
+        <v>139</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>-1002278762192</v>
+        <v>-4562050705</v>
       </c>
       <c r="B105" t="n">
-        <v>3250</v>
+        <v>51354</v>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>104</v>
+        <v>142</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>-1002880181368</v>
+        <v>-1002512266739</v>
       </c>
       <c r="B106" t="n">
-        <v>61392</v>
+        <v>3772</v>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>105</v>
+        <v>143</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-1002738828001</v>
+        <v>-1002073440916</v>
       </c>
       <c r="B107" t="n">
-        <v>3628</v>
+        <v>940877</v>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>106</v>
+        <v>145</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>-1002608731952</v>
+        <v>-1002428009204</v>
       </c>
       <c r="B108" t="n">
-        <v>74728</v>
+        <v>405523</v>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>107</v>
+        <v>146</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-1002634221315</v>
+        <v>-1002834499433</v>
       </c>
       <c r="B109" t="n">
-        <v>23889</v>
+        <v>3404</v>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>108</v>
+        <v>147</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>-1002744838888</v>
+        <v>-1002320967880</v>
       </c>
       <c r="B110" t="n">
-        <v>5102</v>
+        <v>31932</v>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>109</v>
+        <v>148</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>-1002809610954</v>
+        <v>-4974060502</v>
       </c>
       <c r="B111" t="n">
-        <v>6734</v>
+        <v>72344</v>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>110</v>
+        <v>149</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-1002707242957</v>
+        <v>-1002582926621</v>
       </c>
       <c r="B112" t="n">
-        <v>7874</v>
+        <v>11732</v>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>111</v>
+        <v>150</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>-1002321829358</v>
+        <v>-1002778085921</v>
       </c>
       <c r="B113" t="n">
-        <v>287525</v>
+        <v>211</v>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>112</v>
+        <v>151</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-1002862636130</v>
+        <v>-1002815867232</v>
       </c>
       <c r="B114" t="n">
-        <v>730</v>
+        <v>38394</v>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>113</v>
+        <v>152</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-1002887675015</v>
+        <v>-1001406184711</v>
       </c>
       <c r="B115" t="n">
-        <v>4302</v>
+        <v>482368</v>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>114</v>
+        <v>154</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-1002551612447</v>
+        <v>-1002392635902</v>
       </c>
       <c r="B116" t="n">
-        <v>16363</v>
+        <v>309579</v>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>115</v>
+        <v>155</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-1002407097949</v>
+        <v>-1003054525087</v>
       </c>
       <c r="B117" t="n">
-        <v>7271</v>
-      </c>
-      <c r="C117" t="inlineStr"/>
+        <v>2806</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
       <c r="D117" t="n">
-        <v>116</v>
+        <v>157</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-1003030011311</v>
+        <v>-1002879625349</v>
       </c>
       <c r="B118" t="n">
-        <v>598</v>
+        <v>569</v>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
-        <v>117</v>
+        <v>158</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>-1002895178300</v>
+        <v>-1002359134904</v>
       </c>
       <c r="B119" t="n">
-        <v>1121</v>
+        <v>21724</v>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>118</v>
+        <v>161</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-1002263664644</v>
+        <v>-1003007832445</v>
       </c>
       <c r="B120" t="n">
-        <v>1040973</v>
+        <v>145</v>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="n">
-        <v>119</v>
+        <v>162</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-1002595918603</v>
+        <v>-1002908266830</v>
       </c>
       <c r="B121" t="n">
-        <v>22995</v>
+        <v>21406</v>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="n">
-        <v>120</v>
+        <v>163</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>-1002226982992</v>
+        <v>-1002588140799</v>
       </c>
       <c r="B122" t="n">
-        <v>13160</v>
+        <v>87245</v>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
-        <v>121</v>
+        <v>164</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>-1002192798016</v>
+        <v>-1002152254687</v>
       </c>
       <c r="B123" t="n">
-        <v>27811</v>
-      </c>
-      <c r="C123" t="n">
-        <v>1</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>122</v>
+        <v>165</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>-1002603257148</v>
+        <v>-1002769760671</v>
       </c>
       <c r="B124" t="n">
-        <v>5416</v>
+        <v>11456</v>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>123</v>
+        <v>166</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>-1002144563093</v>
+        <v>-1002529665437</v>
       </c>
       <c r="B125" t="n">
-        <v>158984</v>
+        <v>500</v>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>124</v>
+        <v>167</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>-1002745407375</v>
-      </c>
-      <c r="B126" t="inlineStr"/>
+        <v>-1002680979996</v>
+      </c>
+      <c r="B126" t="n">
+        <v>89627</v>
+      </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>125</v>
+        <v>169</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>-1002870935153</v>
+        <v>-1001801324223</v>
       </c>
       <c r="B127" t="n">
-        <v>175443</v>
+        <v>99983</v>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
-        <v>126</v>
+        <v>170</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>-1002710336139</v>
+        <v>-1002438767403</v>
       </c>
       <c r="B128" t="n">
-        <v>2569</v>
+        <v>1275</v>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>127</v>
+        <v>171</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>-1002531024619</v>
+        <v>-1002729517184</v>
       </c>
       <c r="B129" t="n">
-        <v>9027</v>
+        <v>1642</v>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>128</v>
+        <v>172</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>-1002288803058</v>
+        <v>-1001765476229</v>
       </c>
       <c r="B130" t="n">
-        <v>205520</v>
+        <v>162199</v>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>129</v>
+        <v>173</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>-1002374275732</v>
+        <v>-4925721655</v>
       </c>
       <c r="B131" t="n">
-        <v>42021</v>
+        <v>72343</v>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="n">
-        <v>130</v>
+        <v>175</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>-1002999867992</v>
+        <v>-1002773230946</v>
       </c>
       <c r="B132" t="n">
-        <v>728</v>
+        <v>12886</v>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>131</v>
+        <v>176</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>-1002822883977</v>
+        <v>-1001261718716</v>
       </c>
       <c r="B133" t="n">
-        <v>21568</v>
+        <v>1707822</v>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>132</v>
+        <v>177</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>-1002871230433</v>
+        <v>-1002809543928</v>
       </c>
       <c r="B134" t="n">
-        <v>460</v>
+        <v>1764</v>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="n">
-        <v>133</v>
+        <v>178</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>-1002622377359</v>
+        <v>-1002916180495</v>
       </c>
       <c r="B135" t="n">
-        <v>28809</v>
+        <v>2536</v>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="n">
-        <v>134</v>
+        <v>179</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>-1001921955585</v>
+        <v>-4859108486</v>
       </c>
       <c r="B136" t="n">
-        <v>735786</v>
-      </c>
-      <c r="C136" t="n">
-        <v>1</v>
-      </c>
+        <v>72342</v>
+      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="n">
-        <v>135</v>
+        <v>180</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>-1001546837418</v>
-      </c>
-      <c r="B137" t="n">
-        <v>177249</v>
-      </c>
+        <v>-4863174120</v>
+      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>-1002213421807</v>
-      </c>
-      <c r="B138" t="n">
-        <v>57818</v>
-      </c>
+        <v>-4863520102</v>
+      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="n">
-        <v>137</v>
+        <v>184</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>-1001635430845</v>
+        <v>-1001744426195</v>
       </c>
       <c r="B139" t="n">
-        <v>3266</v>
+        <v>927013</v>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>138</v>
+        <v>185</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>-1002234774760</v>
+        <v>-1002260533641</v>
       </c>
       <c r="B140" t="n">
-        <v>8537</v>
+        <v>438</v>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
-        <v>139</v>
+        <v>186</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>-1002860218020</v>
+        <v>-1002549453056</v>
       </c>
       <c r="B141" t="n">
-        <v>5128</v>
-      </c>
-      <c r="C141" t="n">
-        <v>1</v>
-      </c>
+        <v>5594</v>
+      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>140</v>
+        <v>188</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>-1002625815155</v>
+        <v>-1002465441179</v>
       </c>
       <c r="B142" t="n">
-        <v>16226</v>
+        <v>463982</v>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>141</v>
+        <v>190</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>-4562050705</v>
+        <v>-1002338100665</v>
       </c>
       <c r="B143" t="n">
-        <v>51354</v>
+        <v>164733</v>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="n">
-        <v>142</v>
+        <v>191</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>-1002512266739</v>
-      </c>
-      <c r="B144" t="n">
-        <v>3760</v>
-      </c>
+        <v>-4852298794</v>
+      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>143</v>
+        <v>192</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>-1002555897596</v>
+        <v>-1001807175468</v>
       </c>
       <c r="B145" t="n">
-        <v>36170</v>
+        <v>1493271</v>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="n">
-        <v>144</v>
+        <v>193</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>-1002073440916</v>
+        <v>-1002288363987</v>
       </c>
       <c r="B146" t="n">
-        <v>940877</v>
+        <v>410129</v>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="n">
-        <v>145</v>
+        <v>194</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>-1002428009204</v>
+        <v>-4877376604</v>
       </c>
       <c r="B147" t="n">
-        <v>397581</v>
+        <v>72341</v>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="n">
-        <v>146</v>
+        <v>195</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>-1002834499433</v>
+        <v>-1002872770022</v>
       </c>
       <c r="B148" t="n">
-        <v>3392</v>
+        <v>252671</v>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="n">
-        <v>147</v>
+        <v>196</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>-1002320967880</v>
+        <v>-4961873359</v>
       </c>
       <c r="B149" t="n">
-        <v>31920</v>
+        <v>72346</v>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="n">
-        <v>148</v>
+        <v>197</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>-4974060502</v>
+        <v>-1002722253045</v>
       </c>
       <c r="B150" t="n">
-        <v>70074</v>
+        <v>228</v>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="n">
-        <v>149</v>
+        <v>198</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>-1002582926621</v>
+        <v>-1002324412075</v>
       </c>
       <c r="B151" t="n">
-        <v>11286</v>
+        <v>13039</v>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>-1002778085921</v>
+        <v>-1002753235468</v>
       </c>
       <c r="B152" t="n">
-        <v>199</v>
+        <v>2948</v>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="n">
-        <v>151</v>
+        <v>201</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>-1002815867232</v>
-      </c>
-      <c r="B153" t="n">
-        <v>37435</v>
-      </c>
+        <v>-4952186637</v>
+      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>152</v>
+        <v>202</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>-1002889562281</v>
-      </c>
-      <c r="B154" t="n">
-        <v>2322</v>
-      </c>
+        <v>-1002514951234</v>
+      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>153</v>
+        <v>203</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>-1001406184711</v>
+        <v>-1002096741759</v>
       </c>
       <c r="B155" t="n">
-        <v>481897</v>
+        <v>125009</v>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>154</v>
+        <v>204</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>-1002392635902</v>
+        <v>-1002367453033</v>
       </c>
       <c r="B156" t="n">
-        <v>303579</v>
-      </c>
-      <c r="C156" t="inlineStr"/>
+        <v>479928</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
       <c r="D156" t="n">
-        <v>155</v>
+        <v>205</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>-1002559760761</v>
+        <v>-1002806388271</v>
       </c>
       <c r="B157" t="n">
-        <v>6949</v>
+        <v>190</v>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>-1003054525087</v>
+        <v>-1002388609283</v>
       </c>
       <c r="B158" t="n">
-        <v>2780</v>
-      </c>
-      <c r="C158" t="n">
-        <v>1</v>
-      </c>
+        <v>277887</v>
+      </c>
+      <c r="C158" t="inlineStr"/>
       <c r="D158" t="n">
-        <v>157</v>
+        <v>208</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>-1002879625349</v>
+        <v>-1002155445752</v>
       </c>
       <c r="B159" t="n">
-        <v>557</v>
+        <v>1220</v>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="n">
-        <v>158</v>
+        <v>209</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>-1002582720522</v>
+        <v>-1003066477129</v>
       </c>
       <c r="B160" t="n">
-        <v>2034</v>
+        <v>31209</v>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="n">
-        <v>159</v>
+        <v>210</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>-1002705745556</v>
+        <v>-1002587384955</v>
       </c>
       <c r="B161" t="n">
-        <v>22533</v>
+        <v>19506</v>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="n">
-        <v>160</v>
+        <v>211</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>-1002359134904</v>
+        <v>-1002661244330</v>
       </c>
       <c r="B162" t="n">
-        <v>21339</v>
+        <v>2806</v>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="n">
-        <v>161</v>
+        <v>212</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>-1003007832445</v>
+        <v>-1002567310940</v>
       </c>
       <c r="B163" t="n">
-        <v>133</v>
+        <v>1743</v>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="n">
-        <v>162</v>
+        <v>213</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>-1002908266830</v>
+        <v>-1002393739109</v>
       </c>
       <c r="B164" t="n">
-        <v>20672</v>
+        <v>670829</v>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="n">
-        <v>163</v>
+        <v>214</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>-1002588140799</v>
+        <v>-1002368728861</v>
       </c>
       <c r="B165" t="n">
-        <v>86620</v>
+        <v>3955</v>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="n">
-        <v>164</v>
+        <v>215</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>-1002152254687</v>
+        <v>-1001817635995</v>
       </c>
       <c r="B166" t="n">
-        <v>406</v>
+        <v>2750437</v>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="n">
-        <v>165</v>
+        <v>216</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>-1002769760671</v>
+        <v>-1002927005745</v>
       </c>
       <c r="B167" t="n">
-        <v>10919</v>
+        <v>501</v>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="n">
-        <v>166</v>
+        <v>218</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>-1002529665437</v>
+        <v>-1002799861129</v>
       </c>
       <c r="B168" t="n">
-        <v>488</v>
+        <v>227</v>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="n">
-        <v>167</v>
+        <v>219</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>-1002392593385</v>
+        <v>-1002522147223</v>
       </c>
       <c r="B169" t="n">
-        <v>446152</v>
+        <v>440</v>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="n">
-        <v>168</v>
+        <v>220</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>-1002680979996</v>
+        <v>-1002659291107</v>
       </c>
       <c r="B170" t="n">
-        <v>88875</v>
+        <v>22765</v>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="n">
-        <v>169</v>
+        <v>221</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>-1001801324223</v>
+        <v>-1002334852527</v>
       </c>
       <c r="B171" t="n">
-        <v>99528</v>
+        <v>2294</v>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
-        <v>170</v>
+        <v>222</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>-1002438767403</v>
+        <v>-1002423915712</v>
       </c>
       <c r="B172" t="n">
-        <v>1262</v>
+        <v>104354</v>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="n">
-        <v>171</v>
+        <v>223</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>-1002729517184</v>
+        <v>-1002825020185</v>
       </c>
       <c r="B173" t="n">
-        <v>1593</v>
+        <v>418</v>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="n">
-        <v>172</v>
+        <v>224</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>-1001765476229</v>
+        <v>-1002217503260</v>
       </c>
       <c r="B174" t="n">
-        <v>161779</v>
+        <v>158658</v>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="n">
-        <v>173</v>
+        <v>226</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>-1002956355871</v>
+        <v>-1002850122868</v>
       </c>
       <c r="B175" t="n">
-        <v>17247</v>
-      </c>
-      <c r="C175" t="n">
-        <v>1</v>
-      </c>
+        <v>122804</v>
+      </c>
+      <c r="C175" t="inlineStr"/>
       <c r="D175" t="n">
-        <v>174</v>
+        <v>227</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>-4925721655</v>
+        <v>-1002761685886</v>
       </c>
       <c r="B176" t="n">
-        <v>70065</v>
+        <v>7315</v>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="n">
-        <v>175</v>
+        <v>228</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>-1002773230946</v>
+        <v>-1002860460728</v>
       </c>
       <c r="B177" t="n">
-        <v>12886</v>
+        <v>47380</v>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="n">
-        <v>176</v>
+        <v>229</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>-1001261718716</v>
+        <v>-1002414175598</v>
       </c>
       <c r="B178" t="n">
-        <v>1705251</v>
+        <v>32981</v>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="n">
-        <v>177</v>
+        <v>233</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>-1002809543928</v>
+        <v>-1002848062475</v>
       </c>
       <c r="B179" t="n">
-        <v>1748</v>
+        <v>11025</v>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="n">
-        <v>178</v>
+        <v>234</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>-1002916180495</v>
+        <v>-1003038352740</v>
       </c>
       <c r="B180" t="n">
-        <v>2390</v>
+        <v>9065</v>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="n">
-        <v>179</v>
+        <v>235</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>-4859108486</v>
+        <v>-1002368488534</v>
       </c>
       <c r="B181" t="n">
-        <v>70069</v>
+        <v>195740</v>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="n">
-        <v>180</v>
+        <v>236</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>-4863174120</v>
-      </c>
-      <c r="B182" t="inlineStr"/>
+        <v>-1002516135792</v>
+      </c>
+      <c r="B182" t="n">
+        <v>1030</v>
+      </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="n">
-        <v>181</v>
+        <v>237</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>-1002235597132</v>
+        <v>-1002651560084</v>
       </c>
       <c r="B183" t="n">
-        <v>2900</v>
+        <v>15050</v>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>182</v>
+        <v>238</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>-1003041516252</v>
+        <v>-1002518094653</v>
       </c>
       <c r="B184" t="n">
-        <v>528</v>
+        <v>11757</v>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
-        <v>183</v>
+        <v>239</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>-4863520102</v>
-      </c>
-      <c r="B185" t="inlineStr"/>
+        <v>-1002760392715</v>
+      </c>
+      <c r="B185" t="n">
+        <v>73589</v>
+      </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="n">
-        <v>184</v>
+        <v>240</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>-1001744426195</v>
+        <v>-1002579055686</v>
       </c>
       <c r="B186" t="n">
-        <v>925630</v>
+        <v>82131</v>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="n">
-        <v>185</v>
+        <v>241</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>-1002260533641</v>
+        <v>-1002647444996</v>
       </c>
       <c r="B187" t="n">
-        <v>426</v>
+        <v>19208</v>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
-        <v>186</v>
+        <v>243</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>-1002586761919</v>
+        <v>-1002863926597</v>
       </c>
       <c r="B188" t="n">
-        <v>526</v>
+        <v>8461</v>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="n">
-        <v>187</v>
+        <v>244</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>-1002549453056</v>
-      </c>
-      <c r="B189" t="n">
-        <v>5573</v>
-      </c>
+        <v>-4977264275</v>
+      </c>
+      <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="n">
-        <v>188</v>
+        <v>245</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>-1002784515802</v>
+        <v>-1002562282389</v>
       </c>
       <c r="B190" t="n">
-        <v>5155</v>
+        <v>4258</v>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="n">
-        <v>189</v>
+        <v>246</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>-1002465441179</v>
+        <v>-1002416638992</v>
       </c>
       <c r="B191" t="n">
-        <v>463754</v>
+        <v>201423</v>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="n">
-        <v>190</v>
+        <v>247</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>-1002338100665</v>
+        <v>-1002403581849</v>
       </c>
       <c r="B192" t="n">
-        <v>162572</v>
+        <v>9096</v>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="n">
-        <v>191</v>
+        <v>248</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>-4852298794</v>
-      </c>
-      <c r="B193" t="inlineStr"/>
+        <v>-1001460104025</v>
+      </c>
+      <c r="B193" t="n">
+        <v>46389</v>
+      </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="n">
-        <v>192</v>
+        <v>250</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>-1001807175468</v>
+        <v>-1002889377215</v>
       </c>
       <c r="B194" t="n">
-        <v>1493067</v>
+        <v>18972</v>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="n">
-        <v>193</v>
+        <v>251</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>-1002288363987</v>
+        <v>-1002898563298</v>
       </c>
       <c r="B195" t="n">
-        <v>408280</v>
+        <v>11136</v>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="n">
-        <v>194</v>
+        <v>253</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>-4877376604</v>
+        <v>-1002031457701</v>
       </c>
       <c r="B196" t="n">
-        <v>70075</v>
+        <v>470961</v>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="n">
-        <v>195</v>
+        <v>254</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>-1002872770022</v>
+        <v>-1002733851343</v>
       </c>
       <c r="B197" t="n">
-        <v>247896</v>
+        <v>20689</v>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
-        <v>196</v>
+        <v>255</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>-4961873359</v>
+        <v>-4921455900</v>
       </c>
       <c r="B198" t="n">
-        <v>70072</v>
+        <v>72349</v>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="n">
-        <v>197</v>
+        <v>256</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>-1002722253045</v>
+        <v>-1001611710912</v>
       </c>
       <c r="B199" t="n">
-        <v>216</v>
+        <v>1018575</v>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="n">
-        <v>198</v>
+        <v>257</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>-1002687817339</v>
+        <v>-1002977896648</v>
       </c>
       <c r="B200" t="n">
-        <v>305</v>
+        <v>190</v>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="n">
-        <v>199</v>
+        <v>258</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>-1002324412075</v>
+        <v>-1002782716052</v>
       </c>
       <c r="B201" t="n">
-        <v>13027</v>
+        <v>19169</v>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>-1002753235468</v>
+        <v>-1002582659607</v>
       </c>
       <c r="B202" t="n">
-        <v>2683</v>
+        <v>996</v>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="n">
-        <v>201</v>
+        <v>262</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>-4952186637</v>
-      </c>
-      <c r="B203" t="inlineStr"/>
+        <v>-1002169700144</v>
+      </c>
+      <c r="B203" t="n">
+        <v>43815</v>
+      </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="n">
-        <v>202</v>
+        <v>264</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>-1002514951234</v>
-      </c>
-      <c r="B204" t="inlineStr"/>
+        <v>-1001652492827</v>
+      </c>
+      <c r="B204" t="n">
+        <v>3276</v>
+      </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="n">
-        <v>203</v>
+        <v>265</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>-1002096741759</v>
+        <v>-1002560099813</v>
       </c>
       <c r="B205" t="n">
-        <v>124782</v>
+        <v>17808</v>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="n">
-        <v>204</v>
+        <v>266</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>-1002367453033</v>
-      </c>
-      <c r="B206" t="n">
-        <v>434893</v>
-      </c>
-      <c r="C206" t="n">
-        <v>1</v>
-      </c>
+        <v>-4964721197</v>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr"/>
       <c r="D206" t="n">
-        <v>205</v>
+        <v>267</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>-1002806388271</v>
+        <v>-1003045110726</v>
       </c>
       <c r="B207" t="n">
-        <v>178</v>
+        <v>3475</v>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="n">
-        <v>206</v>
+        <v>269</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>-1002574734886</v>
+        <v>-1002168855114</v>
       </c>
       <c r="B208" t="n">
-        <v>830</v>
+        <v>235783</v>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="n">
-        <v>207</v>
+        <v>270</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>-1002388609283</v>
+        <v>-1002420273008</v>
       </c>
       <c r="B209" t="n">
-        <v>277339</v>
+        <v>99677</v>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="n">
-        <v>208</v>
+        <v>272</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>-1002155445752</v>
-      </c>
-      <c r="B210" t="n">
-        <v>1208</v>
-      </c>
+        <v>-4901343480</v>
+      </c>
+      <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="n">
-        <v>209</v>
+        <v>274</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>-1003066477129</v>
+        <v>-1002860463322</v>
       </c>
       <c r="B211" t="n">
-        <v>31015</v>
+        <v>272</v>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="n">
-        <v>210</v>
+        <v>277</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>-1002587384955</v>
+        <v>-1002300501716</v>
       </c>
       <c r="B212" t="n">
-        <v>19494</v>
+        <v>18897</v>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="n">
-        <v>211</v>
+        <v>278</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>-1002661244330</v>
+        <v>-1002621836135</v>
       </c>
       <c r="B213" t="n">
-        <v>2725</v>
+        <v>9129</v>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
-        <v>212</v>
+        <v>279</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>-1002567310940</v>
-      </c>
-      <c r="B214" t="inlineStr"/>
+        <v>-1002632678475</v>
+      </c>
+      <c r="B214" t="n">
+        <v>988</v>
+      </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="n">
-        <v>213</v>
+        <v>280</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>-1002393739109</v>
+        <v>-1002658418497</v>
       </c>
       <c r="B215" t="n">
-        <v>653128</v>
+        <v>6114</v>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="n">
-        <v>214</v>
+        <v>281</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>-1002368728861</v>
+        <v>-4964952099</v>
       </c>
       <c r="B216" t="n">
-        <v>3943</v>
+        <v>51359</v>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="n">
-        <v>215</v>
+        <v>282</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>-1001817635995</v>
+        <v>-1003011064222</v>
       </c>
       <c r="B217" t="n">
-        <v>2744666</v>
+        <v>475</v>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="n">
-        <v>216</v>
+        <v>283</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>-1002289498037</v>
-      </c>
-      <c r="B218" t="inlineStr"/>
+        <v>-1001671470841</v>
+      </c>
+      <c r="B218" t="n">
+        <v>157345</v>
+      </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="n">
-        <v>217</v>
+        <v>284</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>-1002927005745</v>
+        <v>-1002391001829</v>
       </c>
       <c r="B219" t="n">
-        <v>489</v>
+        <v>513</v>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="n">
-        <v>218</v>
+        <v>286</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>-1002799861129</v>
+        <v>-1002614518240</v>
       </c>
       <c r="B220" t="n">
-        <v>215</v>
+        <v>120431</v>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="n">
-        <v>219</v>
+        <v>287</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>-1002522147223</v>
+        <v>-1002713471991</v>
       </c>
       <c r="B221" t="n">
-        <v>428</v>
+        <v>67340</v>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="n">
-        <v>220</v>
+        <v>289</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>-1002659291107</v>
-      </c>
-      <c r="B222" t="n">
-        <v>22714</v>
-      </c>
+        <v>-4912413878</v>
+      </c>
+      <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="n">
-        <v>221</v>
+        <v>290</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>-1002334852527</v>
+        <v>-1001950007498</v>
       </c>
       <c r="B223" t="n">
-        <v>2278</v>
+        <v>608273</v>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="n">
-        <v>222</v>
+        <v>291</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>-1002423915712</v>
+        <v>-1002778350864</v>
       </c>
       <c r="B224" t="n">
-        <v>103841</v>
+        <v>4711</v>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="n">
-        <v>223</v>
+        <v>292</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>-1002825020185</v>
+        <v>-1002670277933</v>
       </c>
       <c r="B225" t="n">
-        <v>406</v>
+        <v>36864</v>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="n">
-        <v>224</v>
+        <v>293</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>-1002402294669</v>
+        <v>-1002776521317</v>
       </c>
       <c r="B226" t="n">
-        <v>2552</v>
+        <v>4876</v>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="n">
-        <v>225</v>
+        <v>294</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>-1002217503260</v>
+        <v>-1002593143797</v>
       </c>
       <c r="B227" t="n">
-        <v>157214</v>
+        <v>3669</v>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="n">
-        <v>226</v>
+        <v>295</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>-1002850122868</v>
+        <v>-1002289430922</v>
       </c>
       <c r="B228" t="n">
-        <v>121961</v>
+        <v>58366</v>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="n">
-        <v>227</v>
+        <v>296</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>-1002761685886</v>
+        <v>-1002761501601</v>
       </c>
       <c r="B229" t="n">
-        <v>6927</v>
+        <v>7204</v>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="n">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>-1002860460728</v>
+        <v>-1002566090891</v>
       </c>
       <c r="B230" t="n">
-        <v>46662</v>
+        <v>6315</v>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="n">
-        <v>229</v>
+        <v>298</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>-1002775767909</v>
+        <v>-1001302667285</v>
       </c>
       <c r="B231" t="n">
-        <v>5006</v>
+        <v>3795289</v>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="n">
-        <v>230</v>
+        <v>299</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>-1002662511273</v>
+        <v>-1002621241174</v>
       </c>
       <c r="B232" t="n">
-        <v>68879</v>
-      </c>
-      <c r="C232" t="n">
-        <v>1</v>
-      </c>
+        <v>7769</v>
+      </c>
+      <c r="C232" t="inlineStr"/>
       <c r="D232" t="n">
-        <v>231</v>
+        <v>300</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>-1002174910172</v>
-      </c>
-      <c r="B233" t="n">
-        <v>85237</v>
-      </c>
+        <v>-1002813643590</v>
+      </c>
+      <c r="B233" t="inlineStr"/>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="n">
-        <v>232</v>
+        <v>301</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>-1002414175598</v>
+        <v>-1002734752869</v>
       </c>
       <c r="B234" t="n">
-        <v>32969</v>
+        <v>2698</v>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="n">
-        <v>233</v>
+        <v>302</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>-1002848062475</v>
+        <v>-1002579287925</v>
       </c>
       <c r="B235" t="n">
-        <v>10630</v>
+        <v>661</v>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="n">
-        <v>234</v>
+        <v>303</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>-1003038352740</v>
+        <v>-1002040217076</v>
       </c>
       <c r="B236" t="n">
-        <v>8390</v>
+        <v>103692</v>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="n">
-        <v>235</v>
+        <v>304</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>-1002368488534</v>
+        <v>-1002486834455</v>
       </c>
       <c r="B237" t="n">
-        <v>195118</v>
+        <v>10031</v>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="n">
-        <v>236</v>
+        <v>305</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>-1002516135792</v>
+        <v>-1001977703658</v>
       </c>
       <c r="B238" t="n">
-        <v>1018</v>
+        <v>81343</v>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>-1002651560084</v>
+        <v>-1002702700644</v>
       </c>
       <c r="B239" t="n">
-        <v>14645</v>
-      </c>
-      <c r="C239" t="inlineStr"/>
+        <v>487</v>
+      </c>
+      <c r="C239" t="n">
+        <v>1</v>
+      </c>
       <c r="D239" t="n">
-        <v>238</v>
+        <v>307</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>-1002518094653</v>
+        <v>-1002702518774</v>
       </c>
       <c r="B240" t="n">
-        <v>11233</v>
+        <v>297</v>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="n">
-        <v>239</v>
+        <v>308</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>-1002760392715</v>
+        <v>-1002998185557</v>
       </c>
       <c r="B241" t="n">
-        <v>73176</v>
+        <v>198</v>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="n">
-        <v>240</v>
+        <v>309</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>-1002579055686</v>
+        <v>-1002342685523</v>
       </c>
       <c r="B242" t="n">
-        <v>79500</v>
+        <v>62805</v>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
-        <v>241</v>
+        <v>310</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>-1002646919667</v>
+        <v>-1002738115577</v>
       </c>
       <c r="B243" t="n">
-        <v>572</v>
+        <v>12162</v>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="n">
-        <v>242</v>
+        <v>311</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>-1002647444996</v>
+        <v>-1002684891199</v>
       </c>
       <c r="B244" t="n">
-        <v>19145</v>
+        <v>31497</v>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="n">
-        <v>243</v>
+        <v>312</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>-1002863926597</v>
+        <v>-1002870267087</v>
       </c>
       <c r="B245" t="n">
-        <v>8078</v>
+        <v>207</v>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="n">
-        <v>244</v>
+        <v>313</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>-4977264275</v>
+        <v>-4989200624</v>
       </c>
       <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="n">
-        <v>245</v>
+        <v>314</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>-1002562282389</v>
+        <v>-1002540598427</v>
       </c>
       <c r="B247" t="n">
-        <v>4217</v>
+        <v>4665</v>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="n">
-        <v>246</v>
+        <v>315</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>-1002416638992</v>
+        <v>-1001985964144</v>
       </c>
       <c r="B248" t="n">
-        <v>200649</v>
+        <v>491604</v>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="n">
-        <v>247</v>
+        <v>316</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>-1002403581849</v>
+        <v>-1003016951295</v>
       </c>
       <c r="B249" t="n">
-        <v>9083</v>
+        <v>40107</v>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="n">
-        <v>248</v>
+        <v>317</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>-1002441090898</v>
+        <v>-1002250428372</v>
       </c>
       <c r="B250" t="n">
-        <v>48378</v>
+        <v>7167</v>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="n">
-        <v>249</v>
+        <v>318</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>-1001460104025</v>
+        <v>-1002999961089</v>
       </c>
       <c r="B251" t="n">
-        <v>46371</v>
+        <v>5122</v>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="n">
-        <v>250</v>
+        <v>319</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>-1002889377215</v>
+        <v>-1002727925450</v>
       </c>
       <c r="B252" t="n">
-        <v>18295</v>
+        <v>1208</v>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="n">
-        <v>251</v>
+        <v>320</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>-1002282996241</v>
+        <v>-1001298208876</v>
       </c>
       <c r="B253" t="n">
-        <v>1044</v>
+        <v>1504959</v>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="n">
-        <v>252</v>
+        <v>321</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>-1002898563298</v>
-      </c>
-      <c r="B254" t="n">
-        <v>10619</v>
-      </c>
+        <v>-1002840970643</v>
+      </c>
+      <c r="B254" t="inlineStr"/>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="n">
-        <v>253</v>
+        <v>322</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>-1002031457701</v>
+        <v>-1002895659136</v>
       </c>
       <c r="B255" t="n">
-        <v>462734</v>
+        <v>1324</v>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="n">
-        <v>254</v>
+        <v>324</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>-1002733851343</v>
+        <v>-1002534699760</v>
       </c>
       <c r="B256" t="n">
-        <v>20520</v>
+        <v>19934</v>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="n">
-        <v>255</v>
+        <v>325</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>-4921455900</v>
+        <v>-1002359766306</v>
       </c>
       <c r="B257" t="n">
-        <v>70067</v>
-      </c>
-      <c r="C257" t="inlineStr"/>
+        <v>13587</v>
+      </c>
+      <c r="C257" t="n">
+        <v>1</v>
+      </c>
       <c r="D257" t="n">
-        <v>256</v>
+        <v>326</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>-1001611710912</v>
+        <v>-1002300324334</v>
       </c>
       <c r="B258" t="n">
-        <v>1018139</v>
+        <v>169218</v>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="n">
-        <v>257</v>
+        <v>328</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>-1002977896648</v>
+        <v>-1002575818224</v>
       </c>
       <c r="B259" t="n">
-        <v>178</v>
+        <v>1418</v>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="n">
-        <v>258</v>
+        <v>329</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>-1002705610341</v>
+        <v>-1002175510705</v>
       </c>
       <c r="B260" t="n">
-        <v>798</v>
+        <v>14315</v>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="n">
-        <v>259</v>
+        <v>330</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>-1002782716052</v>
+        <v>-1002092627141</v>
       </c>
       <c r="B261" t="n">
-        <v>19144</v>
+        <v>42134</v>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="n">
-        <v>260</v>
+        <v>331</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>-1002375757909</v>
+        <v>-1002585116909</v>
       </c>
       <c r="B262" t="n">
-        <v>3040</v>
+        <v>2291</v>
       </c>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="n">
-        <v>261</v>
+        <v>332</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>-1002582659607</v>
+        <v>-1002209520317</v>
       </c>
       <c r="B263" t="n">
-        <v>984</v>
+        <v>238136</v>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="n">
-        <v>262</v>
+        <v>333</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>-1002776420318</v>
+        <v>-1002760607433</v>
       </c>
       <c r="B264" t="n">
-        <v>45459</v>
+        <v>3574</v>
       </c>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="n">
-        <v>263</v>
+        <v>334</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>-1002169700144</v>
+        <v>-1002523705245</v>
       </c>
       <c r="B265" t="n">
-        <v>43525</v>
+        <v>43129</v>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="n">
-        <v>264</v>
+        <v>335</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>-1001652492827</v>
+        <v>-1002600708556</v>
       </c>
       <c r="B266" t="n">
-        <v>3263</v>
+        <v>33111</v>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="n">
-        <v>265</v>
+        <v>337</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>-1002560099813</v>
-      </c>
-      <c r="B267" t="n">
-        <v>17755</v>
-      </c>
+        <v>-4979055727</v>
+      </c>
+      <c r="B267" t="inlineStr"/>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="n">
-        <v>266</v>
+        <v>338</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>-4964721197</v>
-      </c>
-      <c r="B268" t="inlineStr"/>
+        <v>-1002518146543</v>
+      </c>
+      <c r="B268" t="n">
+        <v>128688</v>
+      </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="n">
-        <v>267</v>
+        <v>339</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>-1002285802621</v>
+        <v>-1002509726671</v>
       </c>
       <c r="B269" t="n">
-        <v>20486</v>
+        <v>322</v>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="n">
-        <v>268</v>
+        <v>341</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>-1003045110726</v>
+        <v>-1002753083965</v>
       </c>
       <c r="B270" t="n">
-        <v>3264</v>
+        <v>48800</v>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="n">
-        <v>269</v>
+        <v>342</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>-1002168855114</v>
+        <v>-1002077075261</v>
       </c>
       <c r="B271" t="n">
-        <v>234965</v>
+        <v>47646</v>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="n">
-        <v>270</v>
+        <v>343</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>-1002721639150</v>
+        <v>-1002873170822</v>
       </c>
       <c r="B272" t="n">
-        <v>111986</v>
+        <v>6699</v>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="n">
-        <v>271</v>
+        <v>344</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>-1002420273008</v>
+        <v>-1002872579152</v>
       </c>
       <c r="B273" t="n">
-        <v>99239</v>
+        <v>8089</v>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="n">
-        <v>272</v>
+        <v>345</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>-1002414159979</v>
+        <v>-1002296316011</v>
       </c>
       <c r="B274" t="n">
-        <v>5281</v>
+        <v>12884</v>
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="n">
-        <v>273</v>
+        <v>348</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>-4901343480</v>
-      </c>
-      <c r="B275" t="inlineStr"/>
+        <v>-4162328212</v>
+      </c>
+      <c r="B275" t="n">
+        <v>72345</v>
+      </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="n">
-        <v>274</v>
+        <v>350</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>-1002607966924</v>
+        <v>-4884314925</v>
       </c>
       <c r="B276" t="n">
-        <v>48294</v>
+        <v>72348</v>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="n">
-        <v>275</v>
+        <v>351</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>-4907907911</v>
+        <v>-1002595442276</v>
       </c>
       <c r="B277" t="n">
-        <v>51363</v>
+        <v>22001</v>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="n">
-        <v>276</v>
+        <v>352</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>-1002860463322</v>
+        <v>-1002372506024</v>
       </c>
       <c r="B278" t="n">
-        <v>260</v>
+        <v>36634</v>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="n">
-        <v>277</v>
+        <v>353</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>-1002300501716</v>
+        <v>-1002395833812</v>
       </c>
       <c r="B279" t="n">
-        <v>18341</v>
+        <v>9467</v>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="n">
-        <v>278</v>
+        <v>354</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>-1002621836135</v>
+        <v>-1002600128976</v>
       </c>
       <c r="B280" t="n">
-        <v>8746</v>
+        <v>6960</v>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="n">
-        <v>279</v>
+        <v>355</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>-1002632678475</v>
+        <v>-1002773657299</v>
       </c>
       <c r="B281" t="n">
-        <v>974</v>
+        <v>1938</v>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="n">
-        <v>280</v>
+        <v>358</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>-1002658418497</v>
+        <v>-4819895741</v>
       </c>
       <c r="B282" t="n">
-        <v>6075</v>
+        <v>72347</v>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="n">
-        <v>281</v>
+        <v>360</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>-4964952099</v>
+        <v>-1002571339758</v>
       </c>
       <c r="B283" t="n">
-        <v>51359</v>
+        <v>36597</v>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="n">
-        <v>282</v>
+        <v>361</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>-1003011064222</v>
+        <v>-1002664729996</v>
       </c>
       <c r="B284" t="n">
-        <v>462</v>
+        <v>8212</v>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="n">
-        <v>283</v>
+        <v>362</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>-1001671470841</v>
+        <v>-1002624308239</v>
       </c>
       <c r="B285" t="n">
-        <v>156916</v>
+        <v>18670</v>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="n">
-        <v>284</v>
+        <v>364</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>-1002312340934</v>
+        <v>-1001373559245</v>
       </c>
       <c r="B286" t="n">
-        <v>28864</v>
+        <v>116456</v>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="n">
-        <v>285</v>
+        <v>366</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>-1002391001829</v>
+        <v>-1002826605956</v>
       </c>
       <c r="B287" t="n">
-        <v>501</v>
+        <v>623</v>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="n">
-        <v>286</v>
+        <v>367</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>-1002614518240</v>
+        <v>-1002309114039</v>
       </c>
       <c r="B288" t="n">
-        <v>111560</v>
+        <v>90268</v>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="n">
-        <v>287</v>
+        <v>368</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>-1002294910779</v>
+        <v>-1002618584679</v>
       </c>
       <c r="B289" t="n">
-        <v>114891</v>
+        <v>4755</v>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="n">
-        <v>288</v>
+        <v>369</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>-1002713471991</v>
+        <v>-1001868146441</v>
       </c>
       <c r="B290" t="n">
-        <v>66565</v>
+        <v>262385</v>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="n">
-        <v>289</v>
+        <v>370</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>-4912413878</v>
-      </c>
-      <c r="B291" t="inlineStr"/>
+        <v>-1002288129210</v>
+      </c>
+      <c r="B291" t="n">
+        <v>140469</v>
+      </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="n">
-        <v>290</v>
+        <v>371</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>-1001950007498</v>
+        <v>-1001701084460</v>
       </c>
       <c r="B292" t="n">
-        <v>603631</v>
+        <v>201049</v>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="n">
-        <v>291</v>
+        <v>372</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>-1002778350864</v>
+        <v>-1002418585410</v>
       </c>
       <c r="B293" t="n">
-        <v>4488</v>
+        <v>14173</v>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="n">
-        <v>292</v>
+        <v>373</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>-1002670277933</v>
+        <v>-1003048077625</v>
       </c>
       <c r="B294" t="n">
-        <v>36180</v>
+        <v>474</v>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="n">
-        <v>293</v>
+        <v>375</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>-1002776521317</v>
+        <v>-1002007016158</v>
       </c>
       <c r="B295" t="n">
-        <v>4822</v>
+        <v>1200176</v>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="n">
-        <v>294</v>
+        <v>376</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>-1002593143797</v>
+        <v>-1002597892903</v>
       </c>
       <c r="B296" t="n">
-        <v>3656</v>
+        <v>228136</v>
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="n">
-        <v>295</v>
+        <v>377</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>-1002289430922</v>
+        <v>-1002853960198</v>
       </c>
       <c r="B297" t="n">
-        <v>57773</v>
+        <v>6668</v>
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="n">
-        <v>296</v>
+        <v>378</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>-1002761501601</v>
+        <v>-1002764128440</v>
       </c>
       <c r="B298" t="n">
-        <v>6367</v>
-      </c>
-      <c r="C298" t="inlineStr"/>
+        <v>7363</v>
+      </c>
+      <c r="C298" t="n">
+        <v>1</v>
+      </c>
       <c r="D298" t="n">
-        <v>297</v>
+        <v>379</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>-1002566090891</v>
+        <v>-1002457910402</v>
       </c>
       <c r="B299" t="n">
-        <v>5931</v>
+        <v>5702</v>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="n">
-        <v>298</v>
+        <v>380</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>-1001302667285</v>
+        <v>-1002695735836</v>
       </c>
       <c r="B300" t="n">
-        <v>3793601</v>
+        <v>5228</v>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="n">
-        <v>299</v>
+        <v>381</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>-1002621241174</v>
+        <v>-1003055781840</v>
       </c>
       <c r="B301" t="n">
-        <v>7379</v>
+        <v>5789</v>
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="n">
-        <v>300</v>
+        <v>382</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>-1002813643590</v>
-      </c>
-      <c r="B302" t="inlineStr"/>
+        <v>-1001124651563</v>
+      </c>
+      <c r="B302" t="n">
+        <v>93915</v>
+      </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="n">
-        <v>301</v>
+        <v>384</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>-1002734752869</v>
-      </c>
-      <c r="B303" t="n">
-        <v>2698</v>
-      </c>
+        <v>-4859225688</v>
+      </c>
+      <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="n">
-        <v>302</v>
+        <v>385</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>-1002579287925</v>
+        <v>-1002237965843</v>
       </c>
       <c r="B304" t="n">
-        <v>639</v>
+        <v>201598</v>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="n">
-        <v>303</v>
+        <v>386</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>-1002040217076</v>
+        <v>-1002933730666</v>
       </c>
       <c r="B305" t="n">
-        <v>103149</v>
+        <v>2986</v>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="n">
-        <v>304</v>
+        <v>388</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>-1002486834455</v>
+        <v>-1002593501991</v>
       </c>
       <c r="B306" t="n">
-        <v>9642</v>
+        <v>6341</v>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="n">
-        <v>305</v>
+        <v>389</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>-1001977703658</v>
+        <v>-1002265393780</v>
       </c>
       <c r="B307" t="n">
-        <v>80345</v>
+        <v>49273</v>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="n">
-        <v>306</v>
+        <v>390</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>-1002702700644</v>
+        <v>-1003084989152</v>
       </c>
       <c r="B308" t="n">
-        <v>467</v>
-      </c>
-      <c r="C308" t="n">
-        <v>1</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="C308" t="inlineStr"/>
       <c r="D308" t="n">
-        <v>307</v>
+        <v>391</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>-1002702518774</v>
+        <v>-1003055719997</v>
       </c>
       <c r="B309" t="n">
-        <v>285</v>
+        <v>7177</v>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="n">
-        <v>308</v>
+        <v>392</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>-1002998185557</v>
+        <v>-1003463864177</v>
       </c>
       <c r="B310" t="n">
-        <v>186</v>
-      </c>
-      <c r="C310" t="inlineStr"/>
+        <v>131753</v>
+      </c>
+      <c r="C310" t="n">
+        <v>1</v>
+      </c>
       <c r="D310" t="n">
-        <v>309</v>
+        <v>393</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>-1002342685523</v>
+        <v>-1002812268562</v>
       </c>
       <c r="B311" t="n">
-        <v>62457</v>
+        <v>979</v>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="n">
-        <v>310</v>
+        <v>394</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>-1002738115577</v>
+        <v>-1003141918793</v>
       </c>
       <c r="B312" t="n">
-        <v>11340</v>
-      </c>
-      <c r="C312" t="inlineStr"/>
+        <v>35873</v>
+      </c>
+      <c r="C312" t="n">
+        <v>1</v>
+      </c>
       <c r="D312" t="n">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="n">
-        <v>-1002684891199</v>
-      </c>
-      <c r="B313" t="n">
-        <v>30943</v>
-      </c>
-      <c r="C313" t="inlineStr"/>
-      <c r="D313" t="n">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="n">
-        <v>-1002870267087</v>
-      </c>
-      <c r="B314" t="n">
-        <v>195</v>
-      </c>
-      <c r="C314" t="inlineStr"/>
-      <c r="D314" t="n">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="n">
-        <v>-4989200624</v>
-      </c>
-      <c r="B315" t="inlineStr"/>
-      <c r="C315" t="inlineStr"/>
-      <c r="D315" t="n">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="n">
-        <v>-1002540598427</v>
-      </c>
-      <c r="B316" t="n">
-        <v>4637</v>
-      </c>
-      <c r="C316" t="inlineStr"/>
-      <c r="D316" t="n">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="n">
-        <v>-1001985964144</v>
-      </c>
-      <c r="B317" t="n">
-        <v>489695</v>
-      </c>
-      <c r="C317" t="inlineStr"/>
-      <c r="D317" t="n">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="n">
-        <v>-1003016951295</v>
-      </c>
-      <c r="B318" t="n">
-        <v>39547</v>
-      </c>
-      <c r="C318" t="inlineStr"/>
-      <c r="D318" t="n">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="n">
-        <v>-1002250428372</v>
-      </c>
-      <c r="B319" t="n">
-        <v>6784</v>
-      </c>
-      <c r="C319" t="inlineStr"/>
-      <c r="D319" t="n">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="n">
-        <v>-1002999961089</v>
-      </c>
-      <c r="B320" t="n">
-        <v>4724</v>
-      </c>
-      <c r="C320" t="inlineStr"/>
-      <c r="D320" t="n">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="n">
-        <v>-1002727925450</v>
-      </c>
-      <c r="B321" t="n">
-        <v>1193</v>
-      </c>
-      <c r="C321" t="inlineStr"/>
-      <c r="D321" t="n">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="n">
-        <v>-1001298208876</v>
-      </c>
-      <c r="B322" t="n">
-        <v>1501761</v>
-      </c>
-      <c r="C322" t="inlineStr"/>
-      <c r="D322" t="n">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="n">
-        <v>-1002840970643</v>
-      </c>
-      <c r="B323" t="inlineStr"/>
-      <c r="C323" t="inlineStr"/>
-      <c r="D323" t="n">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="n">
-        <v>-1002000692982</v>
-      </c>
-      <c r="B324" t="n">
-        <v>18170</v>
-      </c>
-      <c r="C324" t="inlineStr"/>
-      <c r="D324" t="n">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="n">
-        <v>-1002895659136</v>
-      </c>
-      <c r="B325" t="n">
-        <v>1260</v>
-      </c>
-      <c r="C325" t="inlineStr"/>
-      <c r="D325" t="n">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="n">
-        <v>-1002534699760</v>
-      </c>
-      <c r="B326" t="n">
-        <v>19395</v>
-      </c>
-      <c r="C326" t="inlineStr"/>
-      <c r="D326" t="n">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="n">
-        <v>-1002359766306</v>
-      </c>
-      <c r="B327" t="n">
-        <v>13438</v>
-      </c>
-      <c r="C327" t="n">
-        <v>1</v>
-      </c>
-      <c r="D327" t="n">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="n">
-        <v>-1002994513926</v>
-      </c>
-      <c r="B328" t="n">
-        <v>105</v>
-      </c>
-      <c r="C328" t="inlineStr"/>
-      <c r="D328" t="n">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="n">
-        <v>-1002300324334</v>
-      </c>
-      <c r="B329" t="n">
-        <v>165930</v>
-      </c>
-      <c r="C329" t="inlineStr"/>
-      <c r="D329" t="n">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="n">
-        <v>-1002575818224</v>
-      </c>
-      <c r="B330" t="n">
-        <v>1406</v>
-      </c>
-      <c r="C330" t="inlineStr"/>
-      <c r="D330" t="n">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="n">
-        <v>-1002175510705</v>
-      </c>
-      <c r="B331" t="n">
-        <v>13931</v>
-      </c>
-      <c r="C331" t="inlineStr"/>
-      <c r="D331" t="n">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="n">
-        <v>-1002092627141</v>
-      </c>
-      <c r="B332" t="n">
-        <v>41749</v>
-      </c>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="n">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="n">
-        <v>-1002585116909</v>
-      </c>
-      <c r="B333" t="n">
-        <v>2279</v>
-      </c>
-      <c r="C333" t="inlineStr"/>
-      <c r="D333" t="n">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="n">
-        <v>-1002209520317</v>
-      </c>
-      <c r="B334" t="n">
-        <v>235370</v>
-      </c>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" t="n">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="n">
-        <v>-1002760607433</v>
-      </c>
-      <c r="B335" t="n">
-        <v>3562</v>
-      </c>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" t="n">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="n">
-        <v>-1002523705245</v>
-      </c>
-      <c r="B336" t="n">
-        <v>43098</v>
-      </c>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="n">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="n">
-        <v>-1002489004153</v>
-      </c>
-      <c r="B337" t="n">
-        <v>3431</v>
-      </c>
-      <c r="C337" t="inlineStr"/>
-      <c r="D337" t="n">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="n">
-        <v>-1002600708556</v>
-      </c>
-      <c r="B338" t="n">
-        <v>32693</v>
-      </c>
-      <c r="C338" t="inlineStr"/>
-      <c r="D338" t="n">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="n">
-        <v>-4979055727</v>
-      </c>
-      <c r="B339" t="inlineStr"/>
-      <c r="C339" t="inlineStr"/>
-      <c r="D339" t="n">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="n">
-        <v>-1002518146543</v>
-      </c>
-      <c r="B340" t="n">
-        <v>127385</v>
-      </c>
-      <c r="C340" t="inlineStr"/>
-      <c r="D340" t="n">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="n">
-        <v>-1001994912432</v>
-      </c>
-      <c r="B341" t="n">
-        <v>35771</v>
-      </c>
-      <c r="C341" t="inlineStr"/>
-      <c r="D341" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="n">
-        <v>-1002509726671</v>
-      </c>
-      <c r="B342" t="n">
-        <v>310</v>
-      </c>
-      <c r="C342" t="inlineStr"/>
-      <c r="D342" t="n">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="n">
-        <v>-1002753083965</v>
-      </c>
-      <c r="B343" t="n">
-        <v>48744</v>
-      </c>
-      <c r="C343" t="inlineStr"/>
-      <c r="D343" t="n">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="n">
-        <v>-1002077075261</v>
-      </c>
-      <c r="B344" t="n">
-        <v>46902</v>
-      </c>
-      <c r="C344" t="inlineStr"/>
-      <c r="D344" t="n">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="n">
-        <v>-1002873170822</v>
-      </c>
-      <c r="B345" t="n">
-        <v>6316</v>
-      </c>
-      <c r="C345" t="inlineStr"/>
-      <c r="D345" t="n">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="n">
-        <v>-1002872579152</v>
-      </c>
-      <c r="B346" t="n">
-        <v>7665</v>
-      </c>
-      <c r="C346" t="inlineStr"/>
-      <c r="D346" t="n">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="n">
-        <v>-1002865073057</v>
-      </c>
-      <c r="B347" t="n">
-        <v>6213</v>
-      </c>
-      <c r="C347" t="inlineStr"/>
-      <c r="D347" t="n">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="n">
-        <v>-1001690032632</v>
-      </c>
-      <c r="B348" t="n">
-        <v>83880</v>
-      </c>
-      <c r="C348" t="inlineStr"/>
-      <c r="D348" t="n">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="n">
-        <v>-1002296316011</v>
-      </c>
-      <c r="B349" t="n">
-        <v>12571</v>
-      </c>
-      <c r="C349" t="inlineStr"/>
-      <c r="D349" t="n">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="n">
-        <v>-1002418045805</v>
-      </c>
-      <c r="B350" t="n">
-        <v>10488</v>
-      </c>
-      <c r="C350" t="inlineStr"/>
-      <c r="D350" t="n">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="n">
-        <v>-4162328212</v>
-      </c>
-      <c r="B351" t="n">
-        <v>70071</v>
-      </c>
-      <c r="C351" t="inlineStr"/>
-      <c r="D351" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="n">
-        <v>-4884314925</v>
-      </c>
-      <c r="B352" t="n">
-        <v>70070</v>
-      </c>
-      <c r="C352" t="inlineStr"/>
-      <c r="D352" t="n">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="n">
-        <v>-1002595442276</v>
-      </c>
-      <c r="B353" t="n">
-        <v>21952</v>
-      </c>
-      <c r="C353" t="inlineStr"/>
-      <c r="D353" t="n">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="n">
-        <v>-1002372506024</v>
-      </c>
-      <c r="B354" t="n">
-        <v>36103</v>
-      </c>
-      <c r="C354" t="inlineStr"/>
-      <c r="D354" t="n">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="n">
-        <v>-1002395833812</v>
-      </c>
-      <c r="B355" t="n">
-        <v>9320</v>
-      </c>
-      <c r="C355" t="inlineStr"/>
-      <c r="D355" t="n">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="n">
-        <v>-1002600128976</v>
-      </c>
-      <c r="B356" t="n">
-        <v>6577</v>
-      </c>
-      <c r="C356" t="inlineStr"/>
-      <c r="D356" t="n">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="n">
-        <v>-1002051152325</v>
-      </c>
-      <c r="B357" t="n">
-        <v>377034</v>
-      </c>
-      <c r="C357" t="n">
-        <v>1</v>
-      </c>
-      <c r="D357" t="n">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="n">
-        <v>-1002793365625</v>
-      </c>
-      <c r="B358" t="n">
-        <v>62636</v>
-      </c>
-      <c r="C358" t="inlineStr"/>
-      <c r="D358" t="n">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="n">
-        <v>-1002773657299</v>
-      </c>
-      <c r="B359" t="n">
-        <v>1876</v>
-      </c>
-      <c r="C359" t="inlineStr"/>
-      <c r="D359" t="n">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="n">
-        <v>-1002817300556</v>
-      </c>
-      <c r="B360" t="n">
-        <v>188</v>
-      </c>
-      <c r="C360" t="inlineStr"/>
-      <c r="D360" t="n">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="n">
-        <v>-4819895741</v>
-      </c>
-      <c r="B361" t="n">
-        <v>70068</v>
-      </c>
-      <c r="C361" t="inlineStr"/>
-      <c r="D361" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="n">
-        <v>-1002571339758</v>
-      </c>
-      <c r="B362" t="n">
-        <v>36010</v>
-      </c>
-      <c r="C362" t="inlineStr"/>
-      <c r="D362" t="n">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="n">
-        <v>-1002664729996</v>
-      </c>
-      <c r="B363" t="n">
-        <v>7827</v>
-      </c>
-      <c r="C363" t="inlineStr"/>
-      <c r="D363" t="n">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="n">
-        <v>-1002704703466</v>
-      </c>
-      <c r="B364" t="n">
-        <v>121282</v>
-      </c>
-      <c r="C364" t="inlineStr"/>
-      <c r="D364" t="n">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="n">
-        <v>-1002624308239</v>
-      </c>
-      <c r="B365" t="n">
-        <v>18135</v>
-      </c>
-      <c r="C365" t="inlineStr"/>
-      <c r="D365" t="n">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="n">
-        <v>-1002651298263</v>
-      </c>
-      <c r="B366" t="n">
-        <v>14892</v>
-      </c>
-      <c r="C366" t="inlineStr"/>
-      <c r="D366" t="n">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="n">
-        <v>-1001373559245</v>
-      </c>
-      <c r="B367" t="n">
-        <v>116292</v>
-      </c>
-      <c r="C367" t="inlineStr"/>
-      <c r="D367" t="n">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="n">
-        <v>-1002826605956</v>
-      </c>
-      <c r="B368" t="n">
-        <v>611</v>
-      </c>
-      <c r="C368" t="inlineStr"/>
-      <c r="D368" t="n">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="n">
-        <v>-1002309114039</v>
-      </c>
-      <c r="B369" t="n">
-        <v>90194</v>
-      </c>
-      <c r="C369" t="inlineStr"/>
-      <c r="D369" t="n">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="n">
-        <v>-1002618584679</v>
-      </c>
-      <c r="B370" t="n">
-        <v>4602</v>
-      </c>
-      <c r="C370" t="inlineStr"/>
-      <c r="D370" t="n">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="n">
-        <v>-1001868146441</v>
-      </c>
-      <c r="B371" t="n">
-        <v>245920</v>
-      </c>
-      <c r="C371" t="inlineStr"/>
-      <c r="D371" t="n">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="n">
-        <v>-1002288129210</v>
-      </c>
-      <c r="B372" t="n">
-        <v>137343</v>
-      </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="n">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="n">
-        <v>-1001701084460</v>
-      </c>
-      <c r="B373" t="n">
-        <v>200498</v>
-      </c>
-      <c r="C373" t="inlineStr"/>
-      <c r="D373" t="n">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="n">
-        <v>-1002418585410</v>
-      </c>
-      <c r="B374" t="n">
-        <v>13451</v>
-      </c>
-      <c r="C374" t="inlineStr"/>
-      <c r="D374" t="n">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="n">
-        <v>-1002588638126</v>
-      </c>
-      <c r="B375" t="n">
-        <v>25243</v>
-      </c>
-      <c r="C375" t="inlineStr"/>
-      <c r="D375" t="n">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="n">
-        <v>-1003048077625</v>
-      </c>
-      <c r="B376" t="n">
-        <v>450</v>
-      </c>
-      <c r="C376" t="inlineStr"/>
-      <c r="D376" t="n">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="n">
-        <v>-1002007016158</v>
-      </c>
-      <c r="B377" t="n">
-        <v>1198037</v>
-      </c>
-      <c r="C377" t="inlineStr"/>
-      <c r="D377" t="n">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="n">
-        <v>-1002597892903</v>
-      </c>
-      <c r="B378" t="n">
-        <v>225339</v>
-      </c>
-      <c r="C378" t="inlineStr"/>
-      <c r="D378" t="n">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="n">
-        <v>-1002853960198</v>
-      </c>
-      <c r="B379" t="n">
-        <v>6285</v>
-      </c>
-      <c r="C379" t="inlineStr"/>
-      <c r="D379" t="n">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="n">
-        <v>-1002764128440</v>
-      </c>
-      <c r="B380" t="n">
-        <v>7206</v>
-      </c>
-      <c r="C380" t="n">
-        <v>1</v>
-      </c>
-      <c r="D380" t="n">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="n">
-        <v>-1002457910402</v>
-      </c>
-      <c r="B381" t="n">
-        <v>5681</v>
-      </c>
-      <c r="C381" t="inlineStr"/>
-      <c r="D381" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="n">
-        <v>-1002695735836</v>
-      </c>
-      <c r="B382" t="n">
-        <v>5216</v>
-      </c>
-      <c r="C382" t="inlineStr"/>
-      <c r="D382" t="n">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="n">
-        <v>-1003055781840</v>
-      </c>
-      <c r="B383" t="n">
-        <v>5406</v>
-      </c>
-      <c r="C383" t="inlineStr"/>
-      <c r="D383" t="n">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="n">
-        <v>-1002663958642</v>
-      </c>
-      <c r="B384" t="n">
-        <v>12435</v>
-      </c>
-      <c r="C384" t="inlineStr"/>
-      <c r="D384" t="n">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="n">
-        <v>-1001124651563</v>
-      </c>
-      <c r="B385" t="n">
-        <v>93183</v>
-      </c>
-      <c r="C385" t="inlineStr"/>
-      <c r="D385" t="n">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="n">
-        <v>-4859225688</v>
-      </c>
-      <c r="B386" t="inlineStr"/>
-      <c r="C386" t="inlineStr"/>
-      <c r="D386" t="n">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="n">
-        <v>-1002237965843</v>
-      </c>
-      <c r="B387" t="n">
-        <v>192191</v>
-      </c>
-      <c r="C387" t="inlineStr"/>
-      <c r="D387" t="n">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="n">
-        <v>-1002828584222</v>
-      </c>
-      <c r="B388" t="n">
-        <v>149825</v>
-      </c>
-      <c r="C388" t="inlineStr"/>
-      <c r="D388" t="n">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="n">
-        <v>-1002933730666</v>
-      </c>
-      <c r="B389" t="n">
-        <v>2974</v>
-      </c>
-      <c r="C389" t="inlineStr"/>
-      <c r="D389" t="n">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="n">
-        <v>-1002593501991</v>
-      </c>
-      <c r="B390" t="n">
-        <v>6328</v>
-      </c>
-      <c r="C390" t="inlineStr"/>
-      <c r="D390" t="n">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="n">
-        <v>-1002265393780</v>
-      </c>
-      <c r="B391" t="n">
-        <v>41592</v>
-      </c>
-      <c r="C391" t="inlineStr"/>
-      <c r="D391" t="n">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="n">
-        <v>-1003084989152</v>
-      </c>
-      <c r="B392" t="n">
-        <v>199</v>
-      </c>
-      <c r="C392" t="inlineStr"/>
-      <c r="D392" t="n">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="n">
-        <v>-1003055719997</v>
-      </c>
-      <c r="B393" t="n">
-        <v>6678</v>
-      </c>
-      <c r="C393" t="inlineStr"/>
-      <c r="D393" t="n">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="n">
-        <v>-1003463864177</v>
-      </c>
-      <c r="B394" t="n">
-        <v>104411</v>
-      </c>
-      <c r="C394" t="n">
-        <v>1</v>
-      </c>
-      <c r="D394" t="n">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="n">
-        <v>-1002812268562</v>
-      </c>
-      <c r="B395" t="n">
-        <v>900</v>
-      </c>
-      <c r="C395" t="inlineStr"/>
-      <c r="D395" t="n">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="n">
-        <v>-1003141918793</v>
-      </c>
-      <c r="B396" t="n">
-        <v>25303</v>
-      </c>
-      <c r="C396" t="inlineStr"/>
-      <c r="D396" t="n">
         <v>395</v>
       </c>
     </row>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -1257,7 +1257,7 @@
         <v>-1002114430690</v>
       </c>
       <c r="B69" t="n">
-        <v>71286</v>
+        <v>71521</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
@@ -3499,7 +3499,7 @@
         <v>-1002359766306</v>
       </c>
       <c r="B257" t="n">
-        <v>13587</v>
+        <v>13787</v>
       </c>
       <c r="C257" t="n">
         <v>1</v>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -1257,7 +1257,7 @@
         <v>-1002114430690</v>
       </c>
       <c r="B69" t="n">
-        <v>71521</v>
+        <v>71286</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
@@ -3499,7 +3499,7 @@
         <v>-1002359766306</v>
       </c>
       <c r="B257" t="n">
-        <v>13787</v>
+        <v>13587</v>
       </c>
       <c r="C257" t="n">
         <v>1</v>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A513"/>
+  <dimension ref="A1:A520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,3584 +438,3633 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-1002753235468</t>
+          <t>-1002927005745</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-1002130498457</t>
+          <t>-4989200624</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-1002702700644</t>
+          <t>-1003462101210</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-1001449424790</t>
+          <t>-1001900924039</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>-1002591852942</t>
+          <t>-1003131016214</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-1003830260747</t>
+          <t>-1001929868118</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-1003121085754</t>
+          <t>-1003690052299</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-5238910430</t>
+          <t>-1002540598427</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>-1002237965843</t>
+          <t>-1002516135792</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>-1002025153129</t>
+          <t>-1002532154366</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>-1002844139639</t>
+          <t>-1003642398244</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>-1002318473731</t>
+          <t>-1001701084460</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>-1003078207757</t>
+          <t>-1001818008631</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>-1003365007302</t>
+          <t>-1002579287925</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>-1002493291997</t>
+          <t>-1002465441179</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>-1003576952118</t>
+          <t>-1001546837418</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>-1002680979996</t>
+          <t>-1002046646497</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>-1002562222456</t>
+          <t>-1002870935153</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>-1002519990156</t>
+          <t>-1002680979996</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>-1003100265374</t>
+          <t>-1003389986244</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>-1003642398244</t>
+          <t>-1002523705245</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>-1002632678475</t>
+          <t>-1002728494984</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>-1002754377559</t>
+          <t>-1002473130324</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>-1001832880643</t>
+          <t>-1002518556633</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>-4977264275</t>
+          <t>-1002750504156</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>-1002514951234</t>
+          <t>-1002372506024</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>-1003279388737</t>
+          <t>-1001668927089</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>-1002552125741</t>
+          <t>-4961873359</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>-1003527335437</t>
+          <t>-1001801324223</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>-1003317755929</t>
+          <t>-1002152254687</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>-1002974874463</t>
+          <t>-1001868146441</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>-1002300501716</t>
+          <t>-1002571339758</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>-1003094878642</t>
+          <t>-1002727925450</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>-1002518556633</t>
+          <t>-1003045110726</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>-4822189866</t>
+          <t>-1002237965843</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-1002529665437</t>
+          <t>-1003505125164</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>-1002452190545</t>
+          <t>-1001741252369</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>-1003131016214</t>
+          <t>-1002338100665</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>-1002659587443</t>
+          <t>-1002368488534</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>-1002016912929</t>
+          <t>-1002769760671</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>-1002848062475</t>
+          <t>-1002684891199</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>-1002998185557</t>
+          <t>-1003483467807</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>-1001994788372</t>
+          <t>-1003144692446</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>-4961873359</t>
+          <t>-1002288363987</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>-1001473268532</t>
+          <t>-1002580159815</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>-1003593024986</t>
+          <t>-1003323511757</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>-1002727925450</t>
+          <t>-1002778085921</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>-1003045110726</t>
+          <t>-1003217773561</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>-1002860463322</t>
+          <t>-1003795984362</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>-1003055781840</t>
+          <t>-1002582659607</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>-1001796760199</t>
+          <t>-1002832898246</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>-1002658418497</t>
+          <t>-1003364207368</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>-1003451010325</t>
+          <t>-1003055719997</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>-1003324947108</t>
+          <t>-1001908446355</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>-1002845355669</t>
+          <t>-1002998185557</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>-1003110118065</t>
+          <t>-4977264275</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>-1002593501991</t>
+          <t>-1002482355272</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>-1001923225361</t>
+          <t>-1001922808139</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>-1002226982992</t>
+          <t>-1001390053729</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>-1002521509637</t>
+          <t>-1003129624230</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>-1003483467807</t>
+          <t>-1003653343830</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>-1002778085921</t>
+          <t>-1002895659136</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>-1002822883977</t>
+          <t>-1003550392581</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>-1003066477129</t>
+          <t>-1003116317699</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>-4863520102</t>
+          <t>-4636171342</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>-1002448038408</t>
+          <t>-1002600128976</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>-1003485367302</t>
+          <t>-1001406184711</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>-1003389986244</t>
+          <t>-1002556802461</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>-1002205410222</t>
+          <t>-1001877368569</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>-1001390053729</t>
+          <t>-1001302667285</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>-1003177468537</t>
+          <t>-1002455033621</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>-1002320967880</t>
+          <t>-1001994788372</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>-1002585116909</t>
+          <t>-1002651012796</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>-1002664729996</t>
+          <t>-1002845355669</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>-1002288129210</t>
+          <t>-1002616170042</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>-1001819768369</t>
+          <t>-1003650147257</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>-1002482355272</t>
+          <t>-4884314925</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>-1003090299188</t>
+          <t>-1002268045818</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>-1002809610954</t>
+          <t>-4863174120</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>-1002621241174</t>
+          <t>-1002581029977</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>-1003559602288</t>
+          <t>-1002529665437</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>-1002639728798</t>
+          <t>-1002575818224</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>-1003586892139</t>
+          <t>-1001124651563</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>-1002388609283</t>
+          <t>-1003002359598</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>-1002110839951</t>
+          <t>-1002566090891</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>-1002368488534</t>
+          <t>-1002904756274</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>-1002836592504</t>
+          <t>-1003150223688</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>-1002300251125</t>
+          <t>-1003046279469</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>-2073589582939</t>
+          <t>-1002702518774</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>-1003583886956</t>
+          <t>-1003140539585</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>-1002813643590</t>
+          <t>-1002512266739</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>-1003097935757</t>
+          <t>-1002881849916</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>-1001801324223</t>
+          <t>-4562050705</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>-4964952099</t>
+          <t>-1002377976370</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>-1002809543928</t>
+          <t>-1002978401429</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>-1002263664644</t>
+          <t>-1002531024619</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>-1002074104758</t>
+          <t>-1003411536398</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>-1002391001829</t>
+          <t>-1002509299058</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>-1002320283926</t>
+          <t>-1003595525652</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>-1001298208876</t>
+          <t>-1002760607433</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>-1003046279469</t>
+          <t>-1002391001829</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>-1002761501601</t>
+          <t>-1003559602288</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>-1002872771874</t>
+          <t>-1002782716052</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>-1003055362508</t>
+          <t>-1002619556227</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>-1002860460728</t>
+          <t>-1002999961089</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>-1002733851343</t>
+          <t>-1001212305259</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>-1003084236608</t>
+          <t>-1002289430922</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>-1001735560772</t>
+          <t>-1001449424790</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>-1002903801746</t>
+          <t>-1002414175598</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>-1002455033621</t>
+          <t>-1002990595475</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>-1002863926597</t>
+          <t>-1002889377215</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>-1001596465392</t>
+          <t>-1002271738387</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>-1001467801859</t>
+          <t>-1002567310940</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>-1002622011374</t>
+          <t>-1002850122868</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>-1002175510705</t>
+          <t>-1003180215428</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>-1002670277933</t>
+          <t>-1001635430845</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>-1003192981088</t>
+          <t>-1003576952118</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>-1002715650097</t>
+          <t>-1001946318041</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>-1002288363987</t>
+          <t>-1003518656172</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>-1002324412075</t>
+          <t>-1003254448559</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>-1002265393780</t>
+          <t>-1001596465392</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>-1002615496638</t>
+          <t>-1001985964144</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>-1003417970722</t>
+          <t>-1002342685523</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>-1002806388271</t>
+          <t>-1002315372056</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>-1001922808139</t>
+          <t>-1002734752869</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>-1003246680728</t>
+          <t>-1002862636130</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>-1002255365525</t>
+          <t>-1002640591890</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>-1003093812371</t>
+          <t>-1003882816542</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>-1002575818224</t>
+          <t>-1002872770022</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>-1002779291814</t>
+          <t>-1003857994445</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>-1002520212825</t>
+          <t>-4974060502</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>-1002296316011</t>
+          <t>-1002822883977</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>-1003697454154</t>
+          <t>-1002346159781</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>-1003364207368</t>
+          <t>-1003527335437</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>-1002939992790</t>
+          <t>-1002832174643</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>-1002597892903</t>
+          <t>-1003007832445</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>-1002510217399</t>
+          <t>-1003100265374</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>-1003352103344</t>
+          <t>-1002016912929</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>-4964721197</t>
+          <t>-1002659587443</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>-1003421411518</t>
+          <t>-1002901874691</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>-1002571339758</t>
+          <t>-1002155445752</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>-1002103104897</t>
+          <t>-1001735560772</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>-1002904756274</t>
+          <t>-1002393739109</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>-1001946318041</t>
+          <t>-1002826605956</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>-1003456241208</t>
+          <t>-1003078207757</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>-1003650147257</t>
+          <t>-1002747623711</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>-4819895741</t>
+          <t>-1003641959918</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>-1002416638992</t>
+          <t>-1002454558597</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>-1002046646497</t>
+          <t>-1002322838597</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>-1002031457701</t>
+          <t>-1002933730666</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>-1002152254687</t>
+          <t>-4877376604</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>-1002428009204</t>
+          <t>-1003502104542</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>-1002144563093</t>
+          <t>-1002809659148</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>-1002303401228</t>
+          <t>-1001832880643</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>-1002889377215</t>
+          <t>-1002679523819</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>-1002795475468</t>
+          <t>-1001885408615</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>-1003007832445</t>
+          <t>-1002664729996</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>-1002092627141</t>
+          <t>-1002510217399</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>-1003595525652</t>
+          <t>-1002779291814</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>-1002750504156</t>
+          <t>-1001744426195</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>-1003016951295</t>
+          <t>-1002864485836</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>-1002679523819</t>
+          <t>-1002800020843</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>-1002832167728</t>
+          <t>-4912413878</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>-1001921955585</t>
+          <t>-1002764128440</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>-1002486834455</t>
+          <t>-1002834499433</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>-1002412562915</t>
+          <t>-1002368728861</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>-1002619556227</t>
+          <t>-1002809543928</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>-1002168855114</t>
+          <t>-1002420273008</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>-1003177115454</t>
+          <t>-1001473268532</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>-1002312125060</t>
+          <t>-1002915894807</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>-1003673597489</t>
+          <t>-1003411469233</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>-1002870201502</t>
+          <t>-1003185630550</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>-1002702621828</t>
+          <t>-1002853960198</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>-1002623818368</t>
+          <t>-1003084236608</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>-1001671470841</t>
+          <t>-1002585116909</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>-1002734752869</t>
+          <t>-1003389444837</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>-4901343480</t>
+          <t>-1002205410222</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>-1002761685886</t>
+          <t>-1003789732989</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>-1001818742779</t>
+          <t>-1002825020185</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>-1003323511757</t>
+          <t>-1003887146140</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>-1002420900028</t>
+          <t>-1002614518240</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>-1002385566540</t>
+          <t>-1002278762192</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>-1002556802461</t>
+          <t>-1003118640750</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>-1003118640750</t>
+          <t>-1002031457701</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>-4884314925</t>
+          <t>-1002422251622</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>-1002551612447</t>
+          <t>-1002522147223</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>-1002274964696</t>
+          <t>-1002866910509</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>-1001908446355</t>
+          <t>-1002719180481</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>-4877376604</t>
+          <t>-1003373308518</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>-4912413878</t>
+          <t>-1002939992790</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>-1002651996794</t>
+          <t>-1002738115577</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>-1002702518774</t>
+          <t>-1002621836135</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>-1002007016158</t>
+          <t>-1002508916910</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>-1003223517585</t>
+          <t>-1002189109599</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>-1003505125164</t>
+          <t>-1002661244330</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>-1002943877453</t>
+          <t>-1002873170822</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>-1002659291107</t>
+          <t>-1002549453056</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>-1002611045810</t>
+          <t>-1002597892903</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>-1002830324668</t>
+          <t>-4964721197</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>-1002217503260</t>
+          <t>-1002651996794</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>-1001124651563</t>
+          <t>-1003048673651</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>-1002600708556</t>
+          <t>-1002522608034</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>-1003011064222</t>
+          <t>-1003487427178</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>-1002530765960</t>
+          <t>-1002815530049</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>-1002437713625</t>
+          <t>-1003657106230</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>-1001807175468</t>
+          <t>-1002359766306</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>-1003394883155</t>
+          <t>-1003661050854</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>-1002372506024</t>
+          <t>-5276076774</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>-1002289430922</t>
+          <t>-1001261718716</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>-1002368728861</t>
+          <t>-1003445206607</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>-1001261718716</t>
+          <t>-1003205119561</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>-1002895178300</t>
+          <t>-1003093812371</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>-1002541795473</t>
+          <t>-1003234452408</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>-1002695735836</t>
+          <t>-1002260533641</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>-1002334852527</t>
+          <t>-1002760392715</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>-1001868146441</t>
+          <t>-1001543478413</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>-1002445903437</t>
+          <t>-1003587135671</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>-1002523705245</t>
+          <t>-1002016535857</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>-1002567310940</t>
+          <t>-1002520212825</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>-1002773657299</t>
+          <t>-1002209520317</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>-1002367453033</t>
+          <t>-1002144563093</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>-1002624308239</t>
+          <t>-1002840970643</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>-1002722253045</t>
+          <t>-1002321829358</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>-1002040217076</t>
+          <t>-1002887971256</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>-1003022236579</t>
+          <t>-1001946166876</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>-1002473130324</t>
+          <t>-1002530765960</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>-1001877368569</t>
+          <t>-1002591852942</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>-1002338100665</t>
+          <t>-1002632678475</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>-1003312077048</t>
+          <t>-1002377511768</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>-1003071062121</t>
+          <t>-1003759072708</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>-1002761573267</t>
+          <t>-1002130498457</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>-1002719180481</t>
+          <t>-4859108486</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>-1002778350864</t>
+          <t>-1002961757053</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>-1003756210868</t>
+          <t>-4964952099</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>-1002101571866</t>
+          <t>-1002312125060</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>-1003116317699</t>
+          <t>-1002379714369</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>-1002582659607</t>
+          <t>-1002848062475</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>-1002409528194</t>
+          <t>-1003577178993</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>-1002793180948</t>
+          <t>-1003694114079</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>-1001729071175</t>
+          <t>-1002445903437</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>-1002395833812</t>
+          <t>-1003150749086</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>-1003185630550</t>
+          <t>-1001671470841</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>-1002760607433</t>
+          <t>-1003092228217</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>-1002534699760</t>
+          <t>-4859225688</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>-1003841319365</t>
+          <t>-1003094878642</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>-1001880110164</t>
+          <t>-1002250428372</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>-1002798893729</t>
+          <t>-4162328212</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>-1003084989152</t>
+          <t>-1002974874463</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>-1002260533641</t>
+          <t>-1002359874556</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>-1002096741759</t>
+          <t>-1002659291107</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>-1002579287925</t>
+          <t>-1001307311832</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>-1002465441179</t>
+          <t>-1002593501991</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>-1002985739762</t>
+          <t>-1002340618636</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>-1002556474841</t>
+          <t>-1002288803058</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>-1002335271770</t>
+          <t>-1003451010325</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>-1002512266739</t>
+          <t>-1002793180948</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>-1001985964144</t>
+          <t>-1002983071868</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>-1002418585410</t>
+          <t>-1002974757160</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>-4863174120</t>
+          <t>-1001611710912</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>-1001635430845</t>
+          <t>-1002977896648</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>-1002321829358</t>
+          <t>-1002670277933</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>-1002155445752</t>
+          <t>-1002863926597</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>-1003500987530</t>
+          <t>-1002836592504</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>-1002616170042</t>
+          <t>-1002985739762</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>-1003048673651</t>
+          <t>-1003246680728</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>-1003307893033</t>
+          <t>-1002621241174</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>-1003373308518</t>
+          <t>-1002403581849</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>-1003036386861</t>
+          <t>-1002007016158</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>-1002769760671</t>
+          <t>-1001493770434</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>-1001818008631</t>
+          <t>-1003354035186</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>-1001406184711</t>
+          <t>-1003344556740</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>-1003882816542</t>
+          <t>-1002531829054</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>-1002209520317</t>
+          <t>-1001796760199</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>-1002647444996</t>
+          <t>-1002555387875</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>-1002710336139</t>
+          <t>-1001298208876</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>-1003888265357</t>
+          <t>-1002092120695</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>-1003057678476</t>
+          <t>-1002956645130</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>-1002956645130</t>
+          <t>-1002872579152</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>-1002271738387</t>
+          <t>-1002710336139</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>-1001946166876</t>
+          <t>-1003841319365</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>-1003520732236</t>
+          <t>-1002918117363</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>-1002850122868</t>
+          <t>-1003343499093</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>-1002808195180</t>
+          <t>-1003036386861</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>-1002870935153</t>
+          <t>-1002903801746</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>-1002880181368</t>
+          <t>-1003313884514</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>-1002403581849</t>
+          <t>-1002753235468</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>-1003509730808</t>
+          <t>-1002615496638</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>-1002560099813</t>
+          <t>-1002887675015</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>-1002234774760</t>
+          <t>-1002870201502</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>-1001543478413</t>
+          <t>-1003177115454</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>-1002760392715</t>
+          <t>-1003192981088</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>-1001817635995</t>
+          <t>-1002265393780</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>-1003227982564</t>
+          <t>-1002192798016</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>-1002268045818</t>
+          <t>-1002392635902</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>-1002420273008</t>
+          <t>-1003048077625</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>-1002340618636</t>
+          <t>-1002168855114</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>-1003653343830</t>
+          <t>-1003596125351</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>-1002706892578</t>
+          <t>-1002250659534</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>-1003689647160</t>
+          <t>-1003371546403</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>-1003352671148</t>
+          <t>-1002385566540</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>-1002870267087</t>
+          <t>-1002622011374</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>-4852298794</t>
+          <t>-1003110118065</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>-1002562282389</t>
+          <t>-1001950007498</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>-1003092984130</t>
+          <t>-1002103104897</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>-1003450809396</t>
+          <t>-1003456241208</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>-1003622694978</t>
+          <t>-1002288129210</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>-1002392635902</t>
+          <t>-4979055727</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>-1003140539585</t>
+          <t>-1003654088798</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>-1002826605956</t>
+          <t>-1002744838888</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>-1002918916933</t>
+          <t>-1001921955585</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>-1002522147223</t>
+          <t>-1003894614780</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>-4859225688</t>
+          <t>-1002651560084</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>-1003226115702</t>
+          <t>-1003739476321</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>-1002853960198</t>
+          <t>-4819895741</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>-1002522608034</t>
+          <t>-1001923225361</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>-4859108486</t>
+          <t>-1002274964696</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>-1002169700144</t>
+          <t>-1002324412075</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>-1003550392581</t>
+          <t>-1002303401228</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>-1002337769587</t>
+          <t>-1002965049763</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>-1002017152549</t>
+          <t>-1002832167728</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>-1002379714369</t>
+          <t>-1003520732236</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>-1001977703658</t>
+          <t>-1002509726671</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>-1003657106230</t>
+          <t>-1001460104025</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>-1002651560084</t>
+          <t>-1003784295528</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>-4974060502</t>
+          <t>-1002359134904</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>-4952186637</t>
+          <t>-1002880181368</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>-1002114430690</t>
+          <t>-1002798893729</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>-1003446515027</t>
+          <t>-1003601362039</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>-1002092120695</t>
+          <t>-1002795475468</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>-1003235008966</t>
+          <t>-1002073440916</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>-1003389444837</t>
+          <t>-1003563627055</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>-1002516135792</t>
+          <t>-1002761501601</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>-1002840970643</t>
+          <t>-1002367453033</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>-1002933730666</t>
+          <t>-1002918916933</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>-1001302667285</t>
+          <t>-1002916180495</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>-1003641959918</t>
+          <t>-1003654139992</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>-1001373559245</t>
+          <t>-1002452190545</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>-1001741252369</t>
+          <t>-1002761685886</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>-4925721655</t>
+          <t>-1002365212456</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>-1003313884514</t>
+          <t>-1002729517184</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>-1003054525087</t>
+          <t>-1003697183887</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>-1002895659136</t>
+          <t>-1001807175468</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>-1002071946221</t>
+          <t>-1002639728798</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>-1003035504222</t>
+          <t>-1002541795473</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>-1002457910402</t>
+          <t>-1001647712873</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>-1003141918793</t>
+          <t>-1002318473731</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>-1003596125351</t>
+          <t>-1002175510705</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>-1003502104542</t>
+          <t>-1003084989152</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>-1002359766306</t>
+          <t>-1003307893033</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>-1002309114039</t>
+          <t>-1002320283926</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>-1002887971256</t>
+          <t>-1002217503260</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>-1002901874691</t>
+          <t>-1001652492827</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>-1002508916910</t>
+          <t>-1002071946221</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>-1001212305259</t>
+          <t>-1002582926621</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>-1002728494984</t>
+          <t>-1002739724307</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>-1002793158118</t>
+          <t>-1002713471991</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>-1002393739109</t>
+          <t>-1003342714213</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>-1003217773561</t>
+          <t>-1003022236579</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>-1002990595475</t>
+          <t>-1002226982992</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>-1002593143797</t>
+          <t>-1002437713625</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>-1002532154366</t>
+          <t>-1002263664644</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>-1003690052299</t>
+          <t>-1002695735836</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>-1002582926621</t>
+          <t>-1002812268562</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>-1003234452408</t>
+          <t>-1002552125741</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>-1001546837418</t>
+          <t>-1001729071175</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>-1001701084460</t>
+          <t>-1002815867232</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>-1003395913805</t>
+          <t>-1002898563298</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>-1003553207742</t>
+          <t>-1003094634117</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>-1002300324334</t>
+          <t>-1003697454154</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>-1002454558597</t>
+          <t>-1003317755929</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>-1002815530049</t>
+          <t>-1003055362508</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>-1002423915712</t>
+          <t>-1002474339744</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>-1001652492827</t>
+          <t>-1002587384955</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>-1002776521317</t>
+          <t>-1001846329972</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>-1002957130138</t>
+          <t>-1002493291997</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>-1002683965508</t>
+          <t>-1003450809396</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>-1002579055686</t>
+          <t>-1003141918793</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>-1002587384955</t>
+          <t>-1003609759956</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>-1002566090891</t>
+          <t>-1001373559245</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>-1002879625349</t>
+          <t>-5214487805</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>-1003445206607</t>
+          <t>-1002560099813</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>-1002359134904</t>
+          <t>-1002110839951</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>-1003269892015</t>
+          <t>-1002879625349</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>-1003205119561</t>
+          <t>-1002588140799</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>-1002288803058</t>
+          <t>-1003312077048</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>-1002359874556</t>
+          <t>-1003543088788</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>-1003411536398</t>
+          <t>-1002300501716</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>-1002799861129</t>
+          <t>-1003011064222</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>-1003092228217</t>
+          <t>-1002860460728</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>-1002862636130</t>
+          <t>-1003055781840</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>-1002950443553</t>
+          <t>-1002806388271</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>-1002898563298</t>
+          <t>-1002595442276</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>-1001611710912</t>
+          <t>-1002934936335</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>-1003173900371</t>
+          <t>-1001819768369</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>-1003543088788</t>
+          <t>-1002335271770</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>-1003001093483</t>
+          <t>-1002464524981</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>-1002189109599</t>
+          <t>-1002300251125</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>-1003343499093</t>
+          <t>-1002412562915</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>-1003038352740</t>
+          <t>-1002519990156</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>-1003887146140</t>
+          <t>-1002518094653</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>-1002518094653</t>
+          <t>-5238910430</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>-1002634221315</t>
+          <t>-1002077075261</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>-1001885408615</t>
+          <t>-1002870267087</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>-1002177327820</t>
+          <t>-1003811694462</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>-1002872579152</t>
+          <t>-4852298794</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>-1002377976370</t>
+          <t>-1001730809010</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>-1002531829054</t>
+          <t>-4863520102</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>-1002983071868</t>
+          <t>-1003177468537</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>-1002927005745</t>
+          <t>-1003030011311</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>-1002744838888</t>
+          <t>-1002702621828</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>-1001460104025</t>
+          <t>-1002754377559</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>-1002077075261</t>
+          <t>-1003057678476</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>-1002190969931</t>
+          <t>-1002416638992</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>-1002621836135</t>
+          <t>-1002040217076</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>-1003609759956</t>
+          <t>-1002096741759</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>-1001668927089</t>
+          <t>-1002706892578</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>-1002815867232</t>
+          <t>-4901343480</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>-1002322838597</t>
+          <t>-1002950443553</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>-1002729517184</t>
+          <t>-1002600708556</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>-1002016535857</t>
+          <t>-1003352103344</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>-1002908266830</t>
+          <t>-1002418585410</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>-1002832898246</t>
+          <t>-1003226115702</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>-1003601362039</t>
+          <t>-1002730203883</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>-1002518146543</t>
+          <t>-1002074104758</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>-1003030011311</t>
+          <t>-1003635435133</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>-1002915894807</t>
+          <t>-1002342989207</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>-1002509726671</t>
+          <t>-1002457910402</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>-1003150749086</t>
+          <t>-1002170512400</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>-1002342989207</t>
+          <t>-1003560349248</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>-4162328212</t>
+          <t>-1002551612447</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>-1002580159815</t>
+          <t>-1002722253045</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>-1002738115577</t>
+          <t>-1003830260747</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>-1002764128440</t>
+          <t>-1002956133115</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>-1003784295528</t>
+          <t>-1002808195180</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>-1003094443944</t>
+          <t>-1002428009204</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>-1002753083965</t>
+          <t>-1002409528194</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>-1003371546403</t>
+          <t>-4822189866</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>-1002834499433</t>
+          <t>-1002813643590</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>-1002916180495</t>
+          <t>-4952186637</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>-1003180215428</t>
+          <t>-1002562282389</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>-1001859766402</t>
+          <t>-1003485367302</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>-1002540598427</t>
+          <t>-1002799861129</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>-1002977896648</t>
+          <t>-1001859766402</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>-1003462101210</t>
+          <t>-1003888265357</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>-1003694114079</t>
+          <t>-1002169700144</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>-4979055727</t>
+          <t>-1002793158118</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>-1002651012796</t>
+          <t>-1003035504222</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>-4562050705</t>
+          <t>-1003227982564</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>-1002618584679</t>
+          <t>-1003421411518</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>-1002250659534</t>
+          <t>-1002860463322</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>-1002872770022</t>
+          <t>-1003622694978</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>-1003094634117</t>
+          <t>-1002624308239</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>-1002414175598</t>
+          <t>-1002448038408</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>-1003411469233</t>
+          <t>-1003417970722</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>-1002684891199</t>
+          <t>-1002683965508</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>-1002661244330</t>
+          <t>-1002309114039</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>-1003030066020</t>
+          <t>-1002753083965</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>-1001307311832</t>
+          <t>-1001977703658</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>-1002509299058</t>
+          <t>-1002957130138</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>-1001493770434</t>
+          <t>-1002647444996</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>-1002614518240</t>
+          <t>-1003066477129</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>-1002532871843</t>
+          <t>-1002809610954</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>-1002866910509</t>
+          <t>-1002872771874</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>-1002640591890</t>
+          <t>-1002114430690</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>-1002965049763</t>
+          <t>-1003090299188</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>-1002544966984</t>
+          <t>-1002092627141</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>-1003048077625</t>
+          <t>-1003756210868</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>-5214487805</t>
+          <t>-1002423915712</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>-1002825020185</t>
+          <t>-1003593024986</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>-1002422251622</t>
+          <t>-1002593143797</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>-4921455900</t>
+          <t>-1003583886956</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>-1002192798016</t>
+          <t>-1001467801859</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>-1001929868118</t>
+          <t>-1001818742779</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>-1002073440916</t>
+          <t>-1003207138530</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>-1002595442276</t>
+          <t>-1002778350864</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>-1003587135671</t>
+          <t>-1002419890323</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>-1002588140799</t>
+          <t>-1002255365525</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>-1001730809010</t>
+          <t>-1002623818368</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>-1001900924039</t>
+          <t>-1003395913805</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>-4989200624</t>
+          <t>-1003810708157</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>-1002555387875</t>
+          <t>-1003092984130</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>-1002812268562</t>
+          <t>-1002702700644</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>-1002773230946</t>
+          <t>-1003001093483</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>-1003344556740</t>
+          <t>-1002579055686</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>-1002346159781</t>
+          <t>-1003650931988</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>-1003661050854</t>
+          <t>-1002190969931</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>-1002549453056</t>
+          <t>-1002658418497</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>-1002782716052</t>
+          <t>-1002514951234</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>-1002278762192</t>
+          <t>-1002420900028</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>-1002342685523</t>
+          <t>-1003070751342</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>-1001950007498</t>
+          <t>-1002534699760</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>-1002999961089</t>
+          <t>-1002532871843</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>-1003654088798</t>
+          <t>-1002101571866</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>-1002832174643</t>
+          <t>-4921455900</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>-1002464524981</t>
+          <t>-1002415992686</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>-1002250428372</t>
+          <t>-1003038352740</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>-1002600128976</t>
+          <t>-1002773657299</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>-1002438767403</t>
+          <t>-1002395833812</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>-1001765476229</t>
+          <t>-1003509730808</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>-1002864485836</t>
+          <t>-1002908266830</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>-1003055719997</t>
+          <t>-1003778480564</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>-1003563627055</t>
+          <t>-1002300324334</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>-1002581029977</t>
+          <t>-1002320967880</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>-1002531024619</t>
+          <t>-4941172345</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>-1002873170822</t>
+          <t>-1001817635995</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>-1002887675015</t>
+          <t>-1002776521317</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>-1002713471991</t>
+          <t>-1002715650097</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>-1002747623711</t>
+          <t>-1002486834455</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>-1002170512400</t>
+          <t>-1002611045810</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>-1002287067426</t>
+          <t>-1003030066020</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>-1002918117363</t>
+          <t>-1002618584679</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>-1001744426195</t>
+          <t>-1002334852527</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>-1002159603263</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>-1001765476229</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>-1002388609283</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>-1002234774760</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>-4925721655</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>-1002761573267</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>-1002830324668</t>
         </is>
       </c>
     </row>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A520"/>
+  <dimension ref="A1:A631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,980 +438,980 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-1002927005745</t>
+          <t>-1001846329972</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-4989200624</t>
+          <t>-1003312077048</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-1003462101210</t>
+          <t>-1002445903437</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-1001900924039</t>
+          <t>-1002493291997</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>-1003131016214</t>
+          <t>-1001730809010</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-1001929868118</t>
+          <t>-1002144563093</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-1003690052299</t>
+          <t>-1003596125351</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-1002540598427</t>
+          <t>-1002679523819</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>-1002516135792</t>
+          <t>-1003462101210</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>-1002532154366</t>
+          <t>-1002016912929</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>-1003642398244</t>
+          <t>-1002793180948</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>-1001701084460</t>
+          <t>-1002359874556</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>-1001818008631</t>
+          <t>-1002918117363</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>-1002579287925</t>
+          <t>-1003798585147</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>-1002465441179</t>
+          <t>-1002486834455</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>-1001546837418</t>
+          <t>-1002974874463</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>-1002046646497</t>
+          <t>-1001817635995</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>-1002870935153</t>
+          <t>-1002660309633</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>-1002680979996</t>
+          <t>-1003661050854</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>-1003389986244</t>
+          <t>-1002518556633</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>-1002523705245</t>
+          <t>-1002474339744</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>-1002728494984</t>
+          <t>-1003577178993</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>-1002473130324</t>
+          <t>-1002651012796</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>-1002518556633</t>
+          <t>-1002379714369</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>-1002750504156</t>
+          <t>-1002744838888</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>-1002372506024</t>
+          <t>-1003150223688</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>-1001668927089</t>
+          <t>-1003456241208</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>-4961873359</t>
+          <t>-1002621836135</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>-1001801324223</t>
+          <t>-1003447123747</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>-1002152254687</t>
+          <t>-1001671470841</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>-1001868146441</t>
+          <t>-1002879625349</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>-1002571339758</t>
+          <t>-1003055362508</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>-1002727925450</t>
+          <t>-1002168855114</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>-1003045110726</t>
+          <t>-1002101571866</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>-1002237965843</t>
+          <t>-1002918916933</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-1003505125164</t>
+          <t>-1003560349248</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>-1001741252369</t>
+          <t>-1002588140799</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>-1002338100665</t>
+          <t>-1002420273008</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>-1002368488534</t>
+          <t>-1003689644532</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>-1002769760671</t>
+          <t>-1002342989207</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>-1002684891199</t>
+          <t>-1002830324668</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>-1003483467807</t>
+          <t>-1002600128976</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>-1003144692446</t>
+          <t>-1003654088798</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>-1002288363987</t>
+          <t>-1002624308239</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>-1002580159815</t>
+          <t>-1002659587443</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>-1003323511757</t>
+          <t>-1002092627141</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>-1002778085921</t>
+          <t>-1002809543928</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>-1003217773561</t>
+          <t>-1002638064433</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>-1003795984362</t>
+          <t>-1002167448908</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>-1002582659607</t>
+          <t>-1003304830106</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>-1002832898246</t>
+          <t>-1002346159781</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>-1003364207368</t>
+          <t>-1002418585410</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>-1003055719997</t>
+          <t>-1002562282389</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>-1001908446355</t>
+          <t>-1003744707157</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>-1002998185557</t>
+          <t>-1002977896648</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>-4977264275</t>
+          <t>-1002297618669</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>-1002482355272</t>
+          <t>-1003122716300</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>-1001922808139</t>
+          <t>-1003150749086</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>-1001390053729</t>
+          <t>-1002760392715</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>-1003129624230</t>
+          <t>-1003205119561</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>-1003653343830</t>
+          <t>-1002706892578</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>-1002895659136</t>
+          <t>-1002534699760</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>-1003550392581</t>
+          <t>-1003389986244</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>-1003116317699</t>
+          <t>-1002999961089</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>-4636171342</t>
+          <t>-1002640591890</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>-1002600128976</t>
+          <t>-1002114430690</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>-1001406184711</t>
+          <t>-1002522608034</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>-1002556802461</t>
+          <t>-1002412562915</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>-1001877368569</t>
+          <t>-1003673427063</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>-1001302667285</t>
+          <t>-1001868146441</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>-1002455033621</t>
+          <t>-1003093812371</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>-1001994788372</t>
+          <t>-1003543088788</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>-1002651012796</t>
+          <t>-1003170688242</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>-1002845355669</t>
+          <t>-5176841635</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>-1002616170042</t>
+          <t>-1002320967880</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>-1003650147257</t>
+          <t>-5214487805</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>-4884314925</t>
+          <t>-1003116317699</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>-1002268045818</t>
+          <t>-1002170512400</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>-4863174120</t>
+          <t>-1001212305259</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>-1002581029977</t>
+          <t>-1002531829054</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>-1002529665437</t>
+          <t>-1003554106710</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>-1002575818224</t>
+          <t>-1003217773561</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>-1001124651563</t>
+          <t>-1002848062475</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>-1003002359598</t>
+          <t>-1003719969742</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>-1002566090891</t>
+          <t>-1003841442683</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>-1002904756274</t>
+          <t>-1001744426195</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>-1003150223688</t>
+          <t>-1002192798016</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>-1003046279469</t>
+          <t>-1003776273822</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>-1002702518774</t>
+          <t>-1002898563298</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>-1003140539585</t>
+          <t>-1002571101349</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>-1002512266739</t>
+          <t>-1002368488534</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>-1002881849916</t>
+          <t>-1003011064222</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>-4562050705</t>
+          <t>-5264614378</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>-1002377976370</t>
+          <t>-1003027038967</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>-1002978401429</t>
+          <t>-1002866910509</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>-1002531024619</t>
+          <t>-5276076774</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>-1003411536398</t>
+          <t>-1002903801746</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>-1002509299058</t>
+          <t>-1001921955585</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>-1003595525652</t>
+          <t>-1001665462509</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>-1002760607433</t>
+          <t>-1002368728861</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>-1002391001829</t>
+          <t>-1003364207368</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>-1003559602288</t>
+          <t>-1002455033621</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>-1002782716052</t>
+          <t>-1002778085921</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>-1002619556227</t>
+          <t>-1003795984362</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>-1002999961089</t>
+          <t>-1002110839951</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>-1001212305259</t>
+          <t>-1002250659534</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>-1002289430922</t>
+          <t>-4912413878</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>-1001449424790</t>
+          <t>-1003784295528</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>-1002414175598</t>
+          <t>-1002934936335</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>-1002990595475</t>
+          <t>-1002651560084</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>-1002889377215</t>
+          <t>-1002209520317</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>-1002271738387</t>
+          <t>-1002556802461</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>-1002567310940</t>
+          <t>-1002415992686</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>-1002850122868</t>
+          <t>-1002448038408</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>-1003180215428</t>
+          <t>-1002864485836</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>-1001635430845</t>
+          <t>-1002730203883</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>-1003576952118</t>
+          <t>-1002514951234</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>-1001946318041</t>
+          <t>-1002753235468</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>-1003518656172</t>
+          <t>-1002860460728</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>-1003254448559</t>
+          <t>-1002621241174</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>-1001596465392</t>
+          <t>-1003317755929</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>-1001985964144</t>
+          <t>-1002338100665</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>-1002342685523</t>
+          <t>-1002159603263</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>-1002315372056</t>
+          <t>-1003502104542</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>-1002734752869</t>
+          <t>-1001877368569</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>-1002862636130</t>
+          <t>-1003865487649</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>-1002640591890</t>
+          <t>-1002391001829</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>-1003882816542</t>
+          <t>-4162328212</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>-1002872770022</t>
+          <t>-1001908446355</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>-1003857994445</t>
+          <t>-1002832174643</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>-4974060502</t>
+          <t>-1003313884514</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>-1002822883977</t>
+          <t>-1002880181368</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>-1002346159781</t>
+          <t>-1003777534388</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>-1003527335437</t>
+          <t>-1002703131951</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>-1002832174643</t>
+          <t>-1002478485922</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>-1003007832445</t>
+          <t>-1002750504156</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>-1003100265374</t>
+          <t>-1002870201502</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>-1002016912929</t>
+          <t>-1003777385076</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>-1002659587443</t>
+          <t>-1002773657299</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>-1002901874691</t>
+          <t>-1001929868118</t>
         </is>
       </c>
     </row>
@@ -1425,2646 +1425,3423 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>-1001735560772</t>
+          <t>-1003131016214</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>-1002393739109</t>
+          <t>-4852298794</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>-1002826605956</t>
+          <t>-1002457910402</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>-1003078207757</t>
+          <t>-1002579055686</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>-1002747623711</t>
+          <t>-1003628737566</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>-1003641959918</t>
+          <t>-1003149481043</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>-1002454558597</t>
+          <t>-1003169930553</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>-1002322838597</t>
+          <t>-1003453389134</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>-1002933730666</t>
+          <t>-1002548868785</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>-4877376604</t>
+          <t>-5238910430</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>-1003502104542</t>
+          <t>-1002040217076</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>-1002809659148</t>
+          <t>-1003055719997</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>-1001832880643</t>
+          <t>-1003411310989</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>-1002679523819</t>
+          <t>-1002591852942</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>-1001885408615</t>
+          <t>-1001543478413</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>-1002664729996</t>
+          <t>-1003094634117</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>-1002510217399</t>
+          <t>-1002278564823</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>-1002779291814</t>
+          <t>-1003587135671</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>-1001744426195</t>
+          <t>-4989200624</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>-1002864485836</t>
+          <t>-1002710336139</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>-1002800020843</t>
+          <t>-1003342714213</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>-4912413878</t>
+          <t>-1002950443553</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>-1002764128440</t>
+          <t>-1003293940909</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>-1002834499433</t>
+          <t>-1003289156239</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>-1002368728861</t>
+          <t>-1002715650097</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>-1002809543928</t>
+          <t>-1003102873353</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>-1002420273008</t>
+          <t>-1002342685523</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>-1001473268532</t>
+          <t>-1003739043411</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>-1002915894807</t>
+          <t>-1002077075261</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>-1003411469233</t>
+          <t>-1001493770434</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>-1003185630550</t>
+          <t>-1002288363987</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>-1002853960198</t>
+          <t>-1001647712873</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>-1003084236608</t>
+          <t>-5182817479</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>-1002585116909</t>
+          <t>-1002318473731</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>-1003389444837</t>
+          <t>-4877376604</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>-1002205410222</t>
+          <t>-1002423915712</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>-1003789732989</t>
+          <t>-1002658418497</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>-1002825020185</t>
+          <t>-1001261718716</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>-1003887146140</t>
+          <t>-1001922808139</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>-1002614518240</t>
+          <t>-1002352486010</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>-1002278762192</t>
+          <t>-1002552125741</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>-1003118640750</t>
+          <t>-1003344556740</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>-1002031457701</t>
+          <t>-1002367453033</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>-1002422251622</t>
+          <t>-1002300324334</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>-1002522147223</t>
+          <t>-1002870267087</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>-1002866910509</t>
+          <t>-1003207138530</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>-1002719180481</t>
+          <t>-1002695735836</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>-1003373308518</t>
+          <t>-1002586036097</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>-1002939992790</t>
+          <t>-1002734752869</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>-1002738115577</t>
+          <t>-1002872770022</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>-1002621836135</t>
+          <t>-1002974757160</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>-1002508916910</t>
+          <t>-1003084989152</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>-1002189109599</t>
+          <t>-1003759164664</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>-1002661244330</t>
+          <t>-1002529665437</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>-1002873170822</t>
+          <t>-1002832167728</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>-1002549453056</t>
+          <t>-1001818008631</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>-1002597892903</t>
+          <t>-1001985964144</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>-4964721197</t>
+          <t>-1003527335437</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>-1002651996794</t>
+          <t>-1002011515239</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>-1003048673651</t>
+          <t>-1003560358780</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>-1002522608034</t>
+          <t>-1002118631320</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>-1003487427178</t>
+          <t>-1002300501716</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>-1002815530049</t>
+          <t>-1002702700644</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>-1003657106230</t>
+          <t>-1003415576816</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>-1002359766306</t>
+          <t>-1002719180481</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>-1003661050854</t>
+          <t>-1001611710912</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>-5276076774</t>
+          <t>-4941172345</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>-1001261718716</t>
+          <t>-1002281112145</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>-1003445206607</t>
+          <t>-1001373559245</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>-1003205119561</t>
+          <t>-1002092120695</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>-1003093812371</t>
+          <t>-1002263664644</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>-1003234452408</t>
+          <t>-1002622011374</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>-1002260533641</t>
+          <t>-1001674602550</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>-1002760392715</t>
+          <t>-1002540598427</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>-1001543478413</t>
+          <t>-1002509299058</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>-1003587135671</t>
+          <t>-1003094878642</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>-1002016535857</t>
+          <t>-1003395913805</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>-1002520212825</t>
+          <t>-1002096741759</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>-1002209520317</t>
+          <t>-1002901874691</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>-1002144563093</t>
+          <t>-1002764128440</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>-1002840970643</t>
+          <t>-1002579287925</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>-1002321829358</t>
+          <t>-1003601362039</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>-1002887971256</t>
+          <t>-1002904756274</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>-1001946166876</t>
+          <t>-1003111708855</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>-1002530765960</t>
+          <t>-1002031457701</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>-1002591852942</t>
+          <t>-1001390053729</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>-1002632678475</t>
+          <t>-4863520102</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>-1002377511768</t>
+          <t>-1001735560772</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>-1003759072708</t>
+          <t>-1001741252369</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>-1002130498457</t>
+          <t>-1003878903675</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>-4859108486</t>
+          <t>-1002840970643</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>-1002961757053</t>
+          <t>-1001473268532</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>-4964952099</t>
+          <t>-1002071946221</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>-1002312125060</t>
+          <t>-1003025068781</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>-1002379714369</t>
+          <t>-1003845773021</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>-1002848062475</t>
+          <t>-1003001093483</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>-1003577178993</t>
+          <t>-1002551612447</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>-1003694114079</t>
+          <t>-1003520732236</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>-1002445903437</t>
+          <t>-1002799861129</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>-1003150749086</t>
+          <t>-1002887971256</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>-1001671470841</t>
+          <t>-1003451010325</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>-1003092228217</t>
+          <t>-1002809610954</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>-4859225688</t>
+          <t>-1002560099813</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>-1003094878642</t>
+          <t>-1002520212825</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>-1002250428372</t>
+          <t>-1003888265357</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>-4162328212</t>
+          <t>-1003856867815</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>-1002974874463</t>
+          <t>-1002531024619</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>-1002359874556</t>
+          <t>-1002739724307</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>-1002659291107</t>
+          <t>-1003177115454</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>-1001307311832</t>
+          <t>-1002388609283</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>-1002593501991</t>
+          <t>-1002395833812</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>-1002340618636</t>
+          <t>-1002519990156</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>-1002288803058</t>
+          <t>-1001885408615</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>-1003451010325</t>
+          <t>-1003234452408</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>-1002793180948</t>
+          <t>-1002074104758</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>-1002983071868</t>
+          <t>-1003864264998</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>-1002974757160</t>
+          <t>-1002322838597</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>-1001611710912</t>
+          <t>-1002664729996</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>-1002977896648</t>
+          <t>-4974060502</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>-1002670277933</t>
+          <t>-1003811694462</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>-1002863926597</t>
+          <t>-1002815867232</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>-1002836592504</t>
+          <t>-1003759072708</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>-1002985739762</t>
+          <t>-1002873170822</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>-1003246680728</t>
+          <t>-1003301419264</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>-1002621241174</t>
+          <t>-1003293930657</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>-1002403581849</t>
+          <t>-1003790209592</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>-1002007016158</t>
+          <t>-1003500481482</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>-1001493770434</t>
+          <t>-1002744387247</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>-1003354035186</t>
+          <t>-1002532154366</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>-1003344556740</t>
+          <t>-1002614518240</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>-1002531829054</t>
+          <t>-1001449424790</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>-1001796760199</t>
+          <t>-1003192981088</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>-1002555387875</t>
+          <t>-1002822883977</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>-1001298208876</t>
+          <t>-1002728494984</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>-1002092120695</t>
+          <t>-1003180215428</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>-1002956645130</t>
+          <t>-1002990734165</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>-1002872579152</t>
+          <t>-1002516135792</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>-1002710336139</t>
+          <t>-1001460104025</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>-1003841319365</t>
+          <t>-1003755868331</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>-1002918117363</t>
+          <t>-1003609759956</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>-1003343499093</t>
+          <t>-1002250428372</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>-1003036386861</t>
+          <t>-1003882816542</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>-1002903801746</t>
+          <t>-1002508916910</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>-1003313884514</t>
+          <t>-1003092228217</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>-1002753235468</t>
+          <t>-1003239240721</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>-1002615496638</t>
+          <t>-1002106096413</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>-1002887675015</t>
+          <t>-4884314925</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>-1002870201502</t>
+          <t>-1002747623711</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>-1003177115454</t>
+          <t>-1002815530049</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>-1003192981088</t>
+          <t>-1003848351434</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>-1002265393780</t>
+          <t>-1002760607433</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>-1002192798016</t>
+          <t>-1002615496638</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>-1002392635902</t>
+          <t>-1002464524981</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>-1003048077625</t>
+          <t>-1003022236579</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>-1002168855114</t>
+          <t>6786983715</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>-1003596125351</t>
+          <t>-1003048673651</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>-1002250659534</t>
+          <t>-1003887146140</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>-1003371546403</t>
+          <t>-1003485367302</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>-1002385566540</t>
+          <t>-1002860463322</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>-1002622011374</t>
+          <t>-1003585578699</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>-1003110118065</t>
+          <t>-1002659291107</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>-1001950007498</t>
+          <t>-1003483467807</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>-1002103104897</t>
+          <t>-1002377511768</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>-1003456241208</t>
+          <t>-1002268045818</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>-1002288129210</t>
+          <t>-1003613698828</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>-4979055727</t>
+          <t>6667684577</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>-1003654088798</t>
+          <t>-1003805893950</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>-1002744838888</t>
+          <t>-1003844657847</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>-1001921955585</t>
+          <t>-1003701419543</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>-1003894614780</t>
+          <t>-1003503147352</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>-1002651560084</t>
+          <t>-1002927005745</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>-1003739476321</t>
+          <t>-1003118640750</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>-4819895741</t>
+          <t>-1001302667285</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>-1001923225361</t>
+          <t>-1002785625174</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>-1002274964696</t>
+          <t>-1003518656172</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>-1002324412075</t>
+          <t>-1002776521317</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>-1002303401228</t>
+          <t>-1002178056369</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>-1002965049763</t>
+          <t>-1003645590334</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>-1002832167728</t>
+          <t>-1001796760199</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>-1003520732236</t>
+          <t>-1002983071868</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>-1002509726671</t>
+          <t>-1002881849916</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>-1001460104025</t>
+          <t>-1002800020843</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>-1003784295528</t>
+          <t>-1002956645130</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>-1002359134904</t>
+          <t>-1002234774760</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>-1002880181368</t>
+          <t>-1003697183887</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>-1002798893729</t>
+          <t>-1003666715930</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>-1003601362039</t>
+          <t>-1002850122868</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>-1002795475468</t>
+          <t>-4961873359</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>-1002073440916</t>
+          <t>-1002414175598</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>-1003563627055</t>
+          <t>-1002632678475</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>-1002761501601</t>
+          <t>-1002320283926</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>-1002367453033</t>
+          <t>-1002365212456</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>-1002918916933</t>
+          <t>-4822189866</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>-1002916180495</t>
+          <t>-1003605325965</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>-1003654139992</t>
+          <t>-1002566090891</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>-1002452190545</t>
+          <t>-1003697454154</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>-1002761685886</t>
+          <t>-1002509726671</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>-1002365212456</t>
+          <t>-1003810708157</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>-1002729517184</t>
+          <t>-1002761573267</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>-1003697183887</t>
+          <t>-1003092984130</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>-1001807175468</t>
+          <t>-1003509730808</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>-1002639728798</t>
+          <t>-1002549453056</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>-1002541795473</t>
+          <t>-1003870585071</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>-1001647712873</t>
+          <t>-1003144692446</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>-1002318473731</t>
+          <t>-5181397583</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>-1002175510705</t>
+          <t>-1003505125164</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>-1003084989152</t>
+          <t>-1001406184711</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>-1003307893033</t>
+          <t>-1003657106230</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>-1002320283926</t>
+          <t>-1002360283286</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>-1002217503260</t>
+          <t>-1002595442276</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>-1001652492827</t>
+          <t>-1003070751342</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>-1002071946221</t>
+          <t>-1002419890323</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>-1002582926621</t>
+          <t>-1002729517184</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>-1002739724307</t>
+          <t>-1001357883446</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>-1002713471991</t>
+          <t>-1003407475393</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>-1003342714213</t>
+          <t>-1002046646497</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>-1003022236579</t>
+          <t>-1003078207757</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>-1002226982992</t>
+          <t>-5293053713</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>-1002437713625</t>
+          <t>-1002377976370</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>-1002263664644</t>
+          <t>-1003371546403</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>-1002695735836</t>
+          <t>-1003374632792</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>-1002812268562</t>
+          <t>-1002826605956</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>-1002552125741</t>
+          <t>-4901343480</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>-1001729071175</t>
+          <t>-1001668927089</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>-1002815867232</t>
+          <t>-1002998185557</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>-1002898563298</t>
+          <t>-1002872579152</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>-1003094634117</t>
+          <t>-1002978401429</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>-1003697454154</t>
+          <t>-1002782716052</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>-1003317755929</t>
+          <t>-4921455900</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>-1003055362508</t>
+          <t>-1001832880643</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>-1002474339744</t>
+          <t>-1003857994445</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>-1002587384955</t>
+          <t>-4964952099</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>-1001846329972</t>
+          <t>-1002237965843</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>-1002493291997</t>
+          <t>-1002600708556</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>-1003450809396</t>
+          <t>-1002073440916</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>-1003141918793</t>
+          <t>-1003229025294</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>-1003609759956</t>
+          <t>-1003354035186</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>-1001373559245</t>
+          <t>-1002808195180</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>-5214487805</t>
+          <t>-1002274964696</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>-1002560099813</t>
+          <t>-1002217503260</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>-1002110839951</t>
+          <t>-1002778457560</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>-1002879625349</t>
+          <t>-1002324412075</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>-1002588140799</t>
+          <t>-1001950007498</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>-1003312077048</t>
+          <t>-1003624752221</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>-1003543088788</t>
+          <t>-1003579299494</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>-1002300501716</t>
+          <t>-1003789732989</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>-1003011064222</t>
+          <t>-1002683965508</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>-1002860460728</t>
+          <t>-1003666795395</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>-1003055781840</t>
+          <t>-1003650147257</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>-1002806388271</t>
+          <t>-5114003285</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>-1002595442276</t>
+          <t>-1003411469233</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>-1002934936335</t>
+          <t>-1003739476321</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>-1001819768369</t>
+          <t>-1003694114079</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>-1002335271770</t>
+          <t>-1003007832445</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>-1002464524981</t>
+          <t>-1002597892903</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>-1002300251125</t>
+          <t>-1002016535857</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>-1002412562915</t>
+          <t>-1002359766306</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>-1002519990156</t>
+          <t>-1002103104897</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>-1002518094653</t>
+          <t>-1002738115577</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>-5238910430</t>
+          <t>-1001546837418</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>-1002077075261</t>
+          <t>-4819895741</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>-1002870267087</t>
+          <t>-1002437713625</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>-1003811694462</t>
+          <t>-1002321829358</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>-4852298794</t>
+          <t>-1003583886956</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>-1001730809010</t>
+          <t>-1002606190918</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>-4863520102</t>
+          <t>-1001819768369</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>-1003177468537</t>
+          <t>-1002618584679</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>-1003030011311</t>
+          <t>-1002150947419</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>-1002702621828</t>
+          <t>-1002393739109</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>-1002754377559</t>
+          <t>-1003615692664</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>-1003057678476</t>
+          <t>-1002189109599</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>-1002416638992</t>
+          <t>-1002512266739</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>-1002040217076</t>
+          <t>-1002312125060</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>-1002096741759</t>
+          <t>-1001923225361</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>-1002706892578</t>
+          <t>-1003035504222</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>-4901343480</t>
+          <t>-1003307893033</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>-1002950443553</t>
+          <t>-1003785529820</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>-1002600708556</t>
+          <t>-1002769760671</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>-1003352103344</t>
+          <t>-1003461246398</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>-1002418585410</t>
+          <t>-1003897294884</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>-1003226115702</t>
+          <t>8002682623</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>-1002730203883</t>
+          <t>-4513511178</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>-1002074104758</t>
+          <t>-4859108486</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>-1003635435133</t>
+          <t>-1002753083965</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>-1002342989207</t>
+          <t>-1002392635902</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>-1002457910402</t>
+          <t>-1003778480564</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>-1002170512400</t>
+          <t>-1002754377559</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>-1003560349248</t>
+          <t>-1003595525652</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>-1002551612447</t>
+          <t>-1003576952118</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>-1002722253045</t>
+          <t>-1002555387875</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>-1003830260747</t>
+          <t>-1003822471010</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>-1002956133115</t>
+          <t>-1003373308518</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>-1002808195180</t>
+          <t>-1002832898246</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>-1002428009204</t>
+          <t>-1001701084460</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>-1002409528194</t>
+          <t>-1002522147223</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>-4822189866</t>
+          <t>-1002580159815</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>-1002813643590</t>
+          <t>-1002712833331</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>-4952186637</t>
+          <t>-1002616170042</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>-1002562282389</t>
+          <t>-4964721197</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>-1003485367302</t>
+          <t>-1003737369393</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>-1002799861129</t>
+          <t>-1003227982564</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>-1001859766402</t>
+          <t>-1002491853737</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>-1003888265357</t>
+          <t>-1003780172654</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>-1002169700144</t>
+          <t>-1003550392581</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>-1002793158118</t>
+          <t>-1003558199964</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>-1003035504222</t>
+          <t>-1002335271770</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>-1003227982564</t>
+          <t>-1003183253419</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>-1003421411518</t>
+          <t>-1002895659136</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>-1002860463322</t>
+          <t>-1002422251622</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>-1003622694978</t>
+          <t>-1001807175468</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>-1002624308239</t>
+          <t>-1003460209587</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>-1002448038408</t>
+          <t>-1003323511757</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>-1003417970722</t>
+          <t>-1003421411518</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>-1002683965508</t>
+          <t>-1003487427178</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>-1002309114039</t>
+          <t>-1002205410222</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>-1002753083965</t>
+          <t>-1003870720812</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>-1001977703658</t>
+          <t>-1003055781840</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>-1002957130138</t>
+          <t>-1002651996794</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>-1002647444996</t>
+          <t>-1003622904170</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>-1003066477129</t>
+          <t>-1002271738387</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>-1002809610954</t>
+          <t>-1003343499093</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>-1002872771874</t>
+          <t>-1003702625153</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>-1002114430690</t>
+          <t>-1002567310940</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>-1003090299188</t>
+          <t>-1001994788372</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>-1002092627141</t>
+          <t>-5212914594</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>-1003756210868</t>
+          <t>-1002420900028</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>-1002423915712</t>
+          <t>-1002949588128</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>-1003593024986</t>
+          <t>-1003129624230</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>-1002593143797</t>
+          <t>-4952186637</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>-1003583886956</t>
+          <t>-1002403581849</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>-1001467801859</t>
+          <t>-1003671208187</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>-1001818742779</t>
+          <t>-1003057678476</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>-1003207138530</t>
+          <t>-1002761501601</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>-1002778350864</t>
+          <t>-1002473130324</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>-1002419890323</t>
+          <t>-4636171342</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>-1002255365525</t>
+          <t>-1002611045810</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>-1002623818368</t>
+          <t>-1002639728798</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>-1003395913805</t>
+          <t>-1002809659148</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>-1003810708157</t>
+          <t>-1002334852527</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>-1003092984130</t>
+          <t>-1002372506024</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>-1002702700644</t>
+          <t>-1001946166876</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>-1003001093483</t>
+          <t>-1002593501991</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>-1002579055686</t>
+          <t>-1002870935153</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>-1003650931988</t>
+          <t>-1003858324278</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>-1002190969931</t>
+          <t>-1002887675015</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>-1002658418497</t>
+          <t>-1001540741017</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>-1002514951234</t>
+          <t>-1001635430845</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>-1002420900028</t>
+          <t>-1003110118065</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>-1003070751342</t>
+          <t>-1003141918793</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>-1002534699760</t>
+          <t>-1002872771874</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>-1002532871843</t>
+          <t>-1003254448559</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>-1002101571866</t>
+          <t>-1002152254687</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>-4921455900</t>
+          <t>-1001652492827</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>-1002415992686</t>
+          <t>-1003055472631</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>-1003038352740</t>
+          <t>-1003756210868</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>-1002773657299</t>
+          <t>-1003417970722</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>-1002395833812</t>
+          <t>-5231222732</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>-1003509730808</t>
+          <t>-1002985739762</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>-1002908266830</t>
+          <t>-1001859766402</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>-1003778480564</t>
+          <t>-1003690052299</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>-1002300324334</t>
+          <t>-1002169700144</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>-1002320967880</t>
+          <t>-1002825020185</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>-4941172345</t>
+          <t>-1002571339758</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>-1001817635995</t>
+          <t>-1002226982992</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>-1002776521317</t>
+          <t>-1002670277933</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>-1002715650097</t>
+          <t>-1002990595475</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>-1002486834455</t>
+          <t>-1002593143797</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>-1002611045810</t>
+          <t>-1001307311832</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>-1003030066020</t>
+          <t>-1003038352740</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>-1002618584679</t>
+          <t>-1002385566540</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>-1002334852527</t>
+          <t>-1003635435133</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>-1002159603263</t>
+          <t>-1002813643590</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>-1001765476229</t>
+          <t>-1003382157325</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>-1002388609283</t>
+          <t>-1002722253045</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>-1002234774760</t>
+          <t>-1002647444996</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>-4925721655</t>
+          <t>-1002834499433</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>-1002761573267</t>
+          <t>-1002727925450</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>-1002830324668</t>
+          <t>-1002862636130</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>-1003881956622</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>-1001765476229</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>-1002530765960</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>-1003185630550</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>-1003445206607</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>-1002965049763</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>-1002779291814</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>-1002582926621</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>-1003568455790</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>-1001298208876</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>-1001900924039</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>-1003650931988</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>-4925721655</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>-1003002359598</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>-1002465441179</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>-1002523705245</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>-1003105061815</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>-1003556812442</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>-1002582659607</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>-1003654139992</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>-1002778350864</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>-1003559602288</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>-1003770148368</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>-1002265393780</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>-1002812268562</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>-1002416638992</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>-1002587384955</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>-1001801324223</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>-1002518094653</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>-1003622694978</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>-1003554414722</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>-1002130498457</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>-1002510217399</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>-1002175510705</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>-1002360094196</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>-4562050705</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>-1002482355272</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>-1002303401228</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>-1002915894807</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>-1003839394701</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>-1003100265374</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>-1003894614780</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>-1002947162126</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>-1002772423367</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>-4977264275</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>-1002289430922</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>-1003048077625</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>-1002957130138</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>-1001467801859</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>-1002278762192</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>-1002908266830</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>-1002551279375</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>-1003030066020</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>-1003646802065</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>-1002340618636</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>-1002532871843</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>-1003782057933</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>-1002190969931</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>-1003140539585</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>-1002309114039</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>-1002623818368</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>-1002661244330</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>-1003688293993</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>-4863174120</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>-1003642033424</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>-4859225688</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>-1002575818224</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>-1002761685886</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>-1003810460807</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>-1001596465392</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>-1002428009204</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>-1002886657320</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>-1002877287868</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>-1002288803058</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>-1003751042188</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>-1002007016158</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>-1003352103344</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>-1002454558597</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>-1002255365525</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>-1003177468537</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>-1002916180495</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>-1002806388271</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>-1003046279469</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>-1001818742779</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>-1003246680728</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>-1002684891199</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>-1001790767217</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>-1002288129210</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>-1001729071175</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>-1002795475468</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>-1003272164317</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>-1002680979996</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>-4979055727</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>-1003786455955</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>-1003066477129</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>-1003563627055</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>-1002619556227</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>-1002836592504</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>-1002889377215</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>-1001124651563</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>-1002713471991</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>-1003826806165</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>-1002359134904</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>-1002702621828</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>-1002581029977</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>-1002853960198</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>-1003389444837</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>-1003090299188</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>-1002016937072</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>-1002541795473</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>-1003642398244</t>
         </is>
       </c>
     </row>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,98 +438,4459 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-1002268045818</t>
+          <t>-4877376604</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-1002359766306</t>
+          <t>-1002412562915</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-1002205410222</t>
+          <t>-1003527335437</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-1001817635995</t>
+          <t>-1002552125741</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>-1002338100665</t>
+          <t>-1003778480564</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-1003149481043</t>
+          <t>-1002957130138</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-1002114430690</t>
+          <t>-1002879625349</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-1003841442683</t>
+          <t>-1003456241208</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>-1003050031260</t>
+          <t>-1003001093483</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>-1002597892903</t>
+          <t>-1002651560084</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>-1003704472568</t>
+          <t>-1003093812371</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>-1003150223688</t>
+          <t>-1002265393780</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>-1002385566540</t>
+          <t>8002682623</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>-1001885408615</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>-1001921955585</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>-1002779291814</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>-1001467801859</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>-1001741252369</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>-1002549453056</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>-1002793180948</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>-1002965049763</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>-1002915894807</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>-1002727925450</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>-1002679523819</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>-1002761573267</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>-4863520102</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>-5231222732</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>-1002423915712</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>-1002281112145</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>-1003622904170</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>-1003770148368</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>-1003790209592</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>-1002278762192</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>-1002588140799</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>-1002619556227</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>-1003503147352</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>-1002908266830</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>-1001124651563</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>-1002683965508</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>-1003417970722</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>-1002346159781</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>-1003786455955</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>-1002464524981</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>-1002990734165</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>-1001859766402</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>-1002611045810</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>-1002278564823</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>-1001729071175</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>-1003354035186</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>-1002144563093</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>-1002659291107</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>-1003596125351</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>-1002728494984</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>-1002071946221</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>-1002288363987</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>-4989200624</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>-1002529665437</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>-1003585578699</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>-1002077075261</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>-1002639728798</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>-1002420273008</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>-4852298794</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>-5276076774</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>-1002556802461</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>-1003642398244</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>-1002555387875</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>-1002990595475</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>-1003234452408</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>-1003111708855</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>-1002360283286</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>-1002192798016</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>-1002493291997</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>-1002250659534</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>-1003118640750</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>-1003780172654</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>-1002834499433</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>-1002638064433</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>-1002895659136</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>-5114003285</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>-1003554414722</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>-1003789732989</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>-1002046646497</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>-1003180215428</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>-1002623818368</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>-1003415576816</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>-1003826806165</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>-1003887146140</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>-1002523705245</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>-1002695735836</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>-1002540598427</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>-1002832167728</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>-1002318473731</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>-1003185630550</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>-1001212305259</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>-1002031457701</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>-1002621836135</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>-1002778457560</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>-1002647444996</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>-1002486834455</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>-1003870585071</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>-4961873359</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>-1002999961089</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>-1003453389134</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>-1002974757160</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>-1002532871843</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>-1002887971256</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>-1002457910402</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>-1003751042188</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>-5212914594</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>-1003304830106</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>-1002864485836</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>-1003777385076</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>-1002832898246</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>-1002850122868</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>-1002747623711</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>-1002710336139</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>-1002007016158</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>-1002320838727</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>-1002567310940</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>-1002974874463</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>-1002761685886</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>-1003776273822</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>-1001923225361</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>-1002815867232</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>-1003857994445</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>-1003122716300</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>-5214487805</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>-1002760392715</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>-1002312125060</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>-1003090299188</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>-1002377511768</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>-1002516135792</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>-1002778350864</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>-4884314925</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>-1002579287925</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>-1002872771874</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>-1003577178993</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>-1002591852942</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>-1002898563298</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>-1002263664644</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>-1001596465392</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>-1002706892578</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>-1003229025294</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>6667684577</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>-1002581029977</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>-4952186637</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>-1003888265357</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>-1002448038408</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>-1002531829054</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>-1002773657299</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>-1003628737566</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>-1002719180481</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>-1002377976370</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>-1002237965843</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>-1003227982564</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>-1001877368569</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>-1002548868785</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>-1001929868118</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>-1002586036097</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>-1002415992686</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>-1002155445752</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>-1003844657847</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>-1002853960198</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>-1003395913805</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>-1001668927089</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>-1003246680728</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>-1003313884514</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>-1003371546403</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>-1002934936335</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>-1003870720812</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>-1001543478413</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>-1003894092375</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>-1003563627055</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>-1002541795473</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>-1002392635902</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>-1002365212456</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>-4859108486</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>-1001744426195</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>-1002870935153</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>-1001460104025</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>-1002950443553</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>-1002288129210</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>-1002799861129</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>-1003759072708</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>-1002624308239</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>-1002385566540</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>-4819895741</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>-1002760607433</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>-1003646802065</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>-1002886657320</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>-1002680979996</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>-1001846329972</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>-1002114430690</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>-1002715650097</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>-1002234774760</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>-1002826605956</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>-1003689644532</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>-1003583886956</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>-1002579055686</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>-1002514951234</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>-1003055781840</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>-1002482355272</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>-1003595525652</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>-1002454558597</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>-1003451010325</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>-1003116317699</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>-1001832880643</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>-1003560349248</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>-1002491853737</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>-1003882816542</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>-1001635430845</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>-1001790767217</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>-1003447123747</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>-1003485367302</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>-1002985739762</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>-5293053713</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>-1002618584679</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>-4941172345</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>-1002947162126</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>-1003642033424</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>-1002753083965</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>-1001674602550</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>-1003070751342</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>-1003462101210</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>-1003030066020</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>-1003613698828</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>-1003312077048</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>-1002782716052</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>-1003719969742</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>-1003856867815</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>-1003805893950</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>-1003739476321</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>-1002352486010</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>-1002393739109</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>-5182817479</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>-1002414175598</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>-1002778085921</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>-1002178056369</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>-1003654088798</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>-1003704472568</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>-1001671470841</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>-1002268045818</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>-1001985964144</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>-1002152254687</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>-1002702700644</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>-1002651012796</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>-1002321829358</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>-1003100265374</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>-1003558199964</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>-1002597892903</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>-1003654139992</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>-1002739724307</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>-5181397583</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>-1003864264998</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>-1003048673651</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>-1002877287868</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>-1002830324668</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>-1003141918793</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>-1003697183887</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>-1003038352740</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>-1003556812442</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>-1001922808139</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>-1003149481043</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>-1003207138530</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>-1002903801746</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>-1002340618636</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>-1002785625174</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>-1002712833331</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>-1002474339744</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>-1003421411518</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>-1003697454154</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>-1002927005745</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>-1003702625153</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>-1002217503260</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>-1003509730808</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>-1003272164317</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>-1002660309633</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>-1003150223688</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>-1002150947419</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>-1002575818224</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>-4863174120</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>-1002769760671</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>-1002101571866</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>-1003411469233</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>-1003382157325</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>-1003025068781</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>-1003661050854</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>-5176841635</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>-1002395833812</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>-1001730809010</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>-1002519990156</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>-1002744387247</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>-1002998185557</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>-1002730203883</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>6786983715</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>-1002703131951</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>-1002074104758</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>-1002367453033</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>-1003737369393</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>-1002532154366</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>-1003810708157</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>-1002512266739</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>-1001298208876</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>-1002978401429</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>-1003622694978</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>-1002659587443</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>-1003177468537</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>-1002168855114</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>-1002562282389</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>-1002106096413</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>-4822189866</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>-1002870267087</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>-1001900924039</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>-4964721197</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>-1002753235468</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>-1002420900028</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>-1003543088788</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>-1003239240721</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>-1002860460728</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>-1002658418497</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>-1002508916910</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>-1003811694462</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>-1002300324334</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>-1001950007498</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>-1001406184711</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>-1002651996794</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>-1002670277933</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>-4562050705</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>-1002419890323</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>-1003002359598</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>-1002873170822</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>-1002428009204</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>-1002860463322</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>-1003777534388</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>-1003690052299</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>-1001735560772</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>-1002510217399</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>-1002118631320</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>-1003845773021</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>-1002808195180</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>-1003389986244</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>-1002368728861</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>-1002226982992</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>-1003140539585</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>-1003007832445</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>-1002169700144</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>-1003035504222</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>-4162328212</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>-1002175510705</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>-1003839394701</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>-1002744838888</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>-1002379714369</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>-1002722253045</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>-1002866910509</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>-1002729517184</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>-1002566090891</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>-1002889377215</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>-1002520212825</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>-1001801324223</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>-1003445206607</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>-1002522147223</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>-1002551279375</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>-1002274964696</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>-1002418585410</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>-1002872579152</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>-1002825020185</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>-1002518556633</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>-1001819768369</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>-1003865487649</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>-1003105061815</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>-1001868146441</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>-1002881849916</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>-1003084989152</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>-1002872770022</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>-1002606190918</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>-1003323511757</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>-1003460209587</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>-1002209520317</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>-1002832174643</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>-1003301419264</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>-1001473268532</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>-4636171342</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>-1001796760199</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>-1003858324278</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>-1003046279469</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>-1002335271770</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>-1003744707157</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>-1001908446355</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>-1003183253419</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>-1002040217076</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>-1003841442683</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>-1002822883977</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>-4901343480</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>-1002616170042</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>-1003810460807</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>-1002324412075</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>-1003055719997</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>-1001493770434</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>-1002812268562</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>-1001652492827</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>-1001302667285</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>-1002531024619</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>-1003615692664</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>-1002800020843</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>-1002813643590</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>-1001946166876</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>-1002473130324</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>-1002016535857</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>-1002713471991</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>-1003317755929</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>-1002702621828</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>-1002621241174</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>-1003177115454</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>-4912413878</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>-1001807175468</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>-1002534699760</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>-1002320283926</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>-1003784295528</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>-1003502104542</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>-1002840970643</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>-1002632678475</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>-1003657106230</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>-1003407475393</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>-1003878903675</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>-1003364207368</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>-1002522608034</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>-1001373559245</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>-1002901874691</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>-1003352103344</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>-1002887675015</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>-1003848351434</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>-1003650931988</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>-1002587384955</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>-1002622011374</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>-1003694114079</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>-1002916180495</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>-1003688293993</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>-1002422251622</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>-1002983071868</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>-1002990158729</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>-1002110839951</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>-1002571339758</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>-1003289156239</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>-1001701084460</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>-1003487427178</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>-1002360094196</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>-1003217773561</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>-1003568455790</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>-1002582659607</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>-1003307893033</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>-1003078207757</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>-1003559602288</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>-1002560099813</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>-1002593501991</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>-4921455900</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>-1003092984130</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>-1002600708556</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>-1003666715930</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>-1003897294884</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>-1003673427063</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>-1002359134904</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>-1002754377559</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>-1003785529820</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>-4513511178</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>-1002320967880</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>-1002465441179</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>-1003605325965</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>-1003755868331</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>-1002836592504</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>-1003500481482</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>-1002255365525</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>-1001665462509</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>-1002359766306</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>-1002338100665</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>-1003798585147</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>-1003344556740</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>-1002518094653</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>-1003550392581</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>-4979055727</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>-1003254448559</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>-1003671208187</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>-1002130498457</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>-1002664729996</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>-1003461246398</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>-1003427818585</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>-1002530765960</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>-1002848062475</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>-1002303401228</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>-1002918117363</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>-1003624752221</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>-1002300501716</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>-1002359874556</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>-1002684891199</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>-1002403581849</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>-1003739043411</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>-1002615496638</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>-1003666795395</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>-1001546837418</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>-1003701419543</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>-1001994788372</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>-1001765476229</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>-1002073440916</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>-1003702553153</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>-1003144692446</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>-1001261718716</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>-1002571101349</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>-1002600128976</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>-1003609759956</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>-4964952099</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>-1003057678476</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>-1003131016214</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>-1002205410222</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>-1003373308518</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>-1002772423367</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>-1002870201502</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>-1002250428372</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>-1003094634117</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>-1002949588128</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>-1003650147257</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>-1003055472631</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>-1003579299494</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>-1002977896648</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>-1002167448908</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>-1002103104897</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>-1003293930657</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>-1003505125164</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
           <t>-1003795984362</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>-1003560358780</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>-1003881956622</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>-1003066477129</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>-1003129624230</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>-1003374632792</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>-1002288803058</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>-1003411310989</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>-1002738115577</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>-1003389444837</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>-1003576952118</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>-1003170688242</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>-1003894614780</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>-1002368488534</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>-5238910430</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>-1002509299058</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>-1002391001829</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>-1002437713625</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>-1002455033621</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>-1001390053729</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>-1003645590334</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>-1003169930553</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>-1002795475468</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>-1002776521317</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>-1002016912929</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>-1002918916933</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>-1002271738387</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>-1002809543928</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>-1001449424790</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>-1003048077625</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>-1002170512400</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>-1003094878642</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>-1002297618669</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>-1002734752869</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>-1002614518240</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>-1002388609283</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>-1002640591890</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>-1002096741759</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>-1003554106710</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>-1002309114039</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>-1001357883446</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>-1002416638992</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>-1002322838597</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>-1002189109599</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>-1002806388271</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>-1002761501601</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>-1003205119561</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>-1002809659148</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>-1002809610954</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>-1002016937072</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>-5264614378</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>-1002551612447</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>-1002011515239</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>-1003102873353</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>-1003150749086</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>-1003293940909</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>-1003601362039</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>-1003055362508</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>-1003518656172</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>-1003483467807</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>-1002509726671</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>-1003756210868</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>-4925721655</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>-1002750504156</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>-1003192981088</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>-1003022236579</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>-1001307311832</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>-1003635435133</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>-1001818008631</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>-1003343499093</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>-1002764128440</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>-1002862636130</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>-1003050031260</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>-1001647712873</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>-4977264275</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>-1003782057933</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>-1002904756274</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>-1002956645130</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>-1002342685523</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>-1003342714213</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>-1002580159815</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>-1002593143797</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>-1003520732236</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>-1002661244330</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>-1002445903437</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>-1002289430922</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>-1003822471010</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>-1002815530049</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>-1003027038967</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>-1003092228217</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>-1002190969931</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>-1002334852527</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>-1001540741017</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>-4974060502</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>-1003011064222</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>-1002092120695</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>-1002582926621</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>-1002880181368</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>-1003587135671</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>-1002372506024</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>-1003110118065</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>-1002159603263</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>-4859225688</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>-1001611710912</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>-1002595442276</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>-1002478485922</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>-1001818742779</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>-1002342989207</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>-1001817635995</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>-1003759164664</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>-1002092627141</t>
         </is>
       </c>
     </row>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A638"/>
+  <dimension ref="A1:A582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,1197 +438,1197 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-4877376604</t>
+          <t>-1003650931988</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-1002412562915</t>
+          <t>-1003624752221</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-1003527335437</t>
+          <t>-1003777534388</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-1002552125741</t>
+          <t>-1001923225361</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>-1003778480564</t>
+          <t>-1002046646497</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-1002957130138</t>
+          <t>-1002806388271</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-1002879625349</t>
+          <t>-1002778350864</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-1003456241208</t>
+          <t>-1002268045818</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>-1003001093483</t>
+          <t>-1003304830106</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>-1002651560084</t>
+          <t>-1002322838597</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>-1003093812371</t>
+          <t>-1003118640750</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>-1002265393780</t>
+          <t>-1002217503260</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8002682623</t>
+          <t>-1002760607433</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>-1001885408615</t>
+          <t>-1002118631320</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>-1001921955585</t>
+          <t>-1003205119561</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>-1002779291814</t>
+          <t>-1001596465392</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>-1001467801859</t>
+          <t>-1002779291814</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>-1001741252369</t>
+          <t>-1002393739109</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>-1002549453056</t>
+          <t>-1002872770022</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>-1002793180948</t>
+          <t>-1002702621828</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>-1002965049763</t>
+          <t>-1003558199964</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>-1002915894807</t>
+          <t>-1003789732989</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>-1002727925450</t>
+          <t>-1003289156239</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>-1002679523819</t>
+          <t>-1001302667285</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>-1002761573267</t>
+          <t>-1003857407484</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>-4863520102</t>
+          <t>-1002530765960</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>-5231222732</t>
+          <t>-1003234452408</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>-1002423915712</t>
+          <t>-1002747623711</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>-1002281112145</t>
+          <t>-1003485367302</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>-1003622904170</t>
+          <t>-1003382157325</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>-1003770148368</t>
+          <t>-1002320967880</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>-1003790209592</t>
+          <t>-1002571339758</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>-1002278762192</t>
+          <t>-1003084989152</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>-1002588140799</t>
+          <t>-1002769760671</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>-1002619556227</t>
+          <t>-1002549453056</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-1003503147352</t>
+          <t>-1002773657299</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>-1002908266830</t>
+          <t>-1003844657847</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>-1001124651563</t>
+          <t>-1002130498457</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>-1002683965508</t>
+          <t>-1002866910509</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>-1003417970722</t>
+          <t>-1003556812442</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>-1002346159781</t>
+          <t>-1003038352740</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>-1003786455955</t>
+          <t>-1003354035186</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>-1002464524981</t>
+          <t>-1002454558597</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>-1002990734165</t>
+          <t>-4941172345</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>-1001859766402</t>
+          <t>-1002754377559</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>-1002611045810</t>
+          <t>-1002990595475</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>-1002278564823</t>
+          <t>-1003364207368</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>-1001729071175</t>
+          <t>-1002639728798</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>-1003354035186</t>
+          <t>-1002870935153</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>-1002144563093</t>
+          <t>-1003411310989</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>-1002659291107</t>
+          <t>-1002761685886</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>-1003596125351</t>
+          <t>-1003055362508</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>-1002728494984</t>
+          <t>-1003373308518</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>-1002071946221</t>
+          <t>-5231222732</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>-1002288363987</t>
+          <t>-1002465441179</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>-4989200624</t>
+          <t>-1003887146140</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>-1002529665437</t>
+          <t>-1003057678476</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>-1003585578699</t>
+          <t>-4562050705</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>-1002077075261</t>
+          <t>-1002738115577</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>-1002639728798</t>
+          <t>-1002879625349</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>-1002420273008</t>
+          <t>-1003689644532</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>-4852298794</t>
+          <t>-1002263664644</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>-5276076774</t>
+          <t>-1002744838888</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>-1002556802461</t>
+          <t>-1003460209587</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>-1003642398244</t>
+          <t>-1002340618636</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>-1002555387875</t>
+          <t>-1002772423367</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>-1002990595475</t>
+          <t>-1002367453033</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>-1003234452408</t>
+          <t>-1003183253419</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>-1003111708855</t>
+          <t>-1002965049763</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>-1002360283286</t>
+          <t>-1002300501716</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>-1002192798016</t>
+          <t>-1002520212825</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>-1002493291997</t>
+          <t>-1003025068781</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>-1002250659534</t>
+          <t>-4636171342</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>-1003118640750</t>
+          <t>-1002288129210</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>-1003780172654</t>
+          <t>-1002898563298</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>-1002834499433</t>
+          <t>-1001493770434</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>-1002638064433</t>
+          <t>-1002031457701</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>-1002895659136</t>
+          <t>-1003169930553</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>-5114003285</t>
+          <t>-1002778085921</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>-1003554414722</t>
+          <t>-1003170688242</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>-1003789732989</t>
+          <t>-4974060502</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>-1002046646497</t>
+          <t>-1002250428372</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>-1003180215428</t>
+          <t>-1003576952118</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>-1002623818368</t>
+          <t>-1003254448559</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>-1003415576816</t>
+          <t>-1003810708157</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>-1003826806165</t>
+          <t>-1001994788372</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>-1003887146140</t>
+          <t>-1002850122868</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>-1002523705245</t>
+          <t>-1002983071868</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>-1002695735836</t>
+          <t>-1003518656172</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>-1002540598427</t>
+          <t>-1002423915712</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>-1002832167728</t>
+          <t>-1002522147223</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>-1002318473731</t>
+          <t>-5264614378</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>-1003185630550</t>
+          <t>-1002312125060</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>-1001212305259</t>
+          <t>-1003778480564</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>-1002031457701</t>
+          <t>-1002473130324</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>-1002621836135</t>
+          <t>-1002887675015</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>-1002778457560</t>
+          <t>-1003207138530</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>-1002647444996</t>
+          <t>-1002815530049</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>-1002486834455</t>
+          <t>-1003505125164</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>-1003870585071</t>
+          <t>-1001546837418</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>-4961873359</t>
+          <t>-1002392635902</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>-1002999961089</t>
+          <t>6667684577</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>-1003453389134</t>
+          <t>-1002334852527</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>-1002974757160</t>
+          <t>-1003889493565</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>-1002532871843</t>
+          <t>-1002300324334</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>-1002887971256</t>
+          <t>-1002567310940</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>-1002457910402</t>
+          <t>-1002324412075</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>-1003751042188</t>
+          <t>-1003389986244</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>-5212914594</t>
+          <t>-1003301419264</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>-1003304830106</t>
+          <t>-1002581029977</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>-1002864485836</t>
+          <t>-1001635430845</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>-1003777385076</t>
+          <t>-1002309114039</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>-1002832898246</t>
+          <t>-1002189109599</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>-1002850122868</t>
+          <t>-1003001093483</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>-1002747623711</t>
+          <t>-1002600128976</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>-1002710336139</t>
+          <t>-1003829992194</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>-1002007016158</t>
+          <t>-1003111708855</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>-1002320838727</t>
+          <t>-1003882816542</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>-1002567310940</t>
+          <t>-1001729071175</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>-1002974874463</t>
+          <t>-1003865487649</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>-1002761685886</t>
+          <t>-1003110118065</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>-1003776273822</t>
+          <t>-1002950443553</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>-1001923225361</t>
+          <t>-1002903801746</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>-1002815867232</t>
+          <t>-1002192798016</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>-1003857994445</t>
+          <t>-5214487805</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>-1003122716300</t>
+          <t>-1002352486010</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>-5214487805</t>
+          <t>-1001801324223</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>-1002760392715</t>
+          <t>-1001950007498</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>-1002312125060</t>
+          <t>-1002509299058</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>-1003090299188</t>
+          <t>-1002551279375</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>-1002377511768</t>
+          <t>-1002719180481</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>-1002516135792</t>
+          <t>-1001908446355</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>-1002778350864</t>
+          <t>-1002303401228</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>-4884314925</t>
+          <t>-1003150223688</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>-1002579287925</t>
+          <t>-1002152254687</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>-1002872771874</t>
+          <t>-1003560349248</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>-1003577178993</t>
+          <t>-1001668927089</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>-1002591852942</t>
+          <t>-1002321829358</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>-1002898563298</t>
+          <t>-1002114430690</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>-1002263664644</t>
+          <t>-1002695735836</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>-1001596465392</t>
+          <t>-1002531829054</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>-1002706892578</t>
+          <t>-1001671470841</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>-1003229025294</t>
+          <t>-1002750504156</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>6667684577</t>
+          <t>-1002812268562</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>-1002581029977</t>
+          <t>-1003560358780</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>-4952186637</t>
+          <t>-1003776273822</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>-1003888265357</t>
+          <t>-1002670277933</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>-1002448038408</t>
+          <t>-1002338100665</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>-1002531829054</t>
+          <t>-1003272164317</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>-1002773657299</t>
+          <t>-5293053713</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>-1003628737566</t>
+          <t>-1002428009204</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>-1002719180481</t>
+          <t>-1003055719997</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>-1002377976370</t>
+          <t>-1003878903675</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>-1002237965843</t>
+          <t>-1002509726671</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>-1003227982564</t>
+          <t>-1002281112145</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>-1001877368569</t>
+          <t>-1002271738387</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>-1002548868785</t>
+          <t>-1002949588128</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>-1001929868118</t>
+          <t>-1002071946221</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>-1002586036097</t>
+          <t>-1002297618669</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>-1002415992686</t>
+          <t>-1002621241174</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>-1002155445752</t>
+          <t>-1002288363987</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>-1003844657847</t>
+          <t>-4852298794</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>-1002853960198</t>
+          <t>-1002795475468</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>-1003395913805</t>
+          <t>-1003502104542</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>-1001668927089</t>
+          <t>-1002778457560</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>-1003246680728</t>
+          <t>-4859225688</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>-1003313884514</t>
+          <t>-1003785529820</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>-1003371546403</t>
+          <t>-1002582659607</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>-1002934936335</t>
+          <t>-1002388609283</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>-1003870720812</t>
+          <t>-1002288803058</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>-1001543478413</t>
+          <t>-1002659291107</t>
         </is>
       </c>
     </row>
@@ -1642,770 +1642,770 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>-1003563627055</t>
+          <t>-1003865824113</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>-1002541795473</t>
+          <t>-5238910430</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>-1002392635902</t>
+          <t>-1002985739762</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>-1002365212456</t>
+          <t>-1002368488534</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>-4859108486</t>
+          <t>-1003543088788</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>-1001744426195</t>
+          <t>-1003520732236</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>-1002870935153</t>
+          <t>-1002809610954</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>-1001460104025</t>
+          <t>-1002622011374</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>-1002950443553</t>
+          <t>-1003451010325</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>-1002288129210</t>
+          <t>-1002205410222</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>-1002799861129</t>
+          <t>-1002566090891</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>-1003759072708</t>
+          <t>-1003185630550</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>-1002624308239</t>
+          <t>-1002793180948</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>-1002385566540</t>
+          <t>-1003784295528</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>-4819895741</t>
+          <t>-1002832174643</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>-1002760607433</t>
+          <t>-1003055472631</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>-1003646802065</t>
+          <t>-1002437713625</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>-1002886657320</t>
+          <t>-1002710336139</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>-1002680979996</t>
+          <t>-1002684891199</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>-1001846329972</t>
+          <t>-1002880181368</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>-1002114430690</t>
+          <t>-1003708151846</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>-1002715650097</t>
+          <t>-1002360283286</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>-1002234774760</t>
+          <t>-1002647444996</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>-1002826605956</t>
+          <t>-1001985964144</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>-1003689644532</t>
+          <t>-1003140539585</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>-1003583886956</t>
+          <t>-1002761501601</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>-1002579055686</t>
+          <t>-1002619556227</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>-1002514951234</t>
+          <t>-1003601362039</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>-1003055781840</t>
+          <t>-1003092984130</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>-1002482355272</t>
+          <t>-1003002359598</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>-1003595525652</t>
+          <t>-1002651996794</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>-1002454558597</t>
+          <t>-1003671208187</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>-1003451010325</t>
+          <t>-1002872579152</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>-1003116317699</t>
+          <t>-1003344556740</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>-1001832880643</t>
+          <t>-1003293930657</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>-1003560349248</t>
+          <t>-1002416638992</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>-1002491853737</t>
+          <t>-1003596125351</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>-1003882816542</t>
+          <t>-1003293940909</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>-1001635430845</t>
+          <t>-1002209520317</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>-1001790767217</t>
+          <t>-1002523705245</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>-1003447123747</t>
+          <t>-1002016912929</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>-1003485367302</t>
+          <t>-1003870585071</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>-1002985739762</t>
+          <t>-1003751042188</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>-5293053713</t>
+          <t>-1003055781840</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>-1002618584679</t>
+          <t>-1003759164664</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>-4941172345</t>
+          <t>-1003011064222</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>-1002947162126</t>
+          <t>-1002092120695</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>-1003642033424</t>
+          <t>-1001540741017</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>-1002753083965</t>
+          <t>-4819895741</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>-1001674602550</t>
+          <t>-1001611710912</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>-1003070751342</t>
+          <t>-1002990158729</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>-1003462101210</t>
+          <t>-1002809543928</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>-1003030066020</t>
+          <t>-1002377976370</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>-1003613698828</t>
+          <t>-1002106096413</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>-1003312077048</t>
+          <t>-4964952099</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>-1002782716052</t>
+          <t>-1003094634117</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>-1003719969742</t>
+          <t>-1003313884514</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>-1003856867815</t>
+          <t>-1003697454154</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>-1003805893950</t>
+          <t>-1002532154366</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>-1003739476321</t>
+          <t>-1003864575810</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>-1002352486010</t>
+          <t>-1003609759956</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>-1002393739109</t>
+          <t>-1003447123747</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>-5182817479</t>
+          <t>-1003352103344</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>-1002414175598</t>
+          <t>-1002870267087</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>-1002778085921</t>
+          <t>-1002614518240</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>-1002178056369</t>
+          <t>-1002575818224</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>-1003654088798</t>
+          <t>-1002658418497</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>-1003704472568</t>
+          <t>-1002580159815</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>-1001671470841</t>
+          <t>-1003704472568</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>-1002268045818</t>
+          <t>6786983715</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>-1001985964144</t>
+          <t>-1001744426195</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>-1002152254687</t>
+          <t>-1002588140799</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>-1002702700644</t>
+          <t>-1002901874691</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>-1002651012796</t>
+          <t>-1003192981088</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>-1002321829358</t>
+          <t>-1002289430922</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>-1003100265374</t>
+          <t>-1002455033621</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>-1003558199964</t>
+          <t>-1002508916910</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>-1002597892903</t>
+          <t>-1002560099813</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>-1003654139992</t>
+          <t>-1003755708310</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>-1002739724307</t>
+          <t>-1001921955585</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>-5181397583</t>
+          <t>-5276076774</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>-1003864264998</t>
+          <t>-1002551612447</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>-1003048673651</t>
+          <t>-1003105061815</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>-1002877287868</t>
+          <t>-1002702700644</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>-1002830324668</t>
+          <t>-1002864485836</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>-1003141918793</t>
+          <t>-1002175510705</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>-1003697183887</t>
+          <t>-1001741252369</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>-1003038352740</t>
+          <t>-1002977896648</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>-1003556812442</t>
+          <t>-1001307311832</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>-1001922808139</t>
+          <t>-1003046279469</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>-1003149481043</t>
+          <t>-1002359874556</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>-1003207138530</t>
+          <t>-1003100265374</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>-1002903801746</t>
+          <t>-1002990734165</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>-1002340618636</t>
+          <t>-1002464524981</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>-1002785625174</t>
+          <t>-1002836592504</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>-1002712833331</t>
+          <t>-1003739476321</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>-1002474339744</t>
+          <t>-1003385914148</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>-1003421411518</t>
+          <t>-1003094878642</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>-1003697454154</t>
+          <t>-1002760392715</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>-1002927005745</t>
+          <t>-4162328212</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>-1003702625153</t>
+          <t>-1003090299188</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>-1002217503260</t>
+          <t>-1002491853737</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>-1003509730808</t>
+          <t>-1003554106710</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>-1003272164317</t>
+          <t>-1002318473731</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>-1002660309633</t>
+          <t>-1002555387875</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>-1003150223688</t>
+          <t>-4989200624</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>-1002150947419</t>
+          <t>-1002587384955</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>-1002575818224</t>
+          <t>-1003180215428</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>-4863174120</t>
+          <t>-1003246680728</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>-1002769760671</t>
+          <t>-1002359134904</t>
         </is>
       </c>
     </row>
@@ -2419,2478 +2419,2086 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>-1003411469233</t>
+          <t>-4877376604</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>-1003382157325</t>
+          <t>-1002190969931</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>-1003025068781</t>
+          <t>-1003483467807</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>-1003661050854</t>
+          <t>-1002651560084</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>-5176841635</t>
+          <t>-1002178056369</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>-1002395833812</t>
+          <t>-1002391001829</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>-1001730809010</t>
+          <t>-1002372506024</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>-1002519990156</t>
+          <t>-1003635435133</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>-1002744387247</t>
+          <t>-1002541795473</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>-1002998185557</t>
+          <t>-1003229025294</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>-1002730203883</t>
+          <t>-1003579299494</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>6786983715</t>
+          <t>-1002904756274</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>-1002703131951</t>
+          <t>-1001807175468</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>-1002074104758</t>
+          <t>-1003445206607</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>-1002367453033</t>
+          <t>-1003856867815</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>-1003737369393</t>
+          <t>-1003858324278</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>-1002532154366</t>
+          <t>-1002226982992</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>-1003810708157</t>
+          <t>-1001735560772</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>-1002512266739</t>
+          <t>-1001467801859</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>-1001298208876</t>
+          <t>-1002532871843</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>-1002978401429</t>
+          <t>-1002522608034</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>-1003622694978</t>
+          <t>-1002683965508</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>-1002659587443</t>
+          <t>-1001460104025</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>-1003177468537</t>
+          <t>-1002368728861</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>-1002168855114</t>
+          <t>-1002512266739</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>-1002562282389</t>
+          <t>-1002661244330</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>-1002106096413</t>
+          <t>-4863520102</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>-4822189866</t>
+          <t>-1002918117363</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>-1002870267087</t>
+          <t>-1002110839951</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>-1001900924039</t>
+          <t>-1002999961089</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>-4964721197</t>
+          <t>-1002540598427</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>-1002753235468</t>
+          <t>-1002611045810</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>-1002420900028</t>
+          <t>-1002478485922</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>-1003543088788</t>
+          <t>-1002128565721</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>-1003239240721</t>
+          <t>-5182817479</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>-1002860460728</t>
+          <t>-1003035504222</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>-1002658418497</t>
+          <t>-1002825020185</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>-1002508916910</t>
+          <t>-1003500481482</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>-1003811694462</t>
+          <t>-1002834499433</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>-1002300324334</t>
+          <t>-1002808195180</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>-1001950007498</t>
+          <t>-1003389444837</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>-1001406184711</t>
+          <t>-5212914594</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>-1002651996794</t>
+          <t>-1003050031260</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>-1002670277933</t>
+          <t>-1001665462509</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>-4562050705</t>
+          <t>-1002320283926</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>-1002419890323</t>
+          <t>-1001373559245</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>-1003002359598</t>
+          <t>-1003690052299</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>-1002873170822</t>
+          <t>-1002734752869</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>-1002428009204</t>
+          <t>-1002422251622</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>-1002860463322</t>
+          <t>-1003007832445</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>-1003777534388</t>
+          <t>-1001765476229</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>-1003690052299</t>
+          <t>-1003805893950</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>-1001735560772</t>
+          <t>-4961873359</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>-1002510217399</t>
+          <t>-1002016535857</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>-1002118631320</t>
+          <t>-1002448038408</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>-1003845773021</t>
+          <t>-1002624308239</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>-1002808195180</t>
+          <t>-1001212305259</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>-1003389986244</t>
+          <t>-5176841635</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>-1002368728861</t>
+          <t>-1003613698828</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>-1002226982992</t>
+          <t>-1001298208876</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>-1003140539585</t>
+          <t>-1002096741759</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>-1003007832445</t>
+          <t>-1002073440916</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>-1002169700144</t>
+          <t>-1002623818368</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>-1003035504222</t>
+          <t>-1002853960198</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>-4162328212</t>
+          <t>-1002753083965</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>-1002175510705</t>
+          <t>-1002886657320</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>-1003839394701</t>
+          <t>-1002586036097</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>-1002744838888</t>
+          <t>-1002621836135</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>-1002379714369</t>
+          <t>-4964721197</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>-1002722253045</t>
+          <t>-1002593143797</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>-1002866910509</t>
+          <t>-1001817635995</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>-1002729517184</t>
+          <t>-1003870720812</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>-1002566090891</t>
+          <t>-1002077075261</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>-1002889377215</t>
+          <t>-1003577178993</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>-1002520212825</t>
+          <t>-1003650147257</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>-1001801324223</t>
+          <t>-1002552125741</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>-1003445206607</t>
+          <t>-1003563627055</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>-1002522147223</t>
+          <t>-1001701084460</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>-1002551279375</t>
+          <t>-1002809659148</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>-1002274964696</t>
+          <t>-1002860460728</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>-1002418585410</t>
+          <t>-1003177115454</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>-1002872579152</t>
+          <t>-1002167448908</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>-1002825020185</t>
+          <t>-1003756210868</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>-1002518556633</t>
+          <t>-1002651012796</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>-1001819768369</t>
+          <t>-1001652492827</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>-1003865487649</t>
+          <t>-1003503147352</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>-1003105061815</t>
+          <t>-1001406184711</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>-1001868146441</t>
+          <t>-1002414175598</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>-1002881849916</t>
+          <t>-1002761573267</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>-1003084989152</t>
+          <t>-1002915894807</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>-1002872770022</t>
+          <t>-1001885408615</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>-1002606190918</t>
+          <t>-1001647712873</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>-1003323511757</t>
+          <t>-4921455900</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>-1003460209587</t>
+          <t>-1002365212456</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>-1002209520317</t>
+          <t>-1002519990156</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>-1002832174643</t>
+          <t>-1001543478413</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>-1003301419264</t>
+          <t>-1003427818585</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>-1001473268532</t>
+          <t>-1002144563093</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>-4636171342</t>
+          <t>-1003719969742</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>-1001796760199</t>
+          <t>-1003673427063</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>-1003858324278</t>
+          <t>-1002664729996</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>-1003046279469</t>
+          <t>-1002342685523</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>-1002335271770</t>
+          <t>-1002616170042</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>-1003744707157</t>
+          <t>-1003177468537</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>-1001908446355</t>
+          <t>-4912413878</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>-1003183253419</t>
+          <t>-1001796760199</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>-1002040217076</t>
+          <t>-1003307893033</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>-1003841442683</t>
+          <t>-1001846329972</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>-1002822883977</t>
+          <t>-1002250659534</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>-4901343480</t>
+          <t>-1001868146441</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>-1002616170042</t>
+          <t>-1003217773561</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>-1003810460807</t>
+          <t>-1002848062475</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>-1002324412075</t>
+          <t>-1002040217076</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>-1003055719997</t>
+          <t>-1002744387247</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>-1001493770434</t>
+          <t>-1002706892578</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>-1002812268562</t>
+          <t>-1003527335437</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>-1001652492827</t>
+          <t>-1003141918793</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>-1001302667285</t>
+          <t>-1003666715930</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>-1002531024619</t>
+          <t>-1002234774760</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>-1003615692664</t>
+          <t>-1002799861129</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>-1002800020843</t>
+          <t>-1001674602550</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>-1002813643590</t>
+          <t>-1002529665437</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>-1001946166876</t>
+          <t>-1002518556633</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>-1002473130324</t>
+          <t>-1001124651563</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>-1002016535857</t>
+          <t>-1002074104758</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>-1002713471991</t>
+          <t>-1002170512400</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>-1003317755929</t>
+          <t>-1001900924039</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>-1002702621828</t>
+          <t>-1003701419543</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>-1002621241174</t>
+          <t>-1003048077625</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>-1003177115454</t>
+          <t>-1001473268532</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>-4912413878</t>
+          <t>-1002764128440</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>-1001807175468</t>
+          <t>-1003022236579</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>-1002534699760</t>
+          <t>-1003848351434</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>-1002320283926</t>
+          <t>-1002615496638</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>-1003784295528</t>
+          <t>-1003839394701</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>-1003502104542</t>
+          <t>-4513511178</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>-1002840970643</t>
+          <t>-1003587135671</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>-1002632678475</t>
+          <t>-1002265393780</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>-1003657106230</t>
+          <t>-1003417970722</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>-1003407475393</t>
+          <t>-1002753235468</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>-1003878903675</t>
+          <t>-1002679523819</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>-1003364207368</t>
+          <t>-1003864264998</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>-1002522608034</t>
+          <t>-1002510217399</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>-1001373559245</t>
+          <t>-1002582926621</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>-1002901874691</t>
+          <t>-1002379714369</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>-1003352103344</t>
+          <t>-4884314925</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>-1002887675015</t>
+          <t>-1002715650097</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>-1003848351434</t>
+          <t>-1001357883446</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>-1003650931988</t>
+          <t>-1003661050854</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>-1002587384955</t>
+          <t>-1002168855114</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>-1002622011374</t>
+          <t>-1002591852942</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>-1003694114079</t>
+          <t>8002682623</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>-1002916180495</t>
+          <t>-1003116317699</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>-1003688293993</t>
+          <t>-1003150749086</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>-1002422251622</t>
+          <t>-1002830324668</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>-1002983071868</t>
+          <t>-1003554414722</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>-1002990158729</t>
+          <t>-1003550392581</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>-1002110839951</t>
+          <t>-1003795984362</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>-1002571339758</t>
+          <t>-1002335271770</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>-1003289156239</t>
+          <t>-1003317755929</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>-1001701084460</t>
+          <t>867824604</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>-1003487427178</t>
+          <t>-1003841442683</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>-1002360094196</t>
+          <t>-1002420273008</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>-1003217773561</t>
+          <t>-1001690032632</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>-1003568455790</t>
+          <t>-1003845773021</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>-1002582659607</t>
+          <t>-1002486834455</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>-1003307893033</t>
+          <t>-1002579055686</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>-1003078207757</t>
+          <t>-1002870201502</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>-1003559602288</t>
+          <t>-1001859766402</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>-1002560099813</t>
+          <t>-1003239240721</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>-1002593501991</t>
+          <t>-1002776521317</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>-4921455900</t>
+          <t>-1003628737566</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>-1003092984130</t>
+          <t>-4901343480</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>-1002600708556</t>
+          <t>-1003343499093</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>-1003666715930</t>
+          <t>-1003559602288</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>-1003897294884</t>
+          <t>-1002947162126</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>-1003673427063</t>
+          <t>-1002908266830</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>-1002359134904</t>
+          <t>-1003027038967</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>-1002754377559</t>
+          <t>-1001922808139</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>-1003785529820</t>
+          <t>-1002832898246</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>-4513511178</t>
+          <t>-1002359766306</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>-1002320967880</t>
+          <t>-1002103104897</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>-1002465441179</t>
+          <t>-1002889377215</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>-1003605325965</t>
+          <t>-1002418585410</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>-1003755868331</t>
+          <t>-1002887971256</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>-1002836592504</t>
+          <t>-1002579287925</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>-1003500481482</t>
+          <t>-1002556802461</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>-1002255365525</t>
+          <t>-1002974874463</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>-1001665462509</t>
+          <t>-1003312077048</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>-1002359766306</t>
+          <t>-1003737369393</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>-1002338100665</t>
+          <t>-1002860463322</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>-1003798585147</t>
+          <t>-1002600708556</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>-1003344556740</t>
+          <t>-4859108486</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>-1002518094653</t>
+          <t>-1002826605956</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>-1003550392581</t>
+          <t>-1001818742779</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>-4979055727</t>
+          <t>-1001449424790</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>-1003254448559</t>
+          <t>-1002385566540</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>-1003671208187</t>
+          <t>-1003131016214</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>-1002130498457</t>
+          <t>-1002274964696</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>-1002664729996</t>
+          <t>-1003897294884</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>-1003461246398</t>
+          <t>-1003702553153</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>-1003427818585</t>
+          <t>-1002493291997</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>-1002530765960</t>
+          <t>-1003657106230</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>-1002848062475</t>
+          <t>-1001946166876</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>-1002303401228</t>
+          <t>-4925721655</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>-1002918117363</t>
+          <t>-1002150947419</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>-1003624752221</t>
+          <t>-1002729517184</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>-1002300501716</t>
+          <t>-1002360094196</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>-1002359874556</t>
+          <t>-1002927005745</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>-1002684891199</t>
+          <t>-1002562282389</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>-1002403581849</t>
+          <t>-1002873170822</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>-1003739043411</t>
+          <t>-1002482355272</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>-1002615496638</t>
+          <t>-1002638064433</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>-1003666795395</t>
+          <t>-1002007016158</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>-1001546837418</t>
+          <t>-1003371546403</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>-1003701419543</t>
+          <t>-1002916180495</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>-1001994788372</t>
+          <t>-1002877287868</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>-1001765476229</t>
+          <t>-1002403581849</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>-1002073440916</t>
+          <t>-1003894614780</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>-1003702553153</t>
+          <t>-1002278564823</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>-1003144692446</t>
+          <t>-1002640591890</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>-1001261718716</t>
+          <t>-1002832167728</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>-1002571101349</t>
+          <t>-1002956645130</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>-1002600128976</t>
+          <t>-1002618584679</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>-1003609759956</t>
+          <t>-1001818008631</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>-4964952099</t>
+          <t>-1003583886956</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>-1003057678476</t>
+          <t>-1002597892903</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>-1003131016214</t>
+          <t>-1002155445752</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>-1002205410222</t>
+          <t>-1003487427178</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>-1003373308518</t>
+          <t>-1002822883977</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>-1002772423367</t>
+          <t>-1002813643590</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>-1002870201502</t>
+          <t>-1002606190918</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>-1002250428372</t>
+          <t>-1002815867232</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>-1003094634117</t>
+          <t>-1002395833812</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>-1002949588128</t>
+          <t>-4952186637</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>-1003650147257</t>
+          <t>-1002474339744</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>-1003055472631</t>
+          <t>-1003782057933</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>-1003579299494</t>
+          <t>-4863174120</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>-1002977896648</t>
+          <t>-1003462101210</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>-1002167448908</t>
+          <t>-1002531024619</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>-1002103104897</t>
+          <t>-1003149481043</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>-1003293930657</t>
+          <t>-1002518094653</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>-1003505125164</t>
+          <t>-1002255365525</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>-1003795984362</t>
+          <t>-1002514951234</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>-1003560358780</t>
+          <t>-1001390053729</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>-1003881956622</t>
+          <t>-4979055727</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>-1003066477129</t>
+          <t>-1001929868118</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>-1003129624230</t>
+          <t>-1003122716300</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>-1003374632792</t>
+          <t>-1003605325965</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>-1002288803058</t>
+          <t>-1003102873353</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>-1003411310989</t>
+          <t>-1003070751342</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>-1002738115577</t>
+          <t>-1003456241208</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>-1003389444837</t>
+          <t>-1003323511757</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>-1003576952118</t>
+          <t>-1003811694462</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>-1003170688242</t>
+          <t>-1003421411518</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>-1003894614780</t>
+          <t>-1002703131951</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>-1002368488534</t>
+          <t>-1002011515239</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>-5238910430</t>
+          <t>-1002169700144</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>-1002509299058</t>
+          <t>-1002722253045</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>-1002391001829</t>
+          <t>-1002092627141</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>-1002437713625</t>
+          <t>-1002632678475</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>-1002455033621</t>
+          <t>-5114003285</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>-1001390053729</t>
+          <t>-1003888265357</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>-1003645590334</t>
+          <t>-1002619575978</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>-1003169930553</t>
+          <t>-1003645590334</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>-1002795475468</t>
+          <t>-1002782716052</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>-1002776521317</t>
+          <t>-1002415992686</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>-1002016912929</t>
+          <t>-1003453389134</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>-1002918916933</t>
+          <t>-1002237965843</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>-1002271738387</t>
+          <t>-1003509730808</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>-1002809543928</t>
+          <t>-1003227982564</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>-1001449424790</t>
+          <t>-4822189866</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>-1003048077625</t>
+          <t>-1002420900028</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>-1002170512400</t>
+          <t>-1002957130138</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>-1003094878642</t>
+          <t>-1003694114079</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>-1002297618669</t>
+          <t>-1003798585147</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>-1002734752869</t>
+          <t>-1002680979996</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>-1002614518240</t>
+          <t>-5181397583</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>-1002388609283</t>
+          <t>-1002534699760</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>-1002640591890</t>
+          <t>-1003622694978</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>-1002096741759</t>
+          <t>-1001730809010</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>-1003554106710</t>
+          <t>-1003881956622</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>-1002309114039</t>
+          <t>-4977264275</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>-1001357883446</t>
+          <t>-1003093812371</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>-1002416638992</t>
+          <t>-1003129624230</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>-1002322838597</t>
+          <t>-1003415576816</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>-1002189109599</t>
+          <t>-1002457910402</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>-1002806388271</t>
+          <t>-1003092228217</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>-1002761501601</t>
+          <t>-1002419890323</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>-1003205119561</t>
+          <t>-1002278762192</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>-1002809659148</t>
+          <t>-1002342989207</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>-1002809610954</t>
+          <t>-1002320838727</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>-1002016937072</t>
+          <t>-1002595442276</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>-5264614378</t>
+          <t>-1002713471991</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>-1002551612447</t>
+          <t>-1002840970643</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>-1002011515239</t>
+          <t>-1002712833331</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>-1003102873353</t>
+          <t>-1003048673651</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>-1003150749086</t>
-        </is>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>-1003293940909</t>
-        </is>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
-        <is>
-          <t>-1003601362039</t>
-        </is>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
-          <t>-1003055362508</t>
-        </is>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>-1003518656172</t>
-        </is>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
-        <is>
-          <t>-1003483467807</t>
-        </is>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
-        <is>
-          <t>-1002509726671</t>
-        </is>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>-1003756210868</t>
-        </is>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
-        <is>
-          <t>-4925721655</t>
-        </is>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
-        <is>
-          <t>-1002750504156</t>
-        </is>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
-        <is>
-          <t>-1003192981088</t>
-        </is>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
-        <is>
-          <t>-1003022236579</t>
-        </is>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
-        <is>
-          <t>-1001307311832</t>
-        </is>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
-        <is>
-          <t>-1003635435133</t>
-        </is>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>-1001818008631</t>
-        </is>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
-        <is>
-          <t>-1003343499093</t>
-        </is>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
-        <is>
-          <t>-1002764128440</t>
-        </is>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
-        <is>
-          <t>-1002862636130</t>
-        </is>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
-        <is>
-          <t>-1003050031260</t>
-        </is>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>-1001647712873</t>
-        </is>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>-4977264275</t>
-        </is>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
-        <is>
-          <t>-1003782057933</t>
-        </is>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>-1002904756274</t>
-        </is>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
-        <is>
-          <t>-1002956645130</t>
-        </is>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
-        <is>
-          <t>-1002342685523</t>
-        </is>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
-        <is>
-          <t>-1003342714213</t>
-        </is>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t>-1002580159815</t>
-        </is>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
-        <is>
-          <t>-1002593143797</t>
-        </is>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
-        <is>
-          <t>-1003520732236</t>
-        </is>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
-        <is>
-          <t>-1002661244330</t>
-        </is>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
-        <is>
-          <t>-1002445903437</t>
-        </is>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
-        <is>
-          <t>-1002289430922</t>
-        </is>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
-        <is>
-          <t>-1003822471010</t>
-        </is>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
-        <is>
-          <t>-1002815530049</t>
-        </is>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>-1003027038967</t>
-        </is>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>-1003092228217</t>
-        </is>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>-1002190969931</t>
-        </is>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>-1002334852527</t>
-        </is>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>-1001540741017</t>
-        </is>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
-        <is>
-          <t>-4974060502</t>
-        </is>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
-        <is>
-          <t>-1003011064222</t>
-        </is>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>-1002092120695</t>
-        </is>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>-1002582926621</t>
-        </is>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
-        <is>
-          <t>-1002880181368</t>
-        </is>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
-        <is>
-          <t>-1003587135671</t>
-        </is>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
-        <is>
-          <t>-1002372506024</t>
-        </is>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
-        <is>
-          <t>-1003110118065</t>
-        </is>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
-        <is>
-          <t>-1002159603263</t>
-        </is>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
-        <is>
-          <t>-4859225688</t>
-        </is>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
-        <is>
-          <t>-1001611710912</t>
-        </is>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
-        <is>
-          <t>-1002595442276</t>
-        </is>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
-        <is>
-          <t>-1002478485922</t>
-        </is>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>-1001818742779</t>
-        </is>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
-        <is>
-          <t>-1002342989207</t>
-        </is>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
-        <is>
-          <t>-1001817635995</t>
-        </is>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
-        <is>
-          <t>-1003759164664</t>
-        </is>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
-        <is>
-          <t>-1002092627141</t>
+          <t>-1003066477129</t>
         </is>
       </c>
     </row>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A582"/>
+  <dimension ref="A1:A596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,1750 +438,1750 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-1003650931988</t>
+          <t>-1001796760199</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-1003624752221</t>
+          <t>-1002582926621</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-1003777534388</t>
+          <t>-1002531024619</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-1001923225361</t>
+          <t>-1003293940909</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>-1002046646497</t>
+          <t>-1003293930657</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-1002806388271</t>
+          <t>-1001652492827</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-1002778350864</t>
+          <t>-1003344556740</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-1002268045818</t>
+          <t>-1002128565721</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>-1003304830106</t>
+          <t>-1002661244330</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>-1002322838597</t>
+          <t>-1003776273822</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>-1003118640750</t>
+          <t>-5238910430</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>-1002217503260</t>
+          <t>-1003719969742</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>-1002760607433</t>
+          <t>-1002455033621</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>-1002118631320</t>
+          <t>-4819895741</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>-1003205119561</t>
+          <t>-1002169700144</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>-1001596465392</t>
+          <t>-1002760392715</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>-1002779291814</t>
+          <t>-1001730809010</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>-1002393739109</t>
+          <t>-1002990595475</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>-1002872770022</t>
+          <t>-1003239240721</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>-1002702621828</t>
+          <t>-1002473130324</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>-1003558199964</t>
+          <t>-1002651996794</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>-1003789732989</t>
+          <t>-1002703131951</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>-1003289156239</t>
+          <t>-1001929868118</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>-1001302667285</t>
+          <t>-1003543088788</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>-1003857407484</t>
+          <t>-1003518656172</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>-1002530765960</t>
+          <t>-1003661050854</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>-1003234452408</t>
+          <t>-1001741252369</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>-1002747623711</t>
+          <t>-4977264275</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>-1003485367302</t>
+          <t>-1001212305259</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>-1003382157325</t>
+          <t>-1002385566540</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>-1002320967880</t>
+          <t>-1002658418497</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>-1002571339758</t>
+          <t>-1001985964144</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>-1003084989152</t>
+          <t>-1002659291107</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>-1002769760671</t>
+          <t>-1003509730808</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>-1002549453056</t>
+          <t>-1002815530049</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-1002773657299</t>
+          <t>-1002809610954</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>-1003844657847</t>
+          <t>-1001859766402</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>-1002130498457</t>
+          <t>-1002806388271</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>-1002866910509</t>
+          <t>-1002359766306</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>-1003556812442</t>
+          <t>-1003111708855</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>-1003038352740</t>
+          <t>-1002850122868</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>-1003354035186</t>
+          <t>-1002587384955</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>-1002454558597</t>
+          <t>-1002274964696</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>-4941172345</t>
+          <t>-1002360283286</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>-1002754377559</t>
+          <t>-1003226509168</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>-1002990595475</t>
+          <t>-1002738115577</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>-1003364207368</t>
+          <t>-1002312125060</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>-1002639728798</t>
+          <t>-1002614518240</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>-1002870935153</t>
+          <t>-1002579055686</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>-1003411310989</t>
+          <t>-1002359134904</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>-1002761685886</t>
+          <t>-1003189090793</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>-1003055362508</t>
+          <t>-1002519990156</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>-1003373308518</t>
+          <t>-1002454558597</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>-5231222732</t>
+          <t>-1002949588128</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>-1002465441179</t>
+          <t>-1001921955585</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>-1003887146140</t>
+          <t>-1002977896648</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>-1003057678476</t>
+          <t>-1002621241174</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>-4562050705</t>
+          <t>-1003180215428</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>-1002738115577</t>
+          <t>-1003690052299</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>-1002879625349</t>
+          <t>-1002761573267</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>-1003689644532</t>
+          <t>-1002040217076</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>-1002263664644</t>
+          <t>-1001540741017</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>-1002744838888</t>
+          <t>-1003671208187</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>-1003460209587</t>
+          <t>-1002175510705</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>-1002340618636</t>
+          <t>-1001473268532</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>-1002772423367</t>
+          <t>-1002647444996</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>-1002367453033</t>
+          <t>-1002918117363</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>-1003183253419</t>
+          <t>-1002092627141</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>-1002965049763</t>
+          <t>-1002518094653</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>-1002300501716</t>
+          <t>-1003131016214</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>-1002520212825</t>
+          <t>-4979055727</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>-1003025068781</t>
+          <t>-1001735560772</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>-4636171342</t>
+          <t>-1003666715930</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>-1002288129210</t>
+          <t>-1003550392581</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>-1002898563298</t>
+          <t>-1001744426195</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>-1001493770434</t>
+          <t>-1003713721988</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>-1002031457701</t>
+          <t>-1002551279375</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>-1003169930553</t>
+          <t>-1002575818224</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>-1002778085921</t>
+          <t>-1003046279469</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>-1003170688242</t>
+          <t>-1002300501716</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>-4974060502</t>
+          <t>-1002271738387</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>-1002250428372</t>
+          <t>-1003689644532</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>-1003576952118</t>
+          <t>-1003487427178</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>-1003254448559</t>
+          <t>-1002190969931</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>-1003810708157</t>
+          <t>-1002377976370</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>-1001994788372</t>
+          <t>-1002702621828</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>-1002850122868</t>
+          <t>-1003778480564</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>-1002983071868</t>
+          <t>-1003576952118</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>-1003518656172</t>
+          <t>-1002809659148</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>-1002423915712</t>
+          <t>-1003234452408</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>-1002522147223</t>
+          <t>-1002713471991</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>-5264614378</t>
+          <t>-1003897294884</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>-1002312125060</t>
+          <t>-1003673427063</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>-1003778480564</t>
+          <t>-1003609759956</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>-1002473130324</t>
+          <t>-1002773657299</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>-1002887675015</t>
+          <t>-1002776521317</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>-1003207138530</t>
+          <t>-1003390988695</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>-1002815530049</t>
+          <t>-1002388609283</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>-1003505125164</t>
+          <t>-1002562282389</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>-1001546837418</t>
+          <t>-1003055719997</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>-1002392635902</t>
+          <t>-4964952099</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>6667684577</t>
+          <t>-1003502104542</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>-1002334852527</t>
+          <t>8002682623</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>-1003889493565</t>
+          <t>-1001946166876</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>-1002300324334</t>
+          <t>-5166274564</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>-1002567310940</t>
+          <t>-1002189109599</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>-1002324412075</t>
+          <t>-1003411310989</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>-1003389986244</t>
+          <t>-1002809543928</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>-1003301419264</t>
+          <t>-1003601362039</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>-1002581029977</t>
+          <t>-1003759164664</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>-1001635430845</t>
+          <t>-1002710336139</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>-1002309114039</t>
+          <t>-1003371546403</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>-1002189109599</t>
+          <t>-1002116108604</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>-1003001093483</t>
+          <t>-1002965049763</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>-1002600128976</t>
+          <t>-1002552125741</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>-1003829992194</t>
+          <t>-1003373308518</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>-1003111708855</t>
+          <t>-1003140539585</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>-1003882816542</t>
+          <t>-1002074104758</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>-1001729071175</t>
+          <t>-1003317755929</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>-1003865487649</t>
+          <t>-1003170688242</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>-1003110118065</t>
+          <t>-1002618584679</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>-1002950443553</t>
+          <t>-1003445206607</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>-1002903801746</t>
+          <t>-1002324412075</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>-1002192798016</t>
+          <t>-1003785529820</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>-5214487805</t>
+          <t>-1002619556227</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>-1002352486010</t>
+          <t>-1003596125351</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>-1001801324223</t>
+          <t>-1003254448559</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>-1001950007498</t>
+          <t>-1003149481043</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>-1002509299058</t>
+          <t>-1002950443553</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>-1002551279375</t>
+          <t>-1002320838727</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>-1002719180481</t>
+          <t>-1003829992194</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>-1001908446355</t>
+          <t>-1001373559245</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>-1002303401228</t>
+          <t>-1001818008631</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>-1003150223688</t>
+          <t>-1002352486010</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>-1002152254687</t>
+          <t>-1003795984362</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>-1003560349248</t>
+          <t>-4974060502</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>-1001668927089</t>
+          <t>-1002898563298</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>-1002321829358</t>
+          <t>-1002541795473</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>-1002114430690</t>
+          <t>-1002342989207</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>-1002695735836</t>
+          <t>6786983715</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>-1002531829054</t>
+          <t>-1002750504156</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>-1001671470841</t>
+          <t>-5212914594</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>-1002750504156</t>
+          <t>-1002510217399</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>-1002812268562</t>
+          <t>-1002320967880</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>-1003560358780</t>
+          <t>-1002478485922</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>-1003776273822</t>
+          <t>-5182817479</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>-1002670277933</t>
+          <t>-1003304830106</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>-1002338100665</t>
+          <t>867824604</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>-1003272164317</t>
+          <t>-1003554414722</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>-5293053713</t>
+          <t>-1002651012796</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>-1002428009204</t>
+          <t>-1002623818368</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>-1003055719997</t>
+          <t>-1003382157325</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>-1003878903675</t>
+          <t>-1002795475468</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>-1002509726671</t>
+          <t>-1002808195180</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>-1002281112145</t>
+          <t>-1003554106710</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>-1002271738387</t>
+          <t>-1002974874463</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>-1002949588128</t>
+          <t>-1002860460728</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>-1002071946221</t>
+          <t>-1002680979996</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>-1002297618669</t>
+          <t>-1001302667285</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>-1002621241174</t>
+          <t>-1003894614780</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>-1002288363987</t>
+          <t>-1002639728798</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>-4852298794</t>
+          <t>-1003857407484</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>-1002795475468</t>
+          <t>-1002999961089</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>-1003502104542</t>
+          <t>-1003624752221</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>-1002778457560</t>
+          <t>-5231222732</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>-4859225688</t>
+          <t>-4822189866</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>-1003785529820</t>
+          <t>-1003094878642</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>-1002582659607</t>
+          <t>-1001908446355</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>-1002388609283</t>
+          <t>-1003227982564</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>-1002288803058</t>
+          <t>-1002600708556</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>-1002659291107</t>
+          <t>-1002915894807</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>-1003894092375</t>
+          <t>-1002571339758</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>-1003865824113</t>
+          <t>-1003057678476</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>-5238910430</t>
+          <t>-1003090299188</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>-1002985739762</t>
+          <t>-4513511178</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>-1002368488534</t>
+          <t>-1003559602288</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>-1003543088788</t>
+          <t>-1002747623711</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>-1003520732236</t>
+          <t>-1001543478413</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>-1002809610954</t>
+          <t>-1002168855114</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>-1002622011374</t>
+          <t>-1003737369393</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>-1003451010325</t>
+          <t>-1003870720812</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>-1002205410222</t>
+          <t>-1002422251622</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>-1002566090891</t>
+          <t>-1003352103344</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>-1003185630550</t>
+          <t>-1002420273008</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>-1002793180948</t>
+          <t>-1001449424790</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>-1003784295528</t>
+          <t>-1003183253419</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>-1002832174643</t>
+          <t>-1002611045810</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>-1003055472631</t>
+          <t>-1003805893950</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>-1002437713625</t>
+          <t>-1003784295528</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>-1002710336139</t>
+          <t>-1002474339744</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>-1002684891199</t>
+          <t>-1002744387247</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>-1002880181368</t>
+          <t>-1002334852527</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>-1003708151846</t>
+          <t>-1003447123747</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>-1002360283286</t>
+          <t>-1002872770022</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>-1002647444996</t>
+          <t>-1002338100665</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>-1001985964144</t>
+          <t>-1002237965843</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>-1003140539585</t>
+          <t>-1002769760671</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>-1002761501601</t>
+          <t>-1002670277933</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>-1002619556227</t>
+          <t>-1002761685886</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>-1003601362039</t>
+          <t>-4925721655</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>-1003092984130</t>
+          <t>-1002320283926</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>-1003002359598</t>
+          <t>-1002016535857</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>-1002651996794</t>
+          <t>-1002288363987</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>-1003671208187</t>
+          <t>-4162328212</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>-1002872579152</t>
+          <t>-1002007016158</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>-1003344556740</t>
+          <t>-1001765476229</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>-1003293930657</t>
+          <t>-1003092228217</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>-1002416638992</t>
+          <t>-1002753083965</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>-1003596125351</t>
+          <t>-1002205410222</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>-1003293940909</t>
+          <t>-1001846329972</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>-1002209520317</t>
+          <t>-5176841635</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>-1002523705245</t>
+          <t>-5114003285</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>-1002016912929</t>
+          <t>-1002530765960</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>-1003870585071</t>
+          <t>-1003002359598</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>-1003751042188</t>
+          <t>-1002365212456</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>-1003055781840</t>
+          <t>-1002395833812</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>-1003759164664</t>
+          <t>-1003177468537</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>-1003011064222</t>
+          <t>-1002632678475</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>-1002092120695</t>
+          <t>-1003856867815</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>-1001540741017</t>
+          <t>-1003453389134</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>-4819895741</t>
+          <t>-5214487805</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>-1001611710912</t>
+          <t>-4877376604</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>-1002990158729</t>
+          <t>-1003462101210</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>-1002809543928</t>
+          <t>-1003848351434</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>-1002377976370</t>
+          <t>-1003845773021</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>-1002106096413</t>
+          <t>-1002593143797</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>-4964952099</t>
+          <t>-1001298208876</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>-1003094634117</t>
+          <t>-4859108486</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>-1003313884514</t>
+          <t>-1002651560084</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>-1003697454154</t>
+          <t>-1002778457560</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>-1002532154366</t>
+          <t>-1003605325965</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>-1003864575810</t>
+          <t>-1003739476321</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>-1003609759956</t>
+          <t>-1002695735836</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>-1003447123747</t>
+          <t>-1003650147257</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>-1003352103344</t>
+          <t>-1002465441179</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>-1002870267087</t>
+          <t>-1002836592504</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>-1002614518240</t>
+          <t>-1002318473731</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>-1002575818224</t>
+          <t>-1003116317699</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>-1002658418497</t>
+          <t>-1002729517184</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>-1002580159815</t>
+          <t>-1002983071868</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>-1003704472568</t>
+          <t>-1003563627055</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>6786983715</t>
+          <t>-1003122716300</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>-1001744426195</t>
+          <t>-1002684891199</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>-1002588140799</t>
+          <t>-1003066477129</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>-1002901874691</t>
+          <t>-1003841442683</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>-1003192981088</t>
+          <t>-1002423915712</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>-1002289430922</t>
+          <t>-1003092984130</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>-1002455033621</t>
+          <t>-1002150947419</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>-1002508916910</t>
+          <t>-1002250659534</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>-1002560099813</t>
+          <t>-1003560349248</t>
         </is>
       </c>
     </row>
@@ -2195,2086 +2195,2086 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>-1001921955585</t>
+          <t>-4912413878</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>-5276076774</t>
+          <t>-1003169930553</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>-1002551612447</t>
+          <t>-1002834499433</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>-1003105061815</t>
+          <t>-1002566090891</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>-1002702700644</t>
+          <t>-1003888265357</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>-1002864485836</t>
+          <t>-1002832174643</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>-1002175510705</t>
+          <t>-1002529665437</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>-1001741252369</t>
+          <t>-1002103104897</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>-1002977896648</t>
+          <t>-1002540598427</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>-1001307311832</t>
+          <t>-1003887146140</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>-1003046279469</t>
+          <t>-1002799861129</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>-1002359874556</t>
+          <t>-1003520732236</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>-1003100265374</t>
+          <t>-1003048673651</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>-1002990734165</t>
+          <t>-1002403581849</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>-1002464524981</t>
+          <t>-1002092120695</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>-1002836592504</t>
+          <t>-1002031457701</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>-1003739476321</t>
+          <t>-1002073440916</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>-1003385914148</t>
+          <t>-1002265393780</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>-1003094878642</t>
+          <t>-1003839394701</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>-1002760392715</t>
+          <t>-1003313884514</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>-4162328212</t>
+          <t>-1002832167728</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>-1003090299188</t>
+          <t>-1002016912929</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>-1002491853737</t>
+          <t>-1002567310940</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>-1003554106710</t>
+          <t>-1002512266739</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>-1002318473731</t>
+          <t>-1003483467807</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>-1002555387875</t>
+          <t>-1002428009204</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>-4989200624</t>
+          <t>-1002872579152</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>-1002587384955</t>
+          <t>-1001546837418</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>-1003180215428</t>
+          <t>-1003704472568</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>-1003246680728</t>
+          <t>-1003864575810</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>-1002359134904</t>
+          <t>-4636171342</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>-1002101571866</t>
+          <t>-1002118631320</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>-4877376604</t>
+          <t>-1002340618636</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>-1002190969931</t>
+          <t>-1002372506024</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>-1003483467807</t>
+          <t>-1003427818585</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>-1002651560084</t>
+          <t>-1002588140799</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>-1002178056369</t>
+          <t>-1003048077625</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>-1002391001829</t>
+          <t>-5264614378</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>-1002372506024</t>
+          <t>-1002615496638</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>-1003635435133</t>
+          <t>-1002985739762</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>-1002541795473</t>
+          <t>-1002887675015</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>-1003229025294</t>
+          <t>-1003118640750</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>-1003579299494</t>
+          <t>-1003022236579</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>-1002904756274</t>
+          <t>-1002638064433</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>-1001807175468</t>
+          <t>-1002778350864</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>-1003445206607</t>
+          <t>-1003558199964</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>-1003856867815</t>
+          <t>-1002778085921</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>-1003858324278</t>
+          <t>-1003485367302</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>-1002226982992</t>
+          <t>-1002342685523</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>-1001735560772</t>
+          <t>-1003882816542</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>-1001467801859</t>
+          <t>-4863520102</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>-1002532871843</t>
+          <t>-1002887971256</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>-1002522608034</t>
+          <t>-1002420900028</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>-1002683965508</t>
+          <t>-1002114430690</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>-1001460104025</t>
+          <t>-1002281112145</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>-1002368728861</t>
+          <t>-1003811694462</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>-1002512266739</t>
+          <t>-1003449656757</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>-1002661244330</t>
+          <t>-1003650931988</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>-4863520102</t>
+          <t>-1001467801859</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>-1002918117363</t>
+          <t>-1002715650097</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>-1002110839951</t>
+          <t>-1002904756274</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>-1002999961089</t>
+          <t>-1002712833331</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>-1002540598427</t>
+          <t>-1003577178993</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>-1002611045810</t>
+          <t>-1003421411518</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>-1002478485922</t>
+          <t>-1002531829054</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>-1002128565721</t>
+          <t>-1001307311832</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>-5182817479</t>
+          <t>-1002522608034</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>-1003035504222</t>
+          <t>-1002560099813</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>-1002825020185</t>
+          <t>-1003456241208</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>-1003500481482</t>
+          <t>-1002392635902</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>-1002834499433</t>
+          <t>-1002359874556</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>-1002808195180</t>
+          <t>-1001493770434</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>-1003389444837</t>
+          <t>-1002734752869</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>-5212914594</t>
+          <t>-1002664729996</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>-1003050031260</t>
+          <t>-1002437713625</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>-1001665462509</t>
+          <t>-1003229025294</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>-1002320283926</t>
+          <t>-5181397583</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>-1001373559245</t>
+          <t>-1002418585410</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>-1003690052299</t>
+          <t>-1002491853737</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>-1002734752869</t>
+          <t>-1001690032632</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>-1002422251622</t>
+          <t>-1002606190918</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>-1003007832445</t>
+          <t>-1003307893033</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>-1001765476229</t>
+          <t>-1002101571866</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>-1003805893950</t>
+          <t>-1003583886956</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>-4961873359</t>
+          <t>-1003694114079</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>-1002016535857</t>
+          <t>-4863174120</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>-1002448038408</t>
+          <t>-1002719180481</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>-1002624308239</t>
+          <t>-1003354035186</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>-1001212305259</t>
+          <t>-1003756210868</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>-5176841635</t>
+          <t>-1002217503260</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>-1003613698828</t>
+          <t>-1001460104025</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>-1001298208876</t>
+          <t>-1002622011374</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>-1002096741759</t>
+          <t>-1002518556633</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>-1002073440916</t>
+          <t>-1002779291814</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>-1002623818368</t>
+          <t>-1002916180495</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>-1002853960198</t>
+          <t>-1003417970722</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>-1002753083965</t>
+          <t>-1003055362508</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>-1002886657320</t>
+          <t>-1003864264998</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>-1002586036097</t>
+          <t>-1003150749086</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>-1002621836135</t>
+          <t>-1002046646497</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>-4964721197</t>
+          <t>-1003798585147</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>-1002593143797</t>
+          <t>-1003364207368</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>-1001817635995</t>
+          <t>-1002509726671</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>-1003870720812</t>
+          <t>-1002702700644</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>-1002077075261</t>
+          <t>-4859225688</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>-1003577178993</t>
+          <t>-1003055472631</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>-1003650147257</t>
+          <t>-1003094634117</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>-1002552125741</t>
+          <t>-1001922808139</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>-1003563627055</t>
+          <t>-1002597892903</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>-1001701084460</t>
+          <t>-1002864485836</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>-1002809659148</t>
+          <t>-1003093812371</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>-1002860460728</t>
+          <t>-1002509299058</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>-1003177115454</t>
+          <t>-1002178056369</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>-1002167448908</t>
+          <t>-1002011515239</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>-1003756210868</t>
+          <t>-1003289156239</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>-1002651012796</t>
+          <t>-1002144563093</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>-1001652492827</t>
+          <t>-4999679751</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>-1003503147352</t>
+          <t>-1002722253045</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>-1001406184711</t>
+          <t>-1002860463322</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>-1002414175598</t>
+          <t>-1002822883977</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>-1002761573267</t>
+          <t>-1003790261630</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>-1002915894807</t>
+          <t>-1001668927089</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>-1001885408615</t>
+          <t>-1002335271770</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>-1001647712873</t>
+          <t>-4961873359</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>-4921455900</t>
+          <t>-1001923225361</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>-1002365212456</t>
+          <t>-1002493291997</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>-1002519990156</t>
+          <t>-1002534699760</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>-1001543478413</t>
+          <t>-1003070751342</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>-1003427818585</t>
+          <t>-1002990734165</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>-1002144563093</t>
+          <t>-1002551612447</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>-1003719969742</t>
+          <t>-1002278762192</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>-1003673427063</t>
+          <t>-1003207138530</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>-1002664729996</t>
+          <t>-1003628737566</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>-1002342685523</t>
+          <t>-1001596465392</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>-1002616170042</t>
+          <t>-1002877287868</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>-1003177468537</t>
+          <t>-1002901874691</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>-4912413878</t>
+          <t>-1002581029977</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>-1001796760199</t>
+          <t>-1002840970643</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>-1003307893033</t>
+          <t>-4884314925</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>-1001846329972</t>
+          <t>-1002556802461</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>-1002250659534</t>
+          <t>-1002192798016</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>-1001868146441</t>
+          <t>-1001647712873</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>-1003217773561</t>
+          <t>-4921455900</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>-1002848062475</t>
+          <t>-1002077075261</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>-1002040217076</t>
+          <t>-1001885408615</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>-1002744387247</t>
+          <t>-1003894092375</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>-1002706892578</t>
+          <t>-1001994788372</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>-1003527335437</t>
+          <t>-1003782057933</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>-1003141918793</t>
+          <t>-1002832898246</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>-1003666715930</t>
+          <t>-1003681847296</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>-1002234774760</t>
+          <t>-1001357883446</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>-1002799861129</t>
+          <t>-1001406184711</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>-1001674602550</t>
+          <t>-1002908266830</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>-1002529665437</t>
+          <t>-1003645590334</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>-1002518556633</t>
+          <t>-4989200624</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>-1001124651563</t>
+          <t>-1002448038408</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>-1002074104758</t>
+          <t>-1003150223688</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>-1002170512400</t>
+          <t>-1002250428372</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>-1001900924039</t>
+          <t>-1003889493565</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>-1003701419543</t>
+          <t>-1002555387875</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>-1003048077625</t>
+          <t>-1002532871843</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>-1001473268532</t>
+          <t>-1002579287925</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>-1002764128440</t>
+          <t>-1002582659607</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>-1003022236579</t>
+          <t>-1002508916910</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>-1003848351434</t>
+          <t>-1002873170822</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>-1002615496638</t>
+          <t>-1003141918793</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>-1003839394701</t>
+          <t>-1002368728861</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>-4513511178</t>
+          <t>-1002234774760</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>-1003587135671</t>
+          <t>-1002753235468</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>-1002265393780</t>
+          <t>-1001950007498</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>-1003417970722</t>
+          <t>-1001635430845</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>-1002753235468</t>
+          <t>-1003451010325</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>-1002679523819</t>
+          <t>-1002956645130</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>-1003864264998</t>
+          <t>-1002322838597</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>-1002510217399</t>
+          <t>-1003635435133</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>-1002582926621</t>
+          <t>-1002870267087</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>-1002379714369</t>
+          <t>-1002464524981</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>-4884314925</t>
+          <t>-1002414175598</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>-1002715650097</t>
+          <t>-1003038352740</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>-1001357883446</t>
+          <t>-1003205119561</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>-1003661050854</t>
+          <t>-1002706892578</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>-1002168855114</t>
+          <t>-1002486834455</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>-1002591852942</t>
+          <t>-1003560358780</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>8002682623</t>
+          <t>-1002880181368</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>-1003116317699</t>
+          <t>-1003007832445</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>-1003150749086</t>
+          <t>-4964721197</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>-1002830324668</t>
+          <t>-1003025068781</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>-1003554414722</t>
+          <t>-1002619575978</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>-1003550392581</t>
+          <t>-1003777534388</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>-1003795984362</t>
+          <t>-1003084989152</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>-1002335271770</t>
+          <t>-1002368488534</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>-1003317755929</t>
+          <t>-1003415576816</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>867824604</t>
+          <t>-1001674602550</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>-1003841442683</t>
+          <t>-1001779368673</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>-1002420273008</t>
+          <t>-1002309114039</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>-1001690032632</t>
+          <t>-1002303401228</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>-1003845773021</t>
+          <t>-1002096741759</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>-1002486834455</t>
+          <t>-1002514951234</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>-1002579055686</t>
+          <t>-1003389444837</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>-1002870201502</t>
+          <t>-1003177115454</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>-1001859766402</t>
+          <t>-1003789732989</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>-1003239240721</t>
+          <t>-1003246680728</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>-1002776521317</t>
+          <t>-1002268045818</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>-1003628737566</t>
+          <t>-4852298794</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>-4901343480</t>
+          <t>-1002957130138</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>-1003343499093</t>
+          <t>-1003622694978</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>-1003559602288</t>
+          <t>-1002679523819</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>-1002947162126</t>
+          <t>-1002760607433</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>-1002908266830</t>
+          <t>-1003503147352</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>-1003027038967</t>
+          <t>-1002830324668</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>-1001922808139</t>
+          <t>-1002600128976</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>-1002832898246</t>
+          <t>-1003001093483</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>-1002359766306</t>
+          <t>-1001124651563</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>-1002103104897</t>
+          <t>-1002848062475</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>-1002889377215</t>
+          <t>-1001900924039</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>-1002418585410</t>
+          <t>-1003505125164</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>-1002887971256</t>
+          <t>-1002782716052</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>-1002579287925</t>
+          <t>-1003129624230</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>-1002556802461</t>
+          <t>-1002419890323</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>-1002974874463</t>
+          <t>-1003878903675</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>-1003312077048</t>
+          <t>-1002586036097</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>-1003737369393</t>
+          <t>-1002155445752</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>-1002860463322</t>
+          <t>-1002289430922</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>-1002600708556</t>
+          <t>-1003579299494</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>-4859108486</t>
+          <t>-1002990158729</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>-1002826605956</t>
+          <t>-1001807175468</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>-1001818742779</t>
+          <t>-1003110118065</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>-1001449424790</t>
+          <t>-1002297618669</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>-1002385566540</t>
+          <t>-1002300324334</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>-1003131016214</t>
+          <t>-1003701419543</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>-1002274964696</t>
+          <t>-1002367453033</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>-1003897294884</t>
+          <t>-1002744838888</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>-1003702553153</t>
+          <t>-1002391001829</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>-1002493291997</t>
+          <t>-1003217773561</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>-1003657106230</t>
+          <t>-1002591852942</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>-1001946166876</t>
+          <t>-1002278564823</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>-4925721655</t>
+          <t>-1003389986244</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>-1002150947419</t>
+          <t>-1003343499093</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>-1002729517184</t>
+          <t>-1002754377559</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>-1002360094196</t>
+          <t>-1003556812442</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>-1002927005745</t>
+          <t>-5293053713</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>-1002562282389</t>
+          <t>-1003751042188</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>-1002873170822</t>
+          <t>-4901343480</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>-1002482355272</t>
+          <t>-1002825020185</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>-1002638064433</t>
+          <t>-1003697454154</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>-1002007016158</t>
+          <t>-1002624308239</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>-1003371546403</t>
+          <t>-1002457910402</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>-1002916180495</t>
+          <t>-1002886657320</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>-1002877287868</t>
+          <t>-1002772423367</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>-1002403581849</t>
+          <t>-1002793180948</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>-1003894614780</t>
+          <t>-1002826605956</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>-1002278564823</t>
+          <t>-1003810708157</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>-1002640591890</t>
+          <t>-1002815867232</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>-1002832167728</t>
+          <t>-1002226982992</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>-1002956645130</t>
+          <t>-1002595442276</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>-1002618584679</t>
+          <t>-1003587135671</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>-1001818008631</t>
+          <t>-1002520212825</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>-1003583886956</t>
+          <t>-1002288129210</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>-1002597892903</t>
+          <t>-1003338695620</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>-1002155445752</t>
+          <t>-1002853960198</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>-1003487427178</t>
+          <t>-1001453302193</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>-1002822883977</t>
+          <t>-1002522147223</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>-1002813643590</t>
+          <t>-1003272164317</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>-1002606190918</t>
+          <t>-1001671470841</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>-1002815867232</t>
+          <t>-4952186637</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>-1002395833812</t>
+          <t>-1003312077048</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>-4952186637</t>
+          <t>-1002106096413</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>-1002474339744</t>
+          <t>-1003050031260</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>-1003782057933</t>
+          <t>-1002640591890</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>-4863174120</t>
+          <t>-1003865487649</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>-1003462101210</t>
+          <t>-1002288803058</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>-1002531024619</t>
+          <t>-1003185630550</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>-1003149481043</t>
+          <t>-1002683965508</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>-1002518094653</t>
+          <t>-1003850370610</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>-1002255365525</t>
+          <t>-1003192981088</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>-1002514951234</t>
+          <t>-1002209520317</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>-1001390053729</t>
+          <t>-1003582386162</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>-4979055727</t>
+          <t>-1003011064222</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>-1001929868118</t>
+          <t>-1001868146441</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>-1003122716300</t>
+          <t>-1002416638992</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>-1003605325965</t>
+          <t>-1003105061815</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>-1003102873353</t>
+          <t>-1002130498457</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>-1003070751342</t>
+          <t>-1002764128440</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>-1003456241208</t>
+          <t>-1002927005745</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>-1003323511757</t>
+          <t>-1003500481482</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>-1003811694462</t>
+          <t>-1002071946221</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>-1003421411518</t>
+          <t>-1003460209587</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>-1002703131951</t>
+          <t>-1001665462509</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>-1002011515239</t>
+          <t>-1001701084460</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>-1002169700144</t>
+          <t>-1002580159815</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>-1002722253045</t>
+          <t>-1002110839951</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>-1002092627141</t>
+          <t>-1001801324223</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>-1002632678475</t>
+          <t>-1003702553153</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>-5114003285</t>
+          <t>-1002621836135</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>-1003888265357</t>
+          <t>-1002870201502</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>-1002619575978</t>
+          <t>-1003881956622</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>-1003645590334</t>
+          <t>-1002393739109</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>-1002782716052</t>
+          <t>-1003323511757</t>
         </is>
       </c>
     </row>
@@ -4288,217 +4288,315 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>-1003453389134</t>
+          <t>-1002321829358</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>-1002237965843</t>
+          <t>-4562050705</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>-1003509730808</t>
+          <t>-1002879625349</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>-1003227982564</t>
+          <t>-1002379714369</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>-4822189866</t>
+          <t>-1002812268562</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>-1002420900028</t>
+          <t>-1002616170042</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>-1002957130138</t>
+          <t>-1003844657847</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>-1003694114079</t>
+          <t>-1003301419264</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>-1003798585147</t>
+          <t>-1003858324278</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>-1002680979996</t>
+          <t>-1001390053729</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>-5181397583</t>
+          <t>-1002947162126</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>-1002534699760</t>
+          <t>-1003027038967</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>-1003622694978</t>
+          <t>-1002285297701</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>-1001730809010</t>
+          <t>-1002761501601</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>-1003881956622</t>
+          <t>-1002482355272</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>-4977264275</t>
+          <t>-1003527335437</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>-1003093812371</t>
+          <t>-1002523705245</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>-1003129624230</t>
+          <t>-1002360094196</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>-1003415576816</t>
+          <t>-1003708151846</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>-1002457910402</t>
+          <t>-1002532154366</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>-1003092228217</t>
+          <t>-1002263664644</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>-1002419890323</t>
+          <t>-1003863407262</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>-1002278762192</t>
+          <t>-4941172345</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>-1002342989207</t>
+          <t>-1002866910509</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>-1002320838727</t>
+          <t>-1003102873353</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>-1002595442276</t>
+          <t>-5276076774</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>-1002713471991</t>
+          <t>-1002170512400</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>-1002840970643</t>
+          <t>-1002813643590</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>-1002712833331</t>
+          <t>-1002903801746</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>-1003048673651</t>
+          <t>-1003100265374</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>-1003066477129</t>
+          <t>-1003870585071</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>-1002152254687</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>-1001611710912</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>-1002549453056</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>-1003055781840</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>6667684577</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>-1003657106230</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>-1002167448908</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>-1001817635995</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>-1001818742779</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>-1002870935153</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>-1003385914148</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>-1002889377215</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>-1001729071175</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>-1003035504222</t>
         </is>
       </c>
     </row>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>-1002359766306</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,21 +438,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5080276560</t>
+          <t>-1002359766306</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-1002114430690</t>
+          <t>5080276560</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-1002359766306</t>
+          <t>-1002114430690</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>-1001817635995</t>
         </is>
       </c>
     </row>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,28 +438,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-1002359766306</t>
+          <t>5080276560</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5080276560</t>
+          <t>-1002114430690</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-1002114430690</t>
+          <t>-1001817635995</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-1001817635995</t>
+          <t>-1002359766306</t>
         </is>
       </c>
     </row>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,7 +438,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5080276560</t>
+          <t>-1003354035186</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-1001817635995</t>
+          <t>-1003205119561</t>
         </is>
       </c>
     </row>
@@ -460,6 +460,27 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>-1002359766306</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>867824604</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>-1001817635995</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5080276560</t>
         </is>
       </c>
     </row>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,49 +438,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-1003354035186</t>
+          <t>-1003205119561</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-1002114430690</t>
+          <t>867824604</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-1003205119561</t>
+          <t>5080276560</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-1002359766306</t>
+          <t>-1003354035186</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>867824604</t>
+          <t>-1001817635995</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-1001817635995</t>
+          <t>-1002114430690</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5080276560</t>
+          <t>-1002359766306</t>
         </is>
       </c>
     </row>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -438,49 +438,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-1003205119561</t>
+          <t>5080276560</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>867824604</t>
+          <t>-1002114430690</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5080276560</t>
+          <t>-1001817635995</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-1003354035186</t>
+          <t>-1002359766306</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>-1001817635995</t>
+          <t>867824604</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-1002114430690</t>
+          <t>-1003354035186</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-1002359766306</t>
+          <t>-1003205119561</t>
         </is>
       </c>
     </row>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,21 +445,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-1002114430690</t>
+          <t>-1001817635995</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-1001817635995</t>
+          <t>-1002359766306</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-1002359766306</t>
+          <t>-1002114430690</t>
         </is>
       </c>
     </row>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,49 +438,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5080276560</t>
+          <t>-1003354035186</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-1001817635995</t>
+          <t>867824604</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-1002359766306</t>
+          <t>-1003205119561</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-1002114430690</t>
+          <t>-1001817635995</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>867824604</t>
+          <t>5080276560</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-1003354035186</t>
+          <t>-1002114430690</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-1003205119561</t>
+          <t>-5033878244</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>-1002359766306</t>
         </is>
       </c>
     </row>

--- a/UserScore/RegisteredGroups.xlsx
+++ b/UserScore/RegisteredGroups.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,56 +438,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-1003354035186</t>
+          <t>-1003205119561</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>867824604</t>
+          <t>-1003354035186</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-1003205119561</t>
+          <t>-1002114430690</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-1001817635995</t>
+          <t>867824604</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5080276560</t>
+          <t>-1002359766306</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-1002114430690</t>
+          <t>-5033878244</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-5033878244</t>
+          <t>-1001817635995</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-1002359766306</t>
+          <t>5080276560</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>-1003818345268</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>-1003525199555</t>
         </is>
       </c>
     </row>
